--- a/tame_output/ON/bt/strategyON_20240915.xlsx
+++ b/tame_output/ON/bt/strategyON_20240915.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-58.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-98.7%</t>
+          <t>-95.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.3%</t>
+          <t>104.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.678296988460028</v>
+        <v>-4.654515880672675</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.804240456208853</v>
+        <v>1.813752899323794</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7094164514126027</v>
+        <v>0.733197559199956</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.101565546754173</v>
+        <v>4.115834211426586</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.581662076441388</v>
+        <v>-4.557880968654035</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.659078417140243</v>
+        <v>1.668590860255184</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8060513634312426</v>
+        <v>0.8298324712185959</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.975730490089292</v>
+        <v>3.989999154761704</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.712242810972231</v>
+        <v>-4.688461703184878</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.61034816740187</v>
+        <v>1.619860610516811</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6754706289004001</v>
+        <v>0.6992517366877534</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.900884093444751</v>
+        <v>3.915152758117163</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.547746476781269</v>
+        <v>-4.523965368993916</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.660573520154338</v>
+        <v>1.670085963269279</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.839966963091362</v>
+        <v>0.8637480708787153</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.98400871303541</v>
+        <v>3.998277377707822</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.470647875239396</v>
+        <v>-4.446866767452043</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.690600671207516</v>
+        <v>1.700113114322457</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.839966963091362</v>
+        <v>0.8637480708787153</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.98319642347184</v>
+        <v>3.997465088144252</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.481033070129286</v>
+        <v>-4.457251962341933</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.696315372376633</v>
+        <v>1.705827815491574</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8295817682014727</v>
+        <v>0.853362875988826</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.986834085662979</v>
+        <v>4.001102750335392</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.499621228851511</v>
+        <v>-4.475840121064158</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.759717114664168</v>
+        <v>1.769229557779109</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8109936094792474</v>
+        <v>0.8347747172666007</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.046518196206069</v>
+        <v>4.060786860878481</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.499919775547546</v>
+        <v>-4.476138667760194</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.756466706804052</v>
+        <v>1.765979149918993</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8106950627832115</v>
+        <v>0.8344761705705648</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.043208079006746</v>
+        <v>4.057476743679158</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.399096641857119</v>
+        <v>-4.375315534069766</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.801326855219615</v>
+        <v>1.810839298334556</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8231592782675653</v>
+        <v>0.8469403860549186</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.05521750323675</v>
+        <v>4.069486167909162</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.208315281104712</v>
+        <v>-4.184534173317358</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.877768652999121</v>
+        <v>1.887281096114062</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.013940639019973</v>
+        <v>1.037721746807326</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.169815573166738</v>
+        <v>4.18408423783915</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.10135192325529</v>
+        <v>-4.077570815467936</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.900390841876486</v>
+        <v>1.909903284991428</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.072405246979774</v>
+        <v>1.096186354767128</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.184731183680215</v>
+        <v>4.198999848352627</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.046021335353528</v>
+        <v>-4.022240227566174</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.95749001364925</v>
+        <v>1.967002456764191</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.127735834881536</v>
+        <v>1.15151694266889</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.252896473033331</v>
+        <v>4.267165137705742</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.033967208440565</v>
+        <v>-4.010186100653211</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.955998232315872</v>
+        <v>1.965510675430814</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.139789961794499</v>
+        <v>1.163571069581852</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.253815517082546</v>
+        <v>4.268084181754958</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.075122328008786</v>
+        <v>-4.051341220221432</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.94141681467272</v>
+        <v>1.950929257787661</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.098634842226278</v>
+        <v>1.122415950013631</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.23100307552575</v>
+        <v>4.245271740198161</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.007073765317256</v>
+        <v>-3.983292657529902</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.981487265627214</v>
+        <v>1.990999708742156</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.166683404917808</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.28468323901855</v>
+        <v>4.298951903690962</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.238674158486757</v>
+        <v>-4.214893050699403</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.909049778533008</v>
+        <v>1.918562221647949</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.166683404917808</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.304885909192144</v>
+        <v>4.319154573864556</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.288725704015976</v>
+        <v>-4.264944596228622</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.872635396388203</v>
+        <v>1.882147839503144</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.166683404917808</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.288492145259026</v>
+        <v>4.302760809931438</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.46383253659242</v>
+        <v>-4.440051428805067</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.762844576951091</v>
+        <v>1.772357020066033</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.166683404917808</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.248744058852493</v>
+        <v>4.263012723524905</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.267732383161897</v>
+        <v>-4.243951275374544</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.848307257320241</v>
+        <v>1.857819700435182</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.362783558348331</v>
+        <v>1.386564666135684</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.373426769907747</v>
+        <v>4.387695434580158</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.114706991048613</v>
+        <v>-4.090925883261259</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.008688413738459</v>
+        <v>2.0182008568534</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.515808950461615</v>
+        <v>1.539590058248968</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.564413004748621</v>
+        <v>4.578681669421033</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.143014304921883</v>
+        <v>-4.11923319713453</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.184831713097443</v>
+        <v>2.194344156212384</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.515808950461615</v>
+        <v>1.539590058248968</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.751879229656914</v>
+        <v>4.766147894329325</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.309607530035406</v>
+        <v>-4.285826422248052</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.087597374406117</v>
+        <v>2.097109817521059</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.349215725348093</v>
+        <v>1.372996833135446</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.621326245942883</v>
+        <v>4.635594910615294</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.28657173667384</v>
+        <v>-4.262790628886486</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.100488094412461</v>
+        <v>2.110000537527402</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.349215725348093</v>
+        <v>1.372996833135446</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.625002648604601</v>
+        <v>4.639271313277012</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.257325756218143</v>
+        <v>-4.233544648430789</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.109804541718235</v>
+        <v>2.119316984833176</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.349215725348093</v>
+        <v>1.372996833135446</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.622620703728096</v>
+        <v>4.636889368400508</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.364251304095994</v>
+        <v>-4.34047019630864</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.064327561724729</v>
+        <v>2.073840004839671</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.242290177470241</v>
+        <v>1.266071285257595</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.555758614159021</v>
+        <v>4.570027278831432</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.509269862603243</v>
+        <v>-4.485488754815889</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.007748940465064</v>
+        <v>2.017261383580006</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.097271618962993</v>
+        <v>1.121052726750346</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.470176281197905</v>
+        <v>4.484444945870317</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.62761162838796</v>
+        <v>-4.603830520600606</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.06034347340893</v>
+        <v>2.069855916523872</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.107957657525883</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.576519143593393</v>
+        <v>4.590787808265804</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.679022050708668</v>
+        <v>-4.655240942921314</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.037565001606586</v>
+        <v>2.047077444721528</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.107957657525883</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.574304840719331</v>
+        <v>4.588573505391744</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.75844150191642</v>
+        <v>-4.734660394129066</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.005700349197775</v>
+        <v>2.015212792312716</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.107957657525883</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.574207968793621</v>
+        <v>4.588476633466033</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.853904499833638</v>
+        <v>-4.830123392046284</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.96750904358893</v>
+        <v>1.977021486703872</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.107957657525883</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.574201862351663</v>
+        <v>4.588470527024076</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.789528588982923</v>
+        <v>-4.765747481195569</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.991355804491827</v>
+        <v>2.000868247606769</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.172333568376598</v>
+        <v>1.196114676163951</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.610923805424703</v>
+        <v>4.625192470097115</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.844897751115116</v>
+        <v>-4.821116643327763</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.974941957386676</v>
+        <v>1.984454400501618</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.172333568376598</v>
+        <v>1.196114676163951</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.61665762317243</v>
+        <v>4.630926287844842</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.890335530945944</v>
+        <v>-4.86655442315859</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.956305208797278</v>
+        <v>1.96581765191222</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.129488577698438</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.590488992108467</v>
+        <v>4.604757656780879</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.802128696798365</v>
+        <v>-4.778347589011012</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.011462335306628</v>
+        <v>2.02097477842157</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.129488577698438</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.610363384958785</v>
+        <v>4.624632049631197</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.696093701593056</v>
+        <v>-4.672312593805702</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.03757703391348</v>
+        <v>2.047089477028421</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.129488577698438</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.594064085483513</v>
+        <v>4.608332750155925</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.512882038459961</v>
+        <v>-4.489100930672607</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.113292648630763</v>
+        <v>2.122805091745705</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.129488577698438</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.596495034947559</v>
+        <v>4.61076369961997</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.44116059144611</v>
+        <v>-4.417379483658756</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.107772413284193</v>
+        <v>2.117284856399135</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.201210024712289</v>
+        <v>1.224991132499643</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.605319089003759</v>
+        <v>4.619587753676171</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.418787565838404</v>
+        <v>-4.39500645805105</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.063637369448447</v>
+        <v>2.073149812563389</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.212465775825191</v>
+        <v>1.236246883612544</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.558988285592672</v>
+        <v>4.573256950265083</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.451803861749148</v>
+        <v>-4.428022753961795</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.235629055969505</v>
+        <v>2.245141499084446</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.143028399158439</v>
+        <v>1.166809506945792</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.702524064477975</v>
+        <v>4.716792729150388</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.44027622609954</v>
+        <v>-4.416495118312186</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.232161336057597</v>
+        <v>2.241673779172539</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.202029057359802</v>
+        <v>1.225810165147155</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.729845685227042</v>
+        <v>4.744114349899454</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.537617727441908</v>
+        <v>-4.513836619654555</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.196892848042438</v>
+        <v>2.20640529115738</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.157608875194313</v>
+        <v>1.181389982981667</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.706861688449537</v>
+        <v>4.72113035312195</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.623473756781875</v>
+        <v>-4.599692648994521</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.16380151849929</v>
+        <v>2.173313961614231</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.115232805968178</v>
+        <v>1.139013913755532</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.682687129106695</v>
+        <v>4.696955793779107</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.632310554197995</v>
+        <v>-4.608529446410641</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.142686001353344</v>
+        <v>2.152198444468286</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.107790633326827</v>
+        <v>1.131571741114181</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.660641027342386</v>
+        <v>4.674909692014799</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.723693116763453</v>
+        <v>-4.699912008976099</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.11629748737221</v>
+        <v>2.125809930487152</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.071225748607483</v>
+        <v>1.095006856394836</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.648866607555829</v>
+        <v>4.663135272228241</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.711986398776447</v>
+        <v>-4.688205290989093</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.22310843239128</v>
+        <v>2.232620875506221</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.082932466594489</v>
+        <v>1.106713574381843</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.7580188961723</v>
+        <v>4.772287560844712</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.612322894692785</v>
+        <v>-4.588541786905431</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.266006172756149</v>
+        <v>2.275518615871091</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.146119549798176</v>
+        <v>1.169900657585529</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.798963484825917</v>
+        <v>4.813232149498329</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.622638992859136</v>
+        <v>-4.598857885071783</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.474784566767667</v>
+        <v>2.484297009882608</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.146119549798176</v>
+        <v>1.169900657585529</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.011868318103975</v>
+        <v>5.026136982776387</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.622545024841764</v>
+        <v>-4.59876391705441</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.474000820886705</v>
+        <v>2.483513264001647</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.011268901824455</v>
+        <v>5.025537566496867</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.629763849041608</v>
+        <v>-4.605982741254254</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.465345277151122</v>
+        <v>2.474857720266063</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.005500887768809</v>
+        <v>5.019769552441221</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.62881542592357</v>
+        <v>-4.605034318136216</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.465724646398337</v>
+        <v>2.475237089513278</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.005500887768809</v>
+        <v>5.019769552441221</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.785883884179194</v>
+        <v>-4.76210277639184</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.415624871077179</v>
+        <v>2.425137314192121</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.018228495749901</v>
+        <v>5.032497160422313</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.779891637390382</v>
+        <v>-4.756110529603029</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.419967768217091</v>
+        <v>2.429480211332033</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.020174494174289</v>
+        <v>5.034443158846701</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.691333676259615</v>
+        <v>-4.667552568472261</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.449045088687168</v>
+        <v>2.458557531802109</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.013828630192058</v>
+        <v>5.02809729486447</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.673574598756541</v>
+        <v>-4.649793490969187</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.455457397127393</v>
+        <v>2.464969840242334</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.013137307631053</v>
+        <v>5.027405972303465</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.573944447707473</v>
+        <v>-4.550163339920119</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.508091643455606</v>
+        <v>2.517604086570548</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.246119562194561</v>
+        <v>1.269900669981915</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.085697584169081</v>
+        <v>5.099966248841493</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.888304885083782</v>
+        <v>3.83450042032714</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.624830452270481</v>
+        <v>-4.625013028203604</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.67689150712913</v>
+        <v>2.676818476755881</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.253360259260344</v>
+        <v>1.280675322229741</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.279196267907277</v>
+        <v>5.295585305688915</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240915.xlsx
+++ b/tame_output/ON/bt/strategyON_20240915.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>60.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-624.1%</t>
+          <t>-618.9%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-108.5%</t>
+          <t>-106.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.1%</t>
+          <t>-58.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-95.9%</t>
+          <t>-99.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>114.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>104.5%</t>
+          <t>103.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.654515880672675</v>
+        <v>-4.678296988460028</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.813752899323794</v>
+        <v>1.804240456208853</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.733197559199956</v>
+        <v>0.7094164514126027</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.115834211426586</v>
+        <v>4.101565546754173</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.557880968654035</v>
+        <v>-4.581662076441388</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.668590860255184</v>
+        <v>1.659078417140243</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8298324712185959</v>
+        <v>0.8060513634312426</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.989999154761704</v>
+        <v>3.975730490089292</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.688461703184878</v>
+        <v>-4.712242810972231</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.619860610516811</v>
+        <v>1.61034816740187</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6992517366877534</v>
+        <v>0.6754706289004001</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.915152758117163</v>
+        <v>3.900884093444751</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.523965368993916</v>
+        <v>-4.547746476781269</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.670085963269279</v>
+        <v>1.660573520154338</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8637480708787153</v>
+        <v>0.839966963091362</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.998277377707822</v>
+        <v>3.98400871303541</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.446866767452043</v>
+        <v>-4.470647875239396</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.700113114322457</v>
+        <v>1.690600671207516</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8637480708787153</v>
+        <v>0.839966963091362</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.997465088144252</v>
+        <v>3.98319642347184</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.457251962341933</v>
+        <v>-4.481033070129286</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.705827815491574</v>
+        <v>1.696315372376633</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.853362875988826</v>
+        <v>0.8295817682014727</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.001102750335392</v>
+        <v>3.986834085662979</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.475840121064158</v>
+        <v>-4.499621228851511</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.769229557779109</v>
+        <v>1.759717114664168</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8347747172666007</v>
+        <v>0.8109936094792474</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.060786860878481</v>
+        <v>4.046518196206069</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.476138667760194</v>
+        <v>-4.499919775547546</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.765979149918993</v>
+        <v>1.756466706804052</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8344761705705648</v>
+        <v>0.8106950627832115</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.057476743679158</v>
+        <v>4.043208079006746</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.375315534069766</v>
+        <v>-4.399096641857119</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.810839298334556</v>
+        <v>1.801326855219615</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8469403860549186</v>
+        <v>0.8231592782675653</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.069486167909162</v>
+        <v>4.05521750323675</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.184534173317358</v>
+        <v>-4.208315281104712</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.887281096114062</v>
+        <v>1.877768652999121</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.037721746807326</v>
+        <v>1.013940639019973</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.18408423783915</v>
+        <v>4.169815573166738</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.077570815467936</v>
+        <v>-4.10135192325529</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.909903284991428</v>
+        <v>1.900390841876486</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.096186354767128</v>
+        <v>1.072405246979774</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.198999848352627</v>
+        <v>4.184731183680215</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.022240227566174</v>
+        <v>-4.046021335353528</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.967002456764191</v>
+        <v>1.95749001364925</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.15151694266889</v>
+        <v>1.127735834881536</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.267165137705742</v>
+        <v>4.252896473033331</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.010186100653211</v>
+        <v>-4.033967208440565</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.965510675430814</v>
+        <v>1.955998232315872</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.163571069581852</v>
+        <v>1.139789961794499</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.268084181754958</v>
+        <v>4.253815517082546</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.051341220221432</v>
+        <v>-4.075122328008786</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.950929257787661</v>
+        <v>1.94141681467272</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.122415950013631</v>
+        <v>1.098634842226278</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.245271740198161</v>
+        <v>4.23100307552575</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.983292657529902</v>
+        <v>-4.007073765317256</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.990999708742156</v>
+        <v>1.981487265627214</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.190464512705161</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.298951903690962</v>
+        <v>4.28468323901855</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.214893050699403</v>
+        <v>-4.238674158486757</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.918562221647949</v>
+        <v>1.909049778533008</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.190464512705161</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.319154573864556</v>
+        <v>4.304885909192144</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.264944596228622</v>
+        <v>-4.288725704015976</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.882147839503144</v>
+        <v>1.872635396388203</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.190464512705161</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.302760809931438</v>
+        <v>4.288492145259026</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.440051428805067</v>
+        <v>-4.46383253659242</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.772357020066033</v>
+        <v>1.762844576951091</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.190464512705161</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.263012723524905</v>
+        <v>4.248744058852493</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.243951275374544</v>
+        <v>-4.267732383161897</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.857819700435182</v>
+        <v>1.848307257320241</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.386564666135684</v>
+        <v>1.362783558348331</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.387695434580158</v>
+        <v>4.373426769907747</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.090925883261259</v>
+        <v>-4.114706991048613</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.0182008568534</v>
+        <v>2.008688413738459</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.539590058248968</v>
+        <v>1.515808950461615</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.578681669421033</v>
+        <v>4.564413004748621</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.11923319713453</v>
+        <v>-4.143014304921883</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.194344156212384</v>
+        <v>2.184831713097443</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.539590058248968</v>
+        <v>1.515808950461615</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.766147894329325</v>
+        <v>4.751879229656914</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.285826422248052</v>
+        <v>-4.309607530035406</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.097109817521059</v>
+        <v>2.087597374406117</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.372996833135446</v>
+        <v>1.349215725348093</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.635594910615294</v>
+        <v>4.621326245942883</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.262790628886486</v>
+        <v>-4.28657173667384</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.110000537527402</v>
+        <v>2.100488094412461</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.372996833135446</v>
+        <v>1.349215725348093</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.639271313277012</v>
+        <v>4.625002648604601</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.233544648430789</v>
+        <v>-4.257325756218143</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.119316984833176</v>
+        <v>2.109804541718235</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.372996833135446</v>
+        <v>1.349215725348093</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.636889368400508</v>
+        <v>4.622620703728096</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.34047019630864</v>
+        <v>-4.364251304095994</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.073840004839671</v>
+        <v>2.064327561724729</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.266071285257595</v>
+        <v>1.242290177470241</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.570027278831432</v>
+        <v>4.555758614159021</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.485488754815889</v>
+        <v>-4.509269862603243</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.017261383580006</v>
+        <v>2.007748940465064</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.121052726750346</v>
+        <v>1.097271618962993</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.484444945870317</v>
+        <v>4.470176281197905</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.603830520600606</v>
+        <v>-4.62761162838796</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.069855916523872</v>
+        <v>2.06034347340893</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.131738765313236</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.590787808265804</v>
+        <v>4.576519143593393</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.655240942921314</v>
+        <v>-4.679022050708668</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.047077444721528</v>
+        <v>2.037565001606586</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.131738765313236</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.588573505391744</v>
+        <v>4.574304840719331</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.734660394129066</v>
+        <v>-4.75844150191642</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.015212792312716</v>
+        <v>2.005700349197775</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.131738765313236</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.588476633466033</v>
+        <v>4.574207968793621</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.830123392046284</v>
+        <v>-4.853904499833638</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.977021486703872</v>
+        <v>1.96750904358893</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.131738765313236</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.588470527024076</v>
+        <v>4.574201862351663</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.765747481195569</v>
+        <v>-4.789528588982923</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.000868247606769</v>
+        <v>1.991355804491827</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.196114676163951</v>
+        <v>1.172333568376598</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.625192470097115</v>
+        <v>4.610923805424703</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.821116643327763</v>
+        <v>-4.844897751115116</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.984454400501618</v>
+        <v>1.974941957386676</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.196114676163951</v>
+        <v>1.172333568376598</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.630926287844842</v>
+        <v>4.61665762317243</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.86655442315859</v>
+        <v>-4.890335530945944</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.96581765191222</v>
+        <v>1.956305208797278</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.153269685485792</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.604757656780879</v>
+        <v>4.590488992108467</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.778347589011012</v>
+        <v>-4.802128696798365</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.02097477842157</v>
+        <v>2.011462335306628</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.153269685485792</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.624632049631197</v>
+        <v>4.610363384958785</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.672312593805702</v>
+        <v>-4.696093701593056</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.047089477028421</v>
+        <v>2.03757703391348</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.153269685485792</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.608332750155925</v>
+        <v>4.594064085483513</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.489100930672607</v>
+        <v>-4.512882038459961</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.122805091745705</v>
+        <v>2.113292648630763</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.153269685485792</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.61076369961997</v>
+        <v>4.596495034947559</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.417379483658756</v>
+        <v>-4.44116059144611</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.117284856399135</v>
+        <v>2.107772413284193</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.224991132499643</v>
+        <v>1.201210024712289</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.619587753676171</v>
+        <v>4.605319089003759</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.39500645805105</v>
+        <v>-4.418787565838404</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.073149812563389</v>
+        <v>2.063637369448447</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.236246883612544</v>
+        <v>1.212465775825191</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.573256950265083</v>
+        <v>4.558988285592672</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.428022753961795</v>
+        <v>-4.451803861749148</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.245141499084446</v>
+        <v>2.235629055969505</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.166809506945792</v>
+        <v>1.143028399158439</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.716792729150388</v>
+        <v>4.702524064477975</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.416495118312186</v>
+        <v>-4.44027622609954</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.241673779172539</v>
+        <v>2.232161336057597</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.225810165147155</v>
+        <v>1.202029057359802</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.744114349899454</v>
+        <v>4.729845685227042</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.513836619654555</v>
+        <v>-4.537617727441908</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.20640529115738</v>
+        <v>2.196892848042438</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.181389982981667</v>
+        <v>1.157608875194313</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.72113035312195</v>
+        <v>4.706861688449537</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.599692648994521</v>
+        <v>-4.623473756781875</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.173313961614231</v>
+        <v>2.16380151849929</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.139013913755532</v>
+        <v>1.115232805968178</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.696955793779107</v>
+        <v>4.682687129106695</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.608529446410641</v>
+        <v>-4.632310554197995</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.152198444468286</v>
+        <v>2.142686001353344</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.131571741114181</v>
+        <v>1.107790633326827</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.674909692014799</v>
+        <v>4.660641027342386</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.699912008976099</v>
+        <v>-4.723693116763453</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.125809930487152</v>
+        <v>2.11629748737221</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.095006856394836</v>
+        <v>1.071225748607483</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.663135272228241</v>
+        <v>4.648866607555829</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.688205290989093</v>
+        <v>-4.711986398776447</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.232620875506221</v>
+        <v>2.22310843239128</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.106713574381843</v>
+        <v>1.082932466594489</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.772287560844712</v>
+        <v>4.7580188961723</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.588541786905431</v>
+        <v>-4.612322894692785</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.275518615871091</v>
+        <v>2.266006172756149</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.169900657585529</v>
+        <v>1.146119549798176</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.813232149498329</v>
+        <v>4.798963484825917</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.598857885071783</v>
+        <v>-4.622638992859136</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.484297009882608</v>
+        <v>2.474784566767667</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.169900657585529</v>
+        <v>1.146119549798176</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.026136982776387</v>
+        <v>5.011868318103975</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.59876391705441</v>
+        <v>-4.622545024841764</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.483513264001647</v>
+        <v>2.474000820886705</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.170270518932847</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.025537566496867</v>
+        <v>5.011268901824455</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.605982741254254</v>
+        <v>-4.629763849041608</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.474857720266063</v>
+        <v>2.465345277151122</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.170270518932847</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.019769552441221</v>
+        <v>5.005500887768809</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.605034318136216</v>
+        <v>-4.62881542592357</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.475237089513278</v>
+        <v>2.465724646398337</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.170270518932847</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.019769552441221</v>
+        <v>5.005500887768809</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.76210277639184</v>
+        <v>-4.785883884179194</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.425137314192121</v>
+        <v>2.415624871077179</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.170270518932847</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.032497160422313</v>
+        <v>5.018228495749901</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.756110529603029</v>
+        <v>-4.779891637390382</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.429480211332033</v>
+        <v>2.419967768217091</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.170270518932847</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.034443158846701</v>
+        <v>5.020174494174289</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.667552568472261</v>
+        <v>-4.691333676259615</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.458557531802109</v>
+        <v>2.449045088687168</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.170270518932847</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.02809729486447</v>
+        <v>5.013828630192058</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.649793490969187</v>
+        <v>-4.673574598756541</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.464969840242334</v>
+        <v>2.455457397127393</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.170270518932847</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.027405972303465</v>
+        <v>5.013137307631053</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.550163339920119</v>
+        <v>-4.573944447707473</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.517604086570548</v>
+        <v>2.508091643455606</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.269900669981915</v>
+        <v>1.246119562194561</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.099966248841493</v>
+        <v>5.085697584169081</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.83450042032714</v>
+        <v>3.888304885083782</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.625013028203604</v>
+        <v>-4.573522176900042</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.676818476755881</v>
+        <v>2.697414817277306</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.280675322229741</v>
+        <v>1.248191531566661</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.295585305688915</v>
+        <v>5.276095031291067</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240915.xlsx
+++ b/tame_output/ON/bt/strategyON_20240915.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-618.9%</t>
+          <t>-621.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-106.5%</t>
+          <t>-107.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-58.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-99.2%</t>
+          <t>-96.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.5%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.2%</t>
+          <t>104.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.678296988460028</v>
+        <v>-4.654515880672675</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.804240456208853</v>
+        <v>1.813752899323794</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7094164514126027</v>
+        <v>0.733197559199956</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.101565546754173</v>
+        <v>4.115834211426586</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.581662076441388</v>
+        <v>-4.557880968654035</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.659078417140243</v>
+        <v>1.668590860255184</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8060513634312426</v>
+        <v>0.8298324712185959</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.975730490089292</v>
+        <v>3.989999154761704</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.712242810972231</v>
+        <v>-4.688461703184878</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.61034816740187</v>
+        <v>1.619860610516811</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6754706289004001</v>
+        <v>0.6992517366877534</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.900884093444751</v>
+        <v>3.915152758117163</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.547746476781269</v>
+        <v>-4.523965368993916</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.660573520154338</v>
+        <v>1.670085963269279</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.839966963091362</v>
+        <v>0.8637480708787153</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.98400871303541</v>
+        <v>3.998277377707822</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.470647875239396</v>
+        <v>-4.446866767452043</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.690600671207516</v>
+        <v>1.700113114322457</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.839966963091362</v>
+        <v>0.8637480708787153</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.98319642347184</v>
+        <v>3.997465088144252</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.481033070129286</v>
+        <v>-4.457251962341933</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.696315372376633</v>
+        <v>1.705827815491574</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8295817682014727</v>
+        <v>0.853362875988826</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.986834085662979</v>
+        <v>4.001102750335392</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.499621228851511</v>
+        <v>-4.475840121064158</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.759717114664168</v>
+        <v>1.769229557779109</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8109936094792474</v>
+        <v>0.8347747172666007</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.046518196206069</v>
+        <v>4.060786860878481</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.499919775547546</v>
+        <v>-4.476138667760194</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.756466706804052</v>
+        <v>1.765979149918993</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8106950627832115</v>
+        <v>0.8344761705705648</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.043208079006746</v>
+        <v>4.057476743679158</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.399096641857119</v>
+        <v>-4.375315534069766</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.801326855219615</v>
+        <v>1.810839298334556</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8231592782675653</v>
+        <v>0.8469403860549186</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.05521750323675</v>
+        <v>4.069486167909162</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.208315281104712</v>
+        <v>-4.184534173317358</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.877768652999121</v>
+        <v>1.887281096114062</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.013940639019973</v>
+        <v>1.037721746807326</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.169815573166738</v>
+        <v>4.18408423783915</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.10135192325529</v>
+        <v>-4.077570815467936</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.900390841876486</v>
+        <v>1.909903284991428</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.072405246979774</v>
+        <v>1.096186354767128</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.184731183680215</v>
+        <v>4.198999848352627</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.046021335353528</v>
+        <v>-4.022240227566174</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.95749001364925</v>
+        <v>1.967002456764191</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.127735834881536</v>
+        <v>1.15151694266889</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.252896473033331</v>
+        <v>4.267165137705742</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.033967208440565</v>
+        <v>-4.010186100653211</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.955998232315872</v>
+        <v>1.965510675430814</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.139789961794499</v>
+        <v>1.163571069581852</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.253815517082546</v>
+        <v>4.268084181754958</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.075122328008786</v>
+        <v>-4.051341220221432</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.94141681467272</v>
+        <v>1.950929257787661</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.098634842226278</v>
+        <v>1.122415950013631</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.23100307552575</v>
+        <v>4.245271740198161</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.007073765317256</v>
+        <v>-3.983292657529902</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.981487265627214</v>
+        <v>1.990999708742156</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.166683404917808</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.28468323901855</v>
+        <v>4.298951903690962</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.238674158486757</v>
+        <v>-4.214893050699403</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.909049778533008</v>
+        <v>1.918562221647949</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.166683404917808</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.304885909192144</v>
+        <v>4.319154573864556</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.288725704015976</v>
+        <v>-4.264944596228622</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.872635396388203</v>
+        <v>1.882147839503144</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.166683404917808</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.288492145259026</v>
+        <v>4.302760809931438</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.46383253659242</v>
+        <v>-4.440051428805067</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.762844576951091</v>
+        <v>1.772357020066033</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.166683404917808</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.248744058852493</v>
+        <v>4.263012723524905</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.267732383161897</v>
+        <v>-4.243951275374544</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.848307257320241</v>
+        <v>1.857819700435182</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.362783558348331</v>
+        <v>1.386564666135684</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.373426769907747</v>
+        <v>4.387695434580158</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.114706991048613</v>
+        <v>-4.090925883261259</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.008688413738459</v>
+        <v>2.0182008568534</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.515808950461615</v>
+        <v>1.539590058248968</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.564413004748621</v>
+        <v>4.578681669421033</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.143014304921883</v>
+        <v>-4.11923319713453</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.184831713097443</v>
+        <v>2.194344156212384</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.515808950461615</v>
+        <v>1.539590058248968</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.751879229656914</v>
+        <v>4.766147894329325</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.309607530035406</v>
+        <v>-4.285826422248052</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.087597374406117</v>
+        <v>2.097109817521059</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.349215725348093</v>
+        <v>1.372996833135446</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.621326245942883</v>
+        <v>4.635594910615294</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.28657173667384</v>
+        <v>-4.262790628886486</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.100488094412461</v>
+        <v>2.110000537527402</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.349215725348093</v>
+        <v>1.372996833135446</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.625002648604601</v>
+        <v>4.639271313277012</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.257325756218143</v>
+        <v>-4.233544648430789</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.109804541718235</v>
+        <v>2.119316984833176</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.349215725348093</v>
+        <v>1.372996833135446</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.622620703728096</v>
+        <v>4.636889368400508</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.364251304095994</v>
+        <v>-4.34047019630864</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.064327561724729</v>
+        <v>2.073840004839671</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.242290177470241</v>
+        <v>1.266071285257595</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.555758614159021</v>
+        <v>4.570027278831432</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.509269862603243</v>
+        <v>-4.485488754815889</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.007748940465064</v>
+        <v>2.017261383580006</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.097271618962993</v>
+        <v>1.121052726750346</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.470176281197905</v>
+        <v>4.484444945870317</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.62761162838796</v>
+        <v>-4.603830520600606</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.06034347340893</v>
+        <v>2.069855916523872</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.107957657525883</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.576519143593393</v>
+        <v>4.590787808265804</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.679022050708668</v>
+        <v>-4.655240942921314</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.037565001606586</v>
+        <v>2.047077444721528</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.107957657525883</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.574304840719331</v>
+        <v>4.588573505391744</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.75844150191642</v>
+        <v>-4.734660394129066</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.005700349197775</v>
+        <v>2.015212792312716</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.107957657525883</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.574207968793621</v>
+        <v>4.588476633466033</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.853904499833638</v>
+        <v>-4.830123392046284</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.96750904358893</v>
+        <v>1.977021486703872</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.107957657525883</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.574201862351663</v>
+        <v>4.588470527024076</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.789528588982923</v>
+        <v>-4.765747481195569</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.991355804491827</v>
+        <v>2.000868247606769</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.172333568376598</v>
+        <v>1.196114676163951</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.610923805424703</v>
+        <v>4.625192470097115</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.844897751115116</v>
+        <v>-4.821116643327763</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.974941957386676</v>
+        <v>1.984454400501618</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.172333568376598</v>
+        <v>1.196114676163951</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.61665762317243</v>
+        <v>4.630926287844842</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.890335530945944</v>
+        <v>-4.86655442315859</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.956305208797278</v>
+        <v>1.96581765191222</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.129488577698438</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.590488992108467</v>
+        <v>4.604757656780879</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.802128696798365</v>
+        <v>-4.778347589011012</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.011462335306628</v>
+        <v>2.02097477842157</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.129488577698438</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.610363384958785</v>
+        <v>4.624632049631197</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.696093701593056</v>
+        <v>-4.672312593805702</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.03757703391348</v>
+        <v>2.047089477028421</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.129488577698438</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.594064085483513</v>
+        <v>4.608332750155925</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.512882038459961</v>
+        <v>-4.489100930672607</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.113292648630763</v>
+        <v>2.122805091745705</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.129488577698438</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.596495034947559</v>
+        <v>4.61076369961997</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.44116059144611</v>
+        <v>-4.417379483658756</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.107772413284193</v>
+        <v>2.117284856399135</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.201210024712289</v>
+        <v>1.224991132499643</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.605319089003759</v>
+        <v>4.619587753676171</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.418787565838404</v>
+        <v>-4.39500645805105</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.063637369448447</v>
+        <v>2.073149812563389</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.212465775825191</v>
+        <v>1.236246883612544</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.558988285592672</v>
+        <v>4.573256950265083</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.451803861749148</v>
+        <v>-4.428022753961795</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.235629055969505</v>
+        <v>2.245141499084446</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.143028399158439</v>
+        <v>1.166809506945792</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.702524064477975</v>
+        <v>4.716792729150388</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.44027622609954</v>
+        <v>-4.416495118312186</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.232161336057597</v>
+        <v>2.241673779172539</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.202029057359802</v>
+        <v>1.225810165147155</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.729845685227042</v>
+        <v>4.744114349899454</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.537617727441908</v>
+        <v>-4.513836619654555</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.196892848042438</v>
+        <v>2.20640529115738</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.157608875194313</v>
+        <v>1.181389982981667</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.706861688449537</v>
+        <v>4.72113035312195</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.623473756781875</v>
+        <v>-4.599692648994521</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.16380151849929</v>
+        <v>2.173313961614231</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.115232805968178</v>
+        <v>1.139013913755532</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.682687129106695</v>
+        <v>4.696955793779107</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.632310554197995</v>
+        <v>-4.608529446410641</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.142686001353344</v>
+        <v>2.152198444468286</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.107790633326827</v>
+        <v>1.131571741114181</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.660641027342386</v>
+        <v>4.674909692014799</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.723693116763453</v>
+        <v>-4.699912008976099</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.11629748737221</v>
+        <v>2.125809930487152</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.071225748607483</v>
+        <v>1.095006856394836</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.648866607555829</v>
+        <v>4.663135272228241</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.711986398776447</v>
+        <v>-4.688205290989093</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.22310843239128</v>
+        <v>2.232620875506221</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.082932466594489</v>
+        <v>1.106713574381843</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.7580188961723</v>
+        <v>4.772287560844712</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.612322894692785</v>
+        <v>-4.588541786905431</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.266006172756149</v>
+        <v>2.275518615871091</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.146119549798176</v>
+        <v>1.169900657585529</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.798963484825917</v>
+        <v>4.813232149498329</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.622638992859136</v>
+        <v>-4.598857885071783</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.474784566767667</v>
+        <v>2.484297009882608</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.146119549798176</v>
+        <v>1.169900657585529</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.011868318103975</v>
+        <v>5.026136982776387</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.622545024841764</v>
+        <v>-4.59876391705441</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.474000820886705</v>
+        <v>2.483513264001647</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.011268901824455</v>
+        <v>5.025537566496867</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.629763849041608</v>
+        <v>-4.605982741254254</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.465345277151122</v>
+        <v>2.474857720266063</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.005500887768809</v>
+        <v>5.019769552441221</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.62881542592357</v>
+        <v>-4.605034318136216</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.465724646398337</v>
+        <v>2.475237089513278</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.005500887768809</v>
+        <v>5.019769552441221</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.785883884179194</v>
+        <v>-4.76210277639184</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.415624871077179</v>
+        <v>2.425137314192121</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.018228495749901</v>
+        <v>5.032497160422313</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.779891637390382</v>
+        <v>-4.756110529603029</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.419967768217091</v>
+        <v>2.429480211332033</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.020174494174289</v>
+        <v>5.034443158846701</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.691333676259615</v>
+        <v>-4.667552568472261</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.449045088687168</v>
+        <v>2.458557531802109</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.013828630192058</v>
+        <v>5.02809729486447</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.673574598756541</v>
+        <v>-4.649793490969187</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.455457397127393</v>
+        <v>2.464969840242334</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.146489411145494</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.013137307631053</v>
+        <v>5.027405972303465</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.573944447707473</v>
+        <v>-4.550163339920119</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.508091643455606</v>
+        <v>2.517604086570548</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.246119562194561</v>
+        <v>1.269900669981915</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.085697584169081</v>
+        <v>5.099966248841493</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.888304885083782</v>
+        <v>3.83450042032714</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.573522176900042</v>
+        <v>-4.59956284860913</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.697414817277306</v>
+        <v>2.68699854859367</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.248191531566661</v>
+        <v>1.280159503413659</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.276095031291067</v>
+        <v>5.295275814399266</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240915.xlsx
+++ b/tame_output/ON/bt/strategyON_20240915.xlsx
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.6%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>141.1%</t>
+          <t>159.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-621.5%</t>
+          <t>-615.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-107.5%</t>
+          <t>-105.1%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.1%</t>
+          <t>-58.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.4%</t>
+          <t>-329.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.0%</t>
+          <t>-95.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>104.5%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>24.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2087"/>
+  <dimension ref="A1:G2088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982222</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509531</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760807</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815451</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131244</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206786</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519904</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181163</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394723</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890606</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798421</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992185</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852418</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319537</v>
+        <v>3.819063300319539</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489377</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397786</v>
+        <v>3.836411672397788</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316241</v>
+        <v>3.833513460316243</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.82156211710596</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190318</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056961</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557288</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932762</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917044</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405954</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265639</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284874</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475133</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404847</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688255</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992653</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636279</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957618</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998749</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782704</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777667</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155026</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516197</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321627</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347696</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887741</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343059</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389342</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378385</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006969</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787382</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585931</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.64075008781466</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.66828900423709</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609749</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973152</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725194</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916195</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830321</v>
+        <v>3.667962306830323</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071544</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868138</v>
+        <v>3.75004401586814</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332683</v>
+        <v>3.783632867332685</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231799</v>
+        <v>3.798296784231801</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818514</v>
+        <v>3.785563924818516</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051781</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679618</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474154</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969536</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.654515880672675</v>
+        <v>-4.644578803287502</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.813752899323794</v>
+        <v>1.817727730277863</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.733197559199956</v>
+        <v>0.7431346365851291</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.115834211426586</v>
+        <v>4.121796457857689</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270047</v>
+        <v>3.825752932700472</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.557880968654035</v>
+        <v>-4.547943891268861</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.668590860255184</v>
+        <v>1.672565691209254</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8298324712185959</v>
+        <v>0.8397695486037691</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.989999154761704</v>
+        <v>3.995961401192808</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077632</v>
+        <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.688461703184878</v>
+        <v>-4.678524625799704</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.619860610516811</v>
+        <v>1.623835441470881</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6992517366877534</v>
+        <v>0.7091888140729266</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.915152758117163</v>
+        <v>3.921115004548267</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083345</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.523965368993916</v>
+        <v>-4.514028291608742</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.670085963269279</v>
+        <v>1.674060794223348</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8637480708787153</v>
+        <v>0.8736851482638884</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.998277377707822</v>
+        <v>4.004239624138926</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077621</v>
+        <v>3.821030660077623</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.446866767452043</v>
+        <v>-4.43692969006687</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.700113114322457</v>
+        <v>1.704087945276527</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8637480708787153</v>
+        <v>0.8736851482638884</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.997465088144252</v>
+        <v>4.003427334575356</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147903</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.457251962341933</v>
+        <v>-4.447314884956759</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.705827815491574</v>
+        <v>1.709802646445644</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.853362875988826</v>
+        <v>0.8632999533739991</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.001102750335392</v>
+        <v>4.007064996766495</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735273</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.475840121064158</v>
+        <v>-4.465903043678984</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.769229557779109</v>
+        <v>1.773204388733179</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8347747172666007</v>
+        <v>0.8447117946517737</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.060786860878481</v>
+        <v>4.066749107309585</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496549</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.476138667760194</v>
+        <v>-4.46620159037502</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.765979149918993</v>
+        <v>1.769953980873063</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8344761705705648</v>
+        <v>0.8444132479557378</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.057476743679158</v>
+        <v>4.063438990110262</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108849</v>
+        <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.375315534069766</v>
+        <v>-4.365378456684592</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.810839298334556</v>
+        <v>1.814814129288626</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8469403860549186</v>
+        <v>0.8568774634400916</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.069486167909162</v>
+        <v>4.075448414340266</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121458</v>
+        <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.184534173317358</v>
+        <v>-4.174597095932185</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.887281096114062</v>
+        <v>1.891255927068132</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.037721746807326</v>
+        <v>1.047658824192499</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.18408423783915</v>
+        <v>4.190046484270253</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906072</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.077570815467936</v>
+        <v>-4.067633738082764</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.909903284991428</v>
+        <v>1.913878115945497</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.096186354767128</v>
+        <v>1.1061234321523</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.198999848352627</v>
+        <v>4.20496209478373</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912977</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.022240227566174</v>
+        <v>-4.012303150181001</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.967002456764191</v>
+        <v>1.97097728771826</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.15151694266889</v>
+        <v>1.161454020054062</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.267165137705742</v>
+        <v>4.273127384136846</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539886</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.010186100653211</v>
+        <v>-4.000249023268038</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.965510675430814</v>
+        <v>1.969485506384883</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.163571069581852</v>
+        <v>1.173508146967025</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.268084181754958</v>
+        <v>4.274046428186062</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811001</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.051341220221432</v>
+        <v>-4.041404142836259</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.950929257787661</v>
+        <v>1.95490408874173</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.122415950013631</v>
+        <v>1.132353027398804</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.245271740198161</v>
+        <v>4.251233986629265</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382912</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.983292657529902</v>
+        <v>-3.973355580144729</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.990999708742156</v>
+        <v>1.994974539696225</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.190464512705161</v>
+        <v>1.200401590090334</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.298951903690962</v>
+        <v>4.304914150122065</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013419</v>
+        <v>3.645256780013421</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.214893050699403</v>
+        <v>-4.20495597331423</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.918562221647949</v>
+        <v>1.922537052602019</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.190464512705161</v>
+        <v>1.200401590090334</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.319154573864556</v>
+        <v>4.325116820295659</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498964</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.264944596228622</v>
+        <v>-4.255007518843449</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.882147839503144</v>
+        <v>1.886122670457213</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.190464512705161</v>
+        <v>1.200401590090334</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.302760809931438</v>
+        <v>4.308723056362542</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800093</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.440051428805067</v>
+        <v>-4.430114351419894</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.772357020066033</v>
+        <v>1.776331851020102</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.190464512705161</v>
+        <v>1.200401590090334</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.263012723524905</v>
+        <v>4.268974969956008</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660846</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.243951275374544</v>
+        <v>-4.234014197989371</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.857819700435182</v>
+        <v>1.861794531389251</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.386564666135684</v>
+        <v>1.396501743520857</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.387695434580158</v>
+        <v>4.393657681011262</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395082</v>
+        <v>3.730570473395084</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.090925883261259</v>
+        <v>-4.080988805876086</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.0182008568534</v>
+        <v>2.022175687807469</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.539590058248968</v>
+        <v>1.549527135634141</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.578681669421033</v>
+        <v>4.584643915852137</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791144</v>
+        <v>3.741278332791146</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.11923319713453</v>
+        <v>-4.109296119749357</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.194344156212384</v>
+        <v>2.198318987166454</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.539590058248968</v>
+        <v>1.549527135634141</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.766147894329325</v>
+        <v>4.77211014076043</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69911561562043</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.285826422248052</v>
+        <v>-4.275889344862879</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.097109817521059</v>
+        <v>2.101084648475128</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.372996833135446</v>
+        <v>1.382933910520619</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.635594910615294</v>
+        <v>4.641557157046399</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285643</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.262790628886486</v>
+        <v>-4.252853551501313</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.110000537527402</v>
+        <v>2.113975368481472</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.372996833135446</v>
+        <v>1.382933910520619</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.639271313277012</v>
+        <v>4.645233559708116</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399464</v>
+        <v>3.740581401399466</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.233544648430789</v>
+        <v>-4.223607571045616</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.119316984833176</v>
+        <v>2.123291815787246</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.372996833135446</v>
+        <v>1.382933910520619</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.636889368400508</v>
+        <v>4.642851614831612</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256366</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.34047019630864</v>
+        <v>-4.330533118923467</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.073840004839671</v>
+        <v>2.07781483579374</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.266071285257595</v>
+        <v>1.276008362642767</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.570027278831432</v>
+        <v>4.575989525262536</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700995</v>
+        <v>3.689942600700997</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.485488754815889</v>
+        <v>-4.475551677430716</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.017261383580006</v>
+        <v>2.021236214534075</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.121052726750346</v>
+        <v>1.130989804135519</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.484444945870317</v>
+        <v>4.490407192301421</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687006</v>
+        <v>3.711852429687008</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.603830520600606</v>
+        <v>-4.593893443215434</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.069855916523872</v>
+        <v>2.073830747477941</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.131738765313236</v>
+        <v>1.141675842698409</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.590787808265804</v>
+        <v>4.596750054696908</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790796</v>
+        <v>3.714879051790798</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.655240942921314</v>
+        <v>-4.645303865536142</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.047077444721528</v>
+        <v>2.051052275675597</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.131738765313236</v>
+        <v>1.141675842698409</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.588573505391744</v>
+        <v>4.594535751822847</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437324</v>
+        <v>3.704757949437326</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.734660394129066</v>
+        <v>-4.724723316743893</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.015212792312716</v>
+        <v>2.019187623266785</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.131738765313236</v>
+        <v>1.141675842698409</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.588476633466033</v>
+        <v>4.594438879897137</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298391</v>
+        <v>3.736804952298392</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.830123392046284</v>
+        <v>-4.820186314661111</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.977021486703872</v>
+        <v>1.980996317657941</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.131738765313236</v>
+        <v>1.141675842698409</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.588470527024076</v>
+        <v>4.594432773455179</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217993</v>
+        <v>3.715372960217994</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.765747481195569</v>
+        <v>-4.755810403810396</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.000868247606769</v>
+        <v>2.004843078560838</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.196114676163951</v>
+        <v>1.206051753549124</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.625192470097115</v>
+        <v>4.631154716528219</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353528</v>
+        <v>3.73608941335353</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.821116643327763</v>
+        <v>-4.81117956594259</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.984454400501618</v>
+        <v>1.988429231455687</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.196114676163951</v>
+        <v>1.206051753549124</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.630926287844842</v>
+        <v>4.636888534275946</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113271</v>
+        <v>3.736822870113273</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.86655442315859</v>
+        <v>-4.856617345773417</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.96581765191222</v>
+        <v>1.969792482866289</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.153269685485792</v>
+        <v>1.163206762870965</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.604757656780879</v>
+        <v>4.610719903211982</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79027250011368</v>
+        <v>3.790272500113682</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.778347589011012</v>
+        <v>-4.768410511625839</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.02097477842157</v>
+        <v>2.024949609375638</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.153269685485792</v>
+        <v>1.163206762870965</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.624632049631197</v>
+        <v>4.630594296062301</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016434</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.672312593805702</v>
+        <v>-4.662375516420529</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.047089477028421</v>
+        <v>2.05106430798249</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.153269685485792</v>
+        <v>1.163206762870965</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.608332750155925</v>
+        <v>4.614294996587029</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307665</v>
+        <v>3.794705093307667</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.489100930672607</v>
+        <v>-4.479163853287434</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.122805091745705</v>
+        <v>2.126779922699773</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.153269685485792</v>
+        <v>1.163206762870965</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.61076369961997</v>
+        <v>4.616725946051075</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863546</v>
+        <v>3.776846557863548</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.417379483658756</v>
+        <v>-4.407442406273583</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.117284856399135</v>
+        <v>2.121259687353204</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.224991132499643</v>
+        <v>1.234928209884815</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.619587753676171</v>
+        <v>4.625550000107275</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394107</v>
+        <v>3.723789705394108</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.39500645805105</v>
+        <v>-4.385069380665877</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.073149812563389</v>
+        <v>2.077124643517458</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.236246883612544</v>
+        <v>1.246183960997717</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.573256950265083</v>
+        <v>4.579219196696187</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456723</v>
+        <v>3.715607446456724</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.428022753961795</v>
+        <v>-4.418085676576622</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.245141499084446</v>
+        <v>2.249116330038516</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.166809506945792</v>
+        <v>1.176746584330965</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.716792729150388</v>
+        <v>4.722754975581491</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883669</v>
+        <v>3.713762536883671</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.416495118312186</v>
+        <v>-4.406558040927013</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.241673779172539</v>
+        <v>2.245648610126608</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.225810165147155</v>
+        <v>1.235747242532328</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.744114349899454</v>
+        <v>4.750076596330558</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236289</v>
+        <v>3.71715069923629</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.513836619654555</v>
+        <v>-4.503899542269382</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.20640529115738</v>
+        <v>2.210380122111449</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.181389982981667</v>
+        <v>1.191327060366839</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.72113035312195</v>
+        <v>4.727092599553053</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427676</v>
+        <v>3.705201079427678</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.599692648994521</v>
+        <v>-4.589755571609349</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.173313961614231</v>
+        <v>2.177288792568301</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.139013913755532</v>
+        <v>1.148950991140704</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.696955793779107</v>
+        <v>4.702918040210211</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610375</v>
+        <v>3.691835499610377</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.608529446410641</v>
+        <v>-4.598592369025468</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.152198444468286</v>
+        <v>2.156173275422354</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.131571741114181</v>
+        <v>1.141508818499354</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.674909692014799</v>
+        <v>4.680871938445902</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667447</v>
+        <v>3.715544411667449</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.699912008976099</v>
+        <v>-4.689974931590926</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.125809930487152</v>
+        <v>2.12978476144122</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.095006856394836</v>
+        <v>1.104943933780009</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.663135272228241</v>
+        <v>4.669097518659345</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889183</v>
+        <v>3.673978374889185</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.688205290989093</v>
+        <v>-4.67826821360392</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.232620875506221</v>
+        <v>2.23659570646029</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.106713574381843</v>
+        <v>1.116650651767015</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.772287560844712</v>
+        <v>4.778249807275816</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409559</v>
+        <v>3.68247609940956</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.588541786905431</v>
+        <v>-4.578604709520258</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.275518615871091</v>
+        <v>2.27949344682516</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.169900657585529</v>
+        <v>1.179837734970702</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.813232149498329</v>
+        <v>4.819194395929433</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452566</v>
+        <v>3.672895177452567</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.598857885071783</v>
+        <v>-4.58892080768661</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.484297009882608</v>
+        <v>2.488271840836677</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.169900657585529</v>
+        <v>1.179837734970702</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.026136982776387</v>
+        <v>5.032099229207491</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762279</v>
+        <v>3.623960959762281</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.59876391705441</v>
+        <v>-4.588826839669237</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.483513264001647</v>
+        <v>2.487488094955716</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.170270518932847</v>
+        <v>1.18020759631802</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.025537566496867</v>
+        <v>5.031499812927971</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.63321346798801</v>
+        <v>3.633213467988012</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.605982741254254</v>
+        <v>-4.596045663869082</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.474857720266063</v>
+        <v>2.478832551220132</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.170270518932847</v>
+        <v>1.18020759631802</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.019769552441221</v>
+        <v>5.025731798872325</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740916</v>
+        <v>3.647907242740918</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.605034318136216</v>
+        <v>-4.595097240751043</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.475237089513278</v>
+        <v>2.479211920467348</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.170270518932847</v>
+        <v>1.18020759631802</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.019769552441221</v>
+        <v>5.025731798872325</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.88106536666362</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.76210277639184</v>
+        <v>-4.752165699006667</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.425137314192121</v>
+        <v>2.42911214514619</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.170270518932847</v>
+        <v>1.18020759631802</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.032497160422313</v>
+        <v>5.038459406853417</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424764</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.756110529603029</v>
+        <v>-4.746173452217856</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.429480211332033</v>
+        <v>2.433455042286102</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.170270518932847</v>
+        <v>1.18020759631802</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.034443158846701</v>
+        <v>5.040405405277805</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149212</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.667552568472261</v>
+        <v>-4.657615491087088</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.458557531802109</v>
+        <v>2.462532362756178</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.170270518932847</v>
+        <v>1.18020759631802</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.02809729486447</v>
+        <v>5.034059541295574</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383085</v>
+        <v>3.735300721383087</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.649793490969187</v>
+        <v>-4.639856413584014</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.464969840242334</v>
+        <v>2.468944671196403</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.170270518932847</v>
+        <v>1.18020759631802</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.027405972303465</v>
+        <v>5.033368218734569</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720992</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.550163339920119</v>
+        <v>-4.540226262534946</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.517604086570548</v>
+        <v>2.521578917524617</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.269900669981915</v>
+        <v>1.279837747367087</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.099966248841493</v>
+        <v>5.105928495272597</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,45 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.83450042032714</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.59956284860913</v>
+        <v>-4.539803991727515</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.68699854859367</v>
+        <v>2.710902091346316</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.280159503413659</v>
+        <v>1.281909716739187</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.295275814399266</v>
+        <v>5.296325942394583</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="2" t="n">
+        <v>45550</v>
+      </c>
+      <c r="B2088" t="n">
+        <v>3.834670950636493</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>4.715372993705039</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>-4.539803991727515</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>2.710902091346316</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>1.281909716739187</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>4.708436790691407</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240915.xlsx
+++ b/tame_output/ON/bt/strategyON_20240915.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.6%</t>
+          <t>-621.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-105.1%</t>
+          <t>-107.5%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.0%</t>
+          <t>-58.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.3%</t>
+          <t>-329.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-95.8%</t>
+          <t>-96.0%</t>
         </is>
       </c>
     </row>
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.644578803287502</v>
+        <v>-4.654515880672675</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.817727730277863</v>
+        <v>1.813752899323794</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7431346365851291</v>
+        <v>0.733197559199956</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.121796457857689</v>
+        <v>4.115834211426586</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.547943891268861</v>
+        <v>-4.557880968654035</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.672565691209254</v>
+        <v>1.668590860255184</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8397695486037691</v>
+        <v>0.8298324712185959</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.995961401192808</v>
+        <v>3.989999154761704</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.678524625799704</v>
+        <v>-4.688461703184878</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.623835441470881</v>
+        <v>1.619860610516811</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7091888140729266</v>
+        <v>0.6992517366877534</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.921115004548267</v>
+        <v>3.915152758117163</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.514028291608742</v>
+        <v>-4.523965368993916</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.674060794223348</v>
+        <v>1.670085963269279</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8736851482638884</v>
+        <v>0.8637480708787153</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.004239624138926</v>
+        <v>3.998277377707822</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.43692969006687</v>
+        <v>-4.446866767452043</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.704087945276527</v>
+        <v>1.700113114322457</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8736851482638884</v>
+        <v>0.8637480708787153</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.003427334575356</v>
+        <v>3.997465088144252</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.447314884956759</v>
+        <v>-4.457251962341933</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.709802646445644</v>
+        <v>1.705827815491574</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8632999533739991</v>
+        <v>0.853362875988826</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.007064996766495</v>
+        <v>4.001102750335392</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.465903043678984</v>
+        <v>-4.475840121064158</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.773204388733179</v>
+        <v>1.769229557779109</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8447117946517737</v>
+        <v>0.8347747172666007</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.066749107309585</v>
+        <v>4.060786860878481</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.46620159037502</v>
+        <v>-4.476138667760194</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.769953980873063</v>
+        <v>1.765979149918993</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8444132479557378</v>
+        <v>0.8344761705705648</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.063438990110262</v>
+        <v>4.057476743679158</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.365378456684592</v>
+        <v>-4.375315534069766</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.814814129288626</v>
+        <v>1.810839298334556</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8568774634400916</v>
+        <v>0.8469403860549186</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.075448414340266</v>
+        <v>4.069486167909162</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.174597095932185</v>
+        <v>-4.184534173317358</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.891255927068132</v>
+        <v>1.887281096114062</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.047658824192499</v>
+        <v>1.037721746807326</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.190046484270253</v>
+        <v>4.18408423783915</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.067633738082764</v>
+        <v>-4.077570815467936</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.913878115945497</v>
+        <v>1.909903284991428</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.1061234321523</v>
+        <v>1.096186354767128</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.20496209478373</v>
+        <v>4.198999848352627</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.012303150181001</v>
+        <v>-4.022240227566174</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.97097728771826</v>
+        <v>1.967002456764191</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.161454020054062</v>
+        <v>1.15151694266889</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.273127384136846</v>
+        <v>4.267165137705742</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.000249023268038</v>
+        <v>-4.010186100653211</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.969485506384883</v>
+        <v>1.965510675430814</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.173508146967025</v>
+        <v>1.163571069581852</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.274046428186062</v>
+        <v>4.268084181754958</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.041404142836259</v>
+        <v>-4.051341220221432</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.95490408874173</v>
+        <v>1.950929257787661</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.132353027398804</v>
+        <v>1.122415950013631</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.251233986629265</v>
+        <v>4.245271740198161</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.973355580144729</v>
+        <v>-3.983292657529902</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.994974539696225</v>
+        <v>1.990999708742156</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.200401590090334</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.304914150122065</v>
+        <v>4.298951903690962</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.20495597331423</v>
+        <v>-4.214893050699403</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.922537052602019</v>
+        <v>1.918562221647949</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.200401590090334</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.325116820295659</v>
+        <v>4.319154573864556</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.255007518843449</v>
+        <v>-4.264944596228622</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.886122670457213</v>
+        <v>1.882147839503144</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.200401590090334</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.308723056362542</v>
+        <v>4.302760809931438</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.430114351419894</v>
+        <v>-4.440051428805067</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.776331851020102</v>
+        <v>1.772357020066033</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.200401590090334</v>
+        <v>1.190464512705161</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.268974969956008</v>
+        <v>4.263012723524905</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.234014197989371</v>
+        <v>-4.243951275374544</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.861794531389251</v>
+        <v>1.857819700435182</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.396501743520857</v>
+        <v>1.386564666135684</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.393657681011262</v>
+        <v>4.387695434580158</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.080988805876086</v>
+        <v>-4.090925883261259</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.022175687807469</v>
+        <v>2.0182008568534</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.549527135634141</v>
+        <v>1.539590058248968</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.584643915852137</v>
+        <v>4.578681669421033</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.109296119749357</v>
+        <v>-4.11923319713453</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.198318987166454</v>
+        <v>2.194344156212384</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.549527135634141</v>
+        <v>1.539590058248968</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.77211014076043</v>
+        <v>4.766147894329325</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.275889344862879</v>
+        <v>-4.285826422248052</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.101084648475128</v>
+        <v>2.097109817521059</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.382933910520619</v>
+        <v>1.372996833135446</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.641557157046399</v>
+        <v>4.635594910615294</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.252853551501313</v>
+        <v>-4.262790628886486</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.113975368481472</v>
+        <v>2.110000537527402</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.382933910520619</v>
+        <v>1.372996833135446</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.645233559708116</v>
+        <v>4.639271313277012</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.223607571045616</v>
+        <v>-4.233544648430789</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.123291815787246</v>
+        <v>2.119316984833176</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.382933910520619</v>
+        <v>1.372996833135446</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.642851614831612</v>
+        <v>4.636889368400508</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.330533118923467</v>
+        <v>-4.34047019630864</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.07781483579374</v>
+        <v>2.073840004839671</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.276008362642767</v>
+        <v>1.266071285257595</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.575989525262536</v>
+        <v>4.570027278831432</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.475551677430716</v>
+        <v>-4.485488754815889</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.021236214534075</v>
+        <v>2.017261383580006</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.130989804135519</v>
+        <v>1.121052726750346</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.490407192301421</v>
+        <v>4.484444945870317</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.593893443215434</v>
+        <v>-4.603830520600606</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.073830747477941</v>
+        <v>2.069855916523872</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.141675842698409</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.596750054696908</v>
+        <v>4.590787808265804</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.645303865536142</v>
+        <v>-4.655240942921314</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.051052275675597</v>
+        <v>2.047077444721528</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.141675842698409</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.594535751822847</v>
+        <v>4.588573505391744</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.724723316743893</v>
+        <v>-4.734660394129066</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.019187623266785</v>
+        <v>2.015212792312716</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.141675842698409</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.594438879897137</v>
+        <v>4.588476633466033</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.820186314661111</v>
+        <v>-4.830123392046284</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.980996317657941</v>
+        <v>1.977021486703872</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.141675842698409</v>
+        <v>1.131738765313236</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.594432773455179</v>
+        <v>4.588470527024076</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.755810403810396</v>
+        <v>-4.765747481195569</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.004843078560838</v>
+        <v>2.000868247606769</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.206051753549124</v>
+        <v>1.196114676163951</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.631154716528219</v>
+        <v>4.625192470097115</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.81117956594259</v>
+        <v>-4.821116643327763</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.988429231455687</v>
+        <v>1.984454400501618</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.206051753549124</v>
+        <v>1.196114676163951</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.636888534275946</v>
+        <v>4.630926287844842</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.856617345773417</v>
+        <v>-4.86655442315859</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.969792482866289</v>
+        <v>1.96581765191222</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.163206762870965</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.610719903211982</v>
+        <v>4.604757656780879</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.768410511625839</v>
+        <v>-4.778347589011012</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.024949609375638</v>
+        <v>2.02097477842157</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.163206762870965</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.630594296062301</v>
+        <v>4.624632049631197</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.662375516420529</v>
+        <v>-4.672312593805702</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.05106430798249</v>
+        <v>2.047089477028421</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.163206762870965</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.614294996587029</v>
+        <v>4.608332750155925</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.479163853287434</v>
+        <v>-4.489100930672607</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.126779922699773</v>
+        <v>2.122805091745705</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.163206762870965</v>
+        <v>1.153269685485792</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.616725946051075</v>
+        <v>4.61076369961997</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.407442406273583</v>
+        <v>-4.417379483658756</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.121259687353204</v>
+        <v>2.117284856399135</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.234928209884815</v>
+        <v>1.224991132499643</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.625550000107275</v>
+        <v>4.619587753676171</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.385069380665877</v>
+        <v>-4.39500645805105</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.077124643517458</v>
+        <v>2.073149812563389</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.246183960997717</v>
+        <v>1.236246883612544</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.579219196696187</v>
+        <v>4.573256950265083</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.418085676576622</v>
+        <v>-4.428022753961795</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.249116330038516</v>
+        <v>2.245141499084446</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.176746584330965</v>
+        <v>1.166809506945792</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.722754975581491</v>
+        <v>4.716792729150388</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.406558040927013</v>
+        <v>-4.416495118312186</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.245648610126608</v>
+        <v>2.241673779172539</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.235747242532328</v>
+        <v>1.225810165147155</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.750076596330558</v>
+        <v>4.744114349899454</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.503899542269382</v>
+        <v>-4.513836619654555</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.210380122111449</v>
+        <v>2.20640529115738</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.191327060366839</v>
+        <v>1.181389982981667</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.727092599553053</v>
+        <v>4.72113035312195</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.589755571609349</v>
+        <v>-4.599692648994521</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.177288792568301</v>
+        <v>2.173313961614231</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.148950991140704</v>
+        <v>1.139013913755532</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.702918040210211</v>
+        <v>4.696955793779107</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.598592369025468</v>
+        <v>-4.608529446410641</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.156173275422354</v>
+        <v>2.152198444468286</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.141508818499354</v>
+        <v>1.131571741114181</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.680871938445902</v>
+        <v>4.674909692014799</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.689974931590926</v>
+        <v>-4.699912008976099</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.12978476144122</v>
+        <v>2.125809930487152</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.104943933780009</v>
+        <v>1.095006856394836</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.669097518659345</v>
+        <v>4.663135272228241</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.67826821360392</v>
+        <v>-4.688205290989093</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.23659570646029</v>
+        <v>2.232620875506221</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.116650651767015</v>
+        <v>1.106713574381843</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.778249807275816</v>
+        <v>4.772287560844712</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.578604709520258</v>
+        <v>-4.588541786905431</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.27949344682516</v>
+        <v>2.275518615871091</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.179837734970702</v>
+        <v>1.169900657585529</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.819194395929433</v>
+        <v>4.813232149498329</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.58892080768661</v>
+        <v>-4.598857885071783</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.488271840836677</v>
+        <v>2.484297009882608</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.179837734970702</v>
+        <v>1.169900657585529</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.032099229207491</v>
+        <v>5.026136982776387</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.588826839669237</v>
+        <v>-4.59876391705441</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.487488094955716</v>
+        <v>2.483513264001647</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.18020759631802</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.031499812927971</v>
+        <v>5.025537566496867</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.596045663869082</v>
+        <v>-4.605982741254254</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.478832551220132</v>
+        <v>2.474857720266063</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.18020759631802</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.025731798872325</v>
+        <v>5.019769552441221</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.595097240751043</v>
+        <v>-4.605034318136216</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.479211920467348</v>
+        <v>2.475237089513278</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.18020759631802</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.025731798872325</v>
+        <v>5.019769552441221</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.752165699006667</v>
+        <v>-4.76210277639184</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.42911214514619</v>
+        <v>2.425137314192121</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.18020759631802</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.038459406853417</v>
+        <v>5.032497160422313</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.746173452217856</v>
+        <v>-4.756110529603029</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.433455042286102</v>
+        <v>2.429480211332033</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.18020759631802</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.040405405277805</v>
+        <v>5.034443158846701</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.657615491087088</v>
+        <v>-4.667552568472261</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.462532362756178</v>
+        <v>2.458557531802109</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.18020759631802</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.034059541295574</v>
+        <v>5.02809729486447</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.639856413584014</v>
+        <v>-4.649793490969187</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.468944671196403</v>
+        <v>2.464969840242334</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.18020759631802</v>
+        <v>1.170270518932847</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.033368218734569</v>
+        <v>5.027405972303465</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.540226262534946</v>
+        <v>-4.550163339920119</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.521578917524617</v>
+        <v>2.517604086570548</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.279837747367087</v>
+        <v>1.269900669981915</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.105928495272597</v>
+        <v>5.099966248841493</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.539803991727515</v>
+        <v>-4.59956284860913</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.710902091346316</v>
+        <v>2.68699854859367</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.281909716739187</v>
+        <v>1.280159503413659</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.296325942394583</v>
+        <v>5.295275814399266</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,13 +49575,13 @@
         <v>4.715372993705039</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.539803991727515</v>
+        <v>-4.59956284860913</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.710902091346316</v>
+        <v>2.68699854859367</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.281909716739187</v>
+        <v>1.280159503413659</v>
       </c>
       <c r="G2088" t="n">
         <v>4.708436790691407</v>

--- a/tame_output/ON/bt/strategyON_20240915.xlsx
+++ b/tame_output/ON/bt/strategyON_20240915.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>65.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>159.9%</t>
+          <t>161.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-621.5%</t>
+          <t>-638.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-107.5%</t>
+          <t>-114.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.1%</t>
+          <t>-58.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.4%</t>
+          <t>-328.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.0%</t>
+          <t>-95.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1476,27 +1476,27 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
     </row>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.603674783618876</v>
+        <v>-3.812060853445169</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.059935978650886</v>
+        <v>0.976581550720369</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6244804616619062</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.648767028452422</v>
+        <v>-3.857153098278715</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.042582472479381</v>
+        <v>0.9592280445488637</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5625844184925164</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.469391607213654</v>
+        <v>-3.677777677039948</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.108119616281303</v>
+        <v>1.024765188350785</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7193611766632351</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.514405820734261</v>
+        <v>-3.722791890560554</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.07092138620465</v>
+        <v>0.9875669582741324</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6890122813486305</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.781410331006696</v>
+        <v>-3.989796400832989</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9698111444346214</v>
+        <v>0.886456716504104</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4946492433056819</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.882608112443869</v>
+        <v>-4.090994182270162</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9285359537562536</v>
+        <v>0.8451815258257365</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4262404297603627</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.876097145829556</v>
+        <v>-4.084483215655849</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9287403019562954</v>
+        <v>0.8453858740257783</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4262404297603627</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.857059018122259</v>
+        <v>-4.065445087948552</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9328802722474592</v>
+        <v>0.849525844316942</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3680568184291682</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.909574820397079</v>
+        <v>-4.117960890223372</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.031168352971722</v>
+        <v>0.9478139250412041</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3680568184291682</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.912983131831659</v>
+        <v>-4.121369201657952</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.030638357384023</v>
+        <v>0.9472839294535058</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4005733874385456</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.893626995937812</v>
+        <v>-4.102013065764105</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.044389342138488</v>
+        <v>0.9610349142079708</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4005733874385456</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.745884025702809</v>
+        <v>-3.954270095529103</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.001436751509688</v>
+        <v>0.9180823235791711</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5683807446734288</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.829705246977507</v>
+        <v>-4.038091316803801</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.97070188453129</v>
+        <v>0.8873474566007729</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5683807446734288</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.823552540924723</v>
+        <v>-4.031938610751016</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9738253153440621</v>
+        <v>0.890470887413545</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5745334507262131</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.840361839075225</v>
+        <v>-4.048747908901518</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9661820728239718</v>
+        <v>0.8828276448934544</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5577241525757115</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.778063840299103</v>
+        <v>-3.986449910125396</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.057436826131241</v>
+        <v>0.9740823982007241</v>
       </c>
       <c r="F1970" t="n">
         <v>0.6030184168501536</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.576273642633945</v>
+        <v>-3.784659712460238</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9404449069114318</v>
+        <v>0.8570904789809144</v>
       </c>
       <c r="F1971" t="n">
         <v>0.801036609019308</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.627160355320139</v>
+        <v>-3.835546425146433</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.990380454159129</v>
+        <v>0.9070260262286116</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7501498963331135</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319539</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.540549612670332</v>
+        <v>-3.748935682496626</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.039652487335096</v>
+        <v>0.9562980594045782</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8287756275382717</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.600758910675617</v>
+        <v>-3.80914498050191</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.014104748957654</v>
+        <v>0.9307503210271362</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7685663295329872</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397788</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.551572261991265</v>
+        <v>-3.759958331817559</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.032271026471323</v>
+        <v>0.9489165985408052</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7685663295329872</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316243</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.507199130352697</v>
+        <v>-3.71558520017899</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.049883146562186</v>
+        <v>0.9665287186316689</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8129394611715558</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.529679481211581</v>
+        <v>-3.738065551037875</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.035284800357223</v>
+        <v>0.9519303724267054</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8129394611715558</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.482023750650526</v>
+        <v>-3.69040982047682</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.06072884960945</v>
+        <v>0.9773744216789322</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8605951917326115</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.381505592151771</v>
+        <v>-3.589891661978065</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.105828486383676</v>
+        <v>1.022474058453159</v>
       </c>
       <c r="F1979" t="n">
         <v>0.961113350231366</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.365600262719418</v>
+        <v>-3.573986332545712</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.09894529063249</v>
+        <v>1.015590862701972</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8820006895221271</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.32076186111102</v>
+        <v>-3.529147930937314</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.120978353886477</v>
+        <v>1.03762392595596</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8865441224669965</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.340260317353029</v>
+        <v>-3.548646387179323</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.117339911020752</v>
+        <v>1.033985483090235</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8384594811870922</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.296057480267128</v>
+        <v>-3.504443550093422</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.14090064838295</v>
+        <v>1.057546220452432</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8826623182729927</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.303617146104175</v>
+        <v>-3.512003215930469</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.136286782517378</v>
+        <v>1.052932354586861</v>
       </c>
       <c r="F1984" t="n">
         <v>0.937465722282812</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.145325728564903</v>
+        <v>-3.353711798391197</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.250851114716127</v>
+        <v>1.167496686785609</v>
       </c>
       <c r="F1985" t="n">
         <v>0.937465722282812</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.937683724930427</v>
+        <v>-3.146069794756721</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.332348620764171</v>
+        <v>1.248994192833653</v>
       </c>
       <c r="F1986" t="n">
         <v>1.145107725917288</v>
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.886651632207899</v>
+        <v>-3.140705407931997</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.347709686091452</v>
+        <v>1.246088175801812</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.196139818639816</v>
+        <v>1.150472112742012</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.220410654472249</v>
+        <v>3.193010030933567</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.821427451080693</v>
+        <v>-3.075481226804792</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.390986762635039</v>
+        <v>1.289365252345399</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.261363999767022</v>
+        <v>1.215696293869218</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.276732567241277</v>
+        <v>3.249331943702595</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.784000431009559</v>
+        <v>-3.038054206733658</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.401918542962773</v>
+        <v>1.300297032673133</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.266615537796203</v>
+        <v>1.220947831898399</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.275844462358067</v>
+        <v>3.248443838819384</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.804112087044267</v>
+        <v>-3.058165862768366</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.39513067288013</v>
+        <v>1.29350916259049</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.277642882793623</v>
+        <v>1.231975176895818</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.283717661687759</v>
+        <v>3.256317038149076</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.775698823944384</v>
+        <v>-3.029752599668483</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.567053749141294</v>
+        <v>1.465432238851655</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.218667320047194</v>
+        <v>1.17299961414939</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.408890095061112</v>
+        <v>3.38148947152243</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.700916562919371</v>
+        <v>-2.95497033864347</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.717079562769116</v>
+        <v>1.615458052479477</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.293449581072206</v>
+        <v>1.247781875174402</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.573872360893937</v>
+        <v>3.546471737355255</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.674832478655563</v>
+        <v>-2.928886254379662</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.719221172488498</v>
+        <v>1.617599662198859</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.293449581072206</v>
+        <v>1.247781875174402</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.565580336907796</v>
+        <v>3.538179713369114</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.586954565546443</v>
+        <v>-2.841008341270542</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.752565533315926</v>
+        <v>1.650944023026287</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.409375223495557</v>
+        <v>1.363707517597753</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.633328917945586</v>
+        <v>3.605928294406903</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.578062104153159</v>
+        <v>-2.832115879877258</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.773676923600031</v>
+        <v>1.672055413310391</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.409375223495557</v>
+        <v>1.363707517597753</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.650883323672377</v>
+        <v>3.623482700133695</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.746538221123037</v>
+        <v>-3.000591996847136</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.698141524216664</v>
+        <v>1.596520013927024</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.381427387778977</v>
+        <v>1.335759681881173</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.625969669647013</v>
+        <v>3.59856904610833</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.300282028493597</v>
+        <v>-2.554335804217696</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.857913698456302</v>
+        <v>1.756292188166662</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.286708718109344</v>
+        <v>1.24104101221154</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.550408165033095</v>
+        <v>3.523007541494413</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.277560924810444</v>
+        <v>-2.567069645917584</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.857666162426467</v>
+        <v>1.741862673983611</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.286708718109344</v>
+        <v>1.24104101221154</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.541072187529999</v>
+        <v>3.513671563991317</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.406762738104487</v>
+        <v>-2.696271459211627</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.964891562960019</v>
+        <v>1.849088074517163</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.157506904815302</v>
+        <v>1.111839198917498</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.622457225404743</v>
+        <v>3.595056601866061</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.432637136578513</v>
+        <v>-2.722145857685653</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.991619626064056</v>
+        <v>1.875816137621199</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.202418513527043</v>
+        <v>1.156750807629239</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.686482013125434</v>
+        <v>3.659081389586752</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.425582446363339</v>
+        <v>-2.715091167470479</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.99111685813967</v>
+        <v>1.875313369696814</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.209473203742217</v>
+        <v>1.163805497844413</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.687390183244084</v>
+        <v>3.659989559705402</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.398631222036851</v>
+        <v>-2.688139943143991</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.011903501515007</v>
+        <v>1.896100013072151</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.224353549769936</v>
+        <v>1.178685843872132</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.706324544505457</v>
+        <v>3.678923920966775</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.420175449867638</v>
+        <v>-2.709684170974778</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.187388942527652</v>
+        <v>2.071585454084796</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.224353549769936</v>
+        <v>1.178685843872132</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.890427676650417</v>
+        <v>3.863027053111734</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.44258356767251</v>
+        <v>-2.73209228877965</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.170542390308696</v>
+        <v>2.05473890186584</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.224353549769936</v>
+        <v>1.178685843872132</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.88254437155341</v>
+        <v>3.855143748014727</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.470807803250111</v>
+        <v>-2.760316524357251</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.161306695627293</v>
+        <v>2.045503207184438</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.242330302221244</v>
+        <v>1.19666259632344</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.895384422573832</v>
+        <v>3.86798379903515</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.480248729138641</v>
+        <v>-2.76975745024578</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.213784042993729</v>
+        <v>2.097980554550873</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.364757419764636</v>
+        <v>1.319089713866832</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.025094410821715</v>
+        <v>3.997693787283032</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.569125360307114</v>
+        <v>-2.858634081414254</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.18112448507164</v>
+        <v>2.065320996628784</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.275880788596162</v>
+        <v>1.230213082698358</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.974659526665931</v>
+        <v>3.947258903127248</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.64545533790802</v>
+        <v>-2.93496405901516</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.148704306925053</v>
+        <v>2.032900818482196</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.275880788596162</v>
+        <v>1.230213082698358</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.972771339559706</v>
+        <v>3.945370716021023</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.739119282585562</v>
+        <v>-3.028628003692702</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.106058958656899</v>
+        <v>1.990255470214042</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.182216843918621</v>
+        <v>1.136549138020817</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.911393202356043</v>
+        <v>3.883992578817361</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.900687708112817</v>
+        <v>-3.190196429219957</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.039865598656148</v>
+        <v>1.924062110213293</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.055433920120741</v>
+        <v>1.009766214222937</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.833757458287468</v>
+        <v>3.806356834748786</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.008988369982936</v>
+        <v>-3.298497091090076</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.00961874077402</v>
+        <v>1.893815252331164</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.055433920120741</v>
+        <v>1.009766214222937</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.846830865153387</v>
+        <v>3.819430241614704</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.02679234170368</v>
+        <v>-3.31630106281082</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.994502348868662</v>
+        <v>1.878698860425806</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9848992972155401</v>
+        <v>0.939231591317736</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.796515288193206</v>
+        <v>3.769114664654524</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.054693128813153</v>
+        <v>-3.344201849920293</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.981866075151875</v>
+        <v>1.866062586709019</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9503023730726053</v>
+        <v>0.9046346671748012</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.774281174834448</v>
+        <v>3.746880551295765</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.177219231516047</v>
+        <v>-3.466727952623187</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.929620078047916</v>
+        <v>1.81381658960506</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8277762703697115</v>
+        <v>0.7821085644719074</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.69752995718991</v>
+        <v>3.670129333651227</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.407733727701636</v>
+        <v>-3.697242448808776</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.904120239164184</v>
+        <v>1.788316750721328</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5972617741841227</v>
+        <v>0.5515940682863186</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.625927219069061</v>
+        <v>3.598526595530378</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.75647881292608</v>
+        <v>-4.04598753403322</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.904933924076254</v>
+        <v>1.789130435633398</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.4428461143674208</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.700990165719569</v>
+        <v>3.673589542180886</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.91046523070222</v>
+        <v>-4.19997395180936</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.912319626111437</v>
+        <v>1.796516137668581</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.4428461143674208</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.769970434865209</v>
+        <v>3.742569811326526</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.115064665565229</v>
+        <v>-4.404573386672369</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.816531054286355</v>
+        <v>1.700727565843499</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.4428461143674208</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.756021636985329</v>
+        <v>3.728621013446647</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.367539819572953</v>
+        <v>-4.657048540680093</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.727411481738679</v>
+        <v>1.611607993295823</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.4428461143674208</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.767892126040743</v>
+        <v>3.740491502502061</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.660435576052365</v>
+        <v>-4.840593851384496</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.611463713665858</v>
+        <v>1.539400403533005</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.4428461143674208</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.769102660559687</v>
+        <v>3.741702037021005</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.847099704187174</v>
+        <v>-5.027257979519304</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.540919804639256</v>
+        <v>1.468856494506404</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.461774849440665</v>
+        <v>0.4161071435428609</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.757181020292272</v>
+        <v>3.72978039675359</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.993120391101136</v>
+        <v>-5.173278666433267</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.477589382609861</v>
+        <v>1.405526072477008</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4526917576468081</v>
+        <v>0.407024051749004</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.746809017952148</v>
+        <v>3.719408394413465</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830323</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.08483440021072</v>
+        <v>-5.264992675542851</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.603107835665071</v>
+        <v>1.531044525532218</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4526917576468081</v>
+        <v>0.407024051749004</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.909013074651192</v>
+        <v>3.88161245111251</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.11648605927069</v>
+        <v>-5.296644334602821</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.585293810004897</v>
+        <v>1.513230499872045</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4475233004023679</v>
+        <v>0.4018555945045638</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.900758638268342</v>
+        <v>3.873358014729659</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586814</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.198420877539573</v>
+        <v>-5.378579152871704</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.562749300265835</v>
+        <v>1.490685990132983</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4375885548152877</v>
+        <v>0.3919208489174836</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.905027208484585</v>
+        <v>3.877626584945903</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332685</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.300396999787981</v>
+        <v>-5.480555275120111</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.530884489822375</v>
+        <v>1.458821179689522</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3356124325668801</v>
+        <v>0.289944726669076</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.852767173591443</v>
+        <v>3.82536655005276</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231801</v>
+        <v>3.798296784231803</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.190390716310759</v>
+        <v>-5.37054899164289</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.567039890457438</v>
+        <v>1.494976580324586</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3588170044841553</v>
+        <v>0.3131492985863512</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.858842803985983</v>
+        <v>3.831442180447301</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818516</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.047331140569833</v>
+        <v>-5.227489415901964</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.628513731475783</v>
+        <v>1.556450421342931</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3668304310741346</v>
+        <v>0.3211627251763305</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.867900870661945</v>
+        <v>3.840500247123263</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051782</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.745884415097995</v>
+        <v>-4.926042690430126</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.756353304547054</v>
+        <v>1.684289994414202</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6682771565459719</v>
+        <v>0.6226094506481678</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.056029788827583</v>
+        <v>4.028629165288901</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.770474659333179</v>
+        <v>-4.95063293466531</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.747488384605691</v>
+        <v>1.675425074472839</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6682771565459719</v>
+        <v>0.6226094506481678</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.057000966580294</v>
+        <v>4.029600343041611</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.719436283326659</v>
+        <v>-4.89959455865879</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.768746639388055</v>
+        <v>1.696683329255202</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6682771565459719</v>
+        <v>0.6226094506481678</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.05784387096005</v>
+        <v>4.030443247421367</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.654515880672675</v>
+        <v>-4.858455263792159</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.813752899323794</v>
+        <v>1.732177146076</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.733197559199956</v>
+        <v>0.6637487455147986</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.115834211426586</v>
+        <v>4.074164923215491</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700472</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.557880968654035</v>
+        <v>-4.761820351773519</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.668590860255184</v>
+        <v>1.587015107007391</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8298324712185959</v>
+        <v>0.7603836575334385</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.989999154761704</v>
+        <v>3.94832986655061</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077634</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.688461703184878</v>
+        <v>-4.892401086304361</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.619860610516811</v>
+        <v>1.538284857269018</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6992517366877534</v>
+        <v>0.629802923002596</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.915152758117163</v>
+        <v>3.873483469906069</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833451</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.523965368993916</v>
+        <v>-4.7279047521134</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.670085963269279</v>
+        <v>1.588510210021485</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8637480708787153</v>
+        <v>0.7942992571935579</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.998277377707822</v>
+        <v>3.956608089496728</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077623</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.446866767452043</v>
+        <v>-4.650806150571527</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.700113114322457</v>
+        <v>1.618537361074664</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8637480708787153</v>
+        <v>0.7942992571935579</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.997465088144252</v>
+        <v>3.955795799933158</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.457251962341933</v>
+        <v>-4.661191345461416</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.705827815491574</v>
+        <v>1.624252062243781</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.853362875988826</v>
+        <v>0.7839140623036686</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.001102750335392</v>
+        <v>3.959433462124297</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735275</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.475840121064158</v>
+        <v>-4.679779504183641</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.769229557779109</v>
+        <v>1.687653804531316</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8347747172666007</v>
+        <v>0.7653259035814433</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.060786860878481</v>
+        <v>4.019117572667387</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.476138667760194</v>
+        <v>-4.680078050879677</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.765979149918993</v>
+        <v>1.6844033966712</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8344761705705648</v>
+        <v>0.7650273568854074</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.057476743679158</v>
+        <v>4.015807455468064</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108851</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.375315534069766</v>
+        <v>-4.57925491718925</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.810839298334556</v>
+        <v>1.729263545086762</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8469403860549186</v>
+        <v>0.7774915723697612</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.069486167909162</v>
+        <v>4.027816879698067</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812146</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.184534173317358</v>
+        <v>-4.388473556436843</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.887281096114062</v>
+        <v>1.805705342866269</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.037721746807326</v>
+        <v>0.9682729331221686</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.18408423783915</v>
+        <v>4.142414949628055</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.077570815467936</v>
+        <v>-4.281510198587421</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.909903284991428</v>
+        <v>1.828327531743634</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.096186354767128</v>
+        <v>1.02673754108197</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.198999848352627</v>
+        <v>4.157330560141532</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912979</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.022240227566174</v>
+        <v>-4.226179610685659</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.967002456764191</v>
+        <v>1.885426703516397</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.15151694266889</v>
+        <v>1.082068128983732</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.267165137705742</v>
+        <v>4.225495849494648</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539888</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.010186100653211</v>
+        <v>-4.214125483772696</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.965510675430814</v>
+        <v>1.88393492218302</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.163571069581852</v>
+        <v>1.094122255896695</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.268084181754958</v>
+        <v>4.226414893543864</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811003</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.051341220221432</v>
+        <v>-4.255280603340917</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.950929257787661</v>
+        <v>1.869353504539867</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.122415950013631</v>
+        <v>1.052967136328474</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.245271740198161</v>
+        <v>4.203602451987067</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.983292657529902</v>
+        <v>-4.187232040649387</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.990999708742156</v>
+        <v>1.909423955494362</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.190464512705161</v>
+        <v>1.121015699020004</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.298951903690962</v>
+        <v>4.257282615479867</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013421</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.214893050699403</v>
+        <v>-4.418832433818888</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.918562221647949</v>
+        <v>1.836986468400156</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.190464512705161</v>
+        <v>1.121015699020004</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.319154573864556</v>
+        <v>4.277485285653461</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.264944596228622</v>
+        <v>-4.468883979348107</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.882147839503144</v>
+        <v>1.80057208625535</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.190464512705161</v>
+        <v>1.121015699020004</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.302760809931438</v>
+        <v>4.261091521720344</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.440051428805067</v>
+        <v>-4.643990811924551</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.772357020066033</v>
+        <v>1.690781266818239</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.190464512705161</v>
+        <v>1.121015699020004</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.263012723524905</v>
+        <v>4.22134343531381</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.243951275374544</v>
+        <v>-4.447890658494028</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.857819700435182</v>
+        <v>1.776243947187388</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.386564666135684</v>
+        <v>1.317115852450527</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.387695434580158</v>
+        <v>4.346026146369064</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395084</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.090925883261259</v>
+        <v>-4.294865266380744</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.0182008568534</v>
+        <v>1.936625103605606</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.539590058248968</v>
+        <v>1.470141244563811</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.578681669421033</v>
+        <v>4.537012381209939</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791146</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.11923319713453</v>
+        <v>-4.323172580254014</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.194344156212384</v>
+        <v>2.112768402964591</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.539590058248968</v>
+        <v>1.470141244563811</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.766147894329325</v>
+        <v>4.724478606118232</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620432</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.285826422248052</v>
+        <v>-4.489765805367536</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.097109817521059</v>
+        <v>2.015534064273265</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.372996833135446</v>
+        <v>1.303548019450288</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.635594910615294</v>
+        <v>4.593925622404201</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.262790628886486</v>
+        <v>-4.466730012005971</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.110000537527402</v>
+        <v>2.028424784279609</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.372996833135446</v>
+        <v>1.303548019450288</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.639271313277012</v>
+        <v>4.597602025065918</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399466</v>
+        <v>3.740581401399468</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.233544648430789</v>
+        <v>-4.437484031550274</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.119316984833176</v>
+        <v>2.037741231585382</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.372996833135446</v>
+        <v>1.303548019450288</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.636889368400508</v>
+        <v>4.595220080189414</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256369</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.34047019630864</v>
+        <v>-4.544409579428125</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.073840004839671</v>
+        <v>1.992264251591877</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.266071285257595</v>
+        <v>1.196622471572437</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.570027278831432</v>
+        <v>4.528357990620338</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700997</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.485488754815889</v>
+        <v>-4.689428137935374</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.017261383580006</v>
+        <v>1.935685630332212</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.121052726750346</v>
+        <v>1.051603913065189</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.484444945870317</v>
+        <v>4.442775657659223</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687008</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.603830520600606</v>
+        <v>-4.807769903720091</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.069855916523872</v>
+        <v>1.988280163276078</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.131738765313236</v>
+        <v>1.062289951628079</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.590787808265804</v>
+        <v>4.54911852005471</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790798</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.655240942921314</v>
+        <v>-4.859180326040799</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.047077444721528</v>
+        <v>1.965501691473734</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.131738765313236</v>
+        <v>1.062289951628079</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.588573505391744</v>
+        <v>4.546904217180649</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437326</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.734660394129066</v>
+        <v>-4.938599777248551</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.015212792312716</v>
+        <v>1.933637039064922</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.131738765313236</v>
+        <v>1.062289951628079</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.588476633466033</v>
+        <v>4.546807345254939</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298392</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.830123392046284</v>
+        <v>-5.034062775165768</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.977021486703872</v>
+        <v>1.895445733456078</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.131738765313236</v>
+        <v>1.062289951628079</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.588470527024076</v>
+        <v>4.546801238812981</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217994</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.765747481195569</v>
+        <v>-4.969686864315054</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.000868247606769</v>
+        <v>1.919292494358975</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.196114676163951</v>
+        <v>1.126665862478794</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.625192470097115</v>
+        <v>4.58352318188602</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73608941335353</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.821116643327763</v>
+        <v>-5.025056026447247</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.984454400501618</v>
+        <v>1.902878647253824</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.196114676163951</v>
+        <v>1.126665862478794</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.630926287844842</v>
+        <v>4.589256999633747</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113273</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.86655442315859</v>
+        <v>-5.070493806278074</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.96581765191222</v>
+        <v>1.884241898664426</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.153269685485792</v>
+        <v>1.083820871800634</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.604757656780879</v>
+        <v>4.563088368569784</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113682</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.778347589011012</v>
+        <v>-4.982286972130496</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.02097477842157</v>
+        <v>1.939399025173776</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.153269685485792</v>
+        <v>1.083820871800634</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.624632049631197</v>
+        <v>4.582962761420103</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016435</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.672312593805702</v>
+        <v>-4.876251976925187</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.047089477028421</v>
+        <v>1.965513723780627</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.153269685485792</v>
+        <v>1.083820871800634</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.608332750155925</v>
+        <v>4.566663461944831</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307667</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.489100930672607</v>
+        <v>-4.693040313792092</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.122805091745705</v>
+        <v>2.041229338497911</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.153269685485792</v>
+        <v>1.083820871800634</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.61076369961997</v>
+        <v>4.569094411408877</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863548</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.417379483658756</v>
+        <v>-4.621318866778241</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.117284856399135</v>
+        <v>2.035709103151341</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.224991132499643</v>
+        <v>1.155542318814485</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.619587753676171</v>
+        <v>4.577918465465077</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394108</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.39500645805105</v>
+        <v>-4.598945841170535</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.073149812563389</v>
+        <v>1.991574059315595</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.236246883612544</v>
+        <v>1.166798069927387</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.573256950265083</v>
+        <v>4.531587662053989</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456724</v>
+        <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.428022753961795</v>
+        <v>-4.631962137081279</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.245141499084446</v>
+        <v>2.163565745836652</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.166809506945792</v>
+        <v>1.097360693260635</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.716792729150388</v>
+        <v>4.675123440939293</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883671</v>
+        <v>3.713762536883673</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.416495118312186</v>
+        <v>-4.620434501431671</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.241673779172539</v>
+        <v>2.160098025924745</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.225810165147155</v>
+        <v>1.156361351461997</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.744114349899454</v>
+        <v>4.70244506168836</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.71715069923629</v>
+        <v>3.717150699236292</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.513836619654555</v>
+        <v>-4.717776002774039</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.20640529115738</v>
+        <v>2.124829537909586</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.181389982981667</v>
+        <v>1.111941169296509</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.72113035312195</v>
+        <v>4.679461064910855</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427678</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.599692648994521</v>
+        <v>-4.803632032114006</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.173313961614231</v>
+        <v>2.091738208366437</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.139013913755532</v>
+        <v>1.069565100070374</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.696955793779107</v>
+        <v>4.655286505568013</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610377</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.608529446410641</v>
+        <v>-4.812468829530125</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.152198444468286</v>
+        <v>2.070622691220492</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.131571741114181</v>
+        <v>1.062122927429023</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.674909692014799</v>
+        <v>4.633240403803704</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667449</v>
+        <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.699912008976099</v>
+        <v>-4.903851392095584</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.125809930487152</v>
+        <v>2.044234177239358</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.095006856394836</v>
+        <v>1.025558042709679</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.663135272228241</v>
+        <v>4.621465984017147</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889185</v>
+        <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.688205290989093</v>
+        <v>-4.892144674108578</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.232620875506221</v>
+        <v>2.151045122258427</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.106713574381843</v>
+        <v>1.037264760696685</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.772287560844712</v>
+        <v>4.730618272633618</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940956</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.588541786905431</v>
+        <v>-4.792481170024915</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.275518615871091</v>
+        <v>2.193942862623297</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.169900657585529</v>
+        <v>1.100451843900372</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.813232149498329</v>
+        <v>4.771562861287235</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452567</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.598857885071783</v>
+        <v>-4.802797268191267</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.484297009882608</v>
+        <v>2.402721256634814</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.169900657585529</v>
+        <v>1.100451843900372</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.026136982776387</v>
+        <v>4.984467694565293</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762281</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.59876391705441</v>
+        <v>-4.802703300173895</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.483513264001647</v>
+        <v>2.401937510753853</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.170270518932847</v>
+        <v>1.10082170524769</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.025537566496867</v>
+        <v>4.983868278285773</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988012</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.605982741254254</v>
+        <v>-4.809922124373739</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.474857720266063</v>
+        <v>2.393281967018269</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.170270518932847</v>
+        <v>1.10082170524769</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.019769552441221</v>
+        <v>4.978100264230127</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740918</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.605034318136216</v>
+        <v>-4.808973701255701</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.475237089513278</v>
+        <v>2.393661336265485</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.170270518932847</v>
+        <v>1.10082170524769</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.019769552441221</v>
+        <v>4.978100264230127</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.76210277639184</v>
+        <v>-4.966042159511325</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.425137314192121</v>
+        <v>2.343561560944327</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.170270518932847</v>
+        <v>1.10082170524769</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.032497160422313</v>
+        <v>4.990827872211219</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.756110529603029</v>
+        <v>-4.960049912722513</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.429480211332033</v>
+        <v>2.347904458084239</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.170270518932847</v>
+        <v>1.10082170524769</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.034443158846701</v>
+        <v>4.992773870635607</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.667552568472261</v>
+        <v>-4.871491951591746</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.458557531802109</v>
+        <v>2.376981778554315</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.170270518932847</v>
+        <v>1.10082170524769</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.02809729486447</v>
+        <v>4.986428006653376</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383087</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.649793490969187</v>
+        <v>-4.853732874088672</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.464969840242334</v>
+        <v>2.38339408699454</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.170270518932847</v>
+        <v>1.10082170524769</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.027405972303465</v>
+        <v>4.985736684092371</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.550163339920119</v>
+        <v>-4.754102723039604</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.517604086570548</v>
+        <v>2.436028333322755</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.269900669981915</v>
+        <v>1.200451856296757</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.099966248841493</v>
+        <v>5.058296960630399</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455268</v>
+        <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.59956284860913</v>
+        <v>-4.769645373645788</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.68699854859367</v>
+        <v>2.618965538579007</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.280159503413659</v>
+        <v>1.287068327129093</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.295275814399266</v>
+        <v>5.299421108628526</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.834670950636493</v>
+        <v>3.932150949698931</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.715372993705039</v>
+        <v>4.731171553180499</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.59956284860913</v>
+        <v>-4.769645373645788</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.68699854859367</v>
+        <v>2.618965538579007</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.280159503413659</v>
+        <v>1.287068327129093</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.708436790691407</v>
+        <v>4.724235350166867</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240915.xlsx
+++ b/tame_output/ON/bt/strategyON_20240915.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>62.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>161.5%</t>
+          <t>159.0%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-638.5%</t>
+          <t>-617.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-114.3%</t>
+          <t>-105.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.4%</t>
+          <t>-329.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-95.3%</t>
+          <t>-98.4%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
     </row>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.4719632562191</v>
+        <v>-8.407193204873073</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2223462179359545</v>
+        <v>-0.1964381973975438</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.456586204360987</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.374056217542609</v>
+        <v>-8.309286166196582</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1834837174388193</v>
+        <v>-0.1575756969004085</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.388600454500431</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.350102676566651</v>
+        <v>-8.285332625220624</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1732337949029423</v>
+        <v>-0.1473257743645315</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.364646913524473</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.086042738243854</v>
+        <v>-8.021272686897827</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08087013573557567</v>
+        <v>-0.05496211519716487</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.100586975201677</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.378963114739016</v>
+        <v>-7.314193063392989</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1991746800060588</v>
+        <v>0.2250827005444695</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.100586975201677</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.338778816372826</v>
+        <v>-7.274008765026799</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2155920232403763</v>
+        <v>0.2415000437787871</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.060402676835486</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.175378945433463</v>
+        <v>-7.110608894087436</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2803187928368782</v>
+        <v>0.306226813375289</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.8970028058961237</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.941897723203865</v>
+        <v>-6.877127671857838</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3816357105665698</v>
+        <v>0.4075437311049805</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.6635215836665251</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.79223133219635</v>
+        <v>-6.727461280850322</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4386100566566169</v>
+        <v>0.4645180771950277</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.5706180924239892</v>
@@ -45366,10 +45366,10 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.659955858565463</v>
+        <v>-6.595185807219436</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.392781032116126</v>
+        <v>0.4186890526545368</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4383426187931025</v>
@@ -45389,10 +45389,10 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.488094643000561</v>
+        <v>-6.423324591654533</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4643405790297237</v>
+        <v>0.4902485995681345</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.2664814032281997</v>
@@ -45412,10 +45412,10 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.403129976271241</v>
+        <v>-6.338359924925214</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5112327869451101</v>
+        <v>0.5371408074835209</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.1815167364988801</v>
@@ -45435,10 +45435,10 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.508719966044346</v>
+        <v>-6.443949914698319</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3410208614366494</v>
+        <v>0.3669288819750607</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.2871067262719845</v>
@@ -45458,10 +45458,10 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.440485381418918</v>
+        <v>-6.375715330072891</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4168590371639072</v>
+        <v>0.4427670577023179</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.2686914033994485</v>
@@ -45481,10 +45481,10 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.292545340011319</v>
+        <v>-6.227775288665292</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3594142450885398</v>
+        <v>0.3853222656269506</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.2483704874908909</v>
@@ -45504,10 +45504,10 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.239575817757331</v>
+        <v>-6.174805766411303</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3718880677366569</v>
+        <v>0.3977960882750677</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.195400965236902</v>
@@ -45527,10 +45527,10 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.07378762179704</v>
+        <v>-6.009017570451013</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4312427340256799</v>
+        <v>0.4571507545640907</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.195400965236902</v>
@@ -45550,10 +45550,10 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.040424415318271</v>
+        <v>-5.975654363972244</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4590503709983307</v>
+        <v>0.4849583915367415</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.195400965236902</v>
@@ -45573,10 +45573,10 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.932165278195749</v>
+        <v>-5.867395226849722</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4968861463065344</v>
+        <v>0.5227941668449452</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.195400965236902</v>
@@ -45596,10 +45596,10 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.808874143378619</v>
+        <v>-5.744104092032591</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5437006942439635</v>
+        <v>0.5696087147823743</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.07210983041977154</v>
@@ -45619,10 +45619,10 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.756177276247327</v>
+        <v>-5.6914072249013</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5724804193338051</v>
+        <v>0.5983884398722163</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.01941296328848036</v>
@@ -45642,10 +45642,10 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.512411834263883</v>
+        <v>-5.447641782917856</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6657673044742336</v>
+        <v>0.6916753250126444</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.01941296328848036</v>
@@ -45665,10 +45665,10 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.422636161887411</v>
+        <v>-5.357866110541384</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7038018873448384</v>
+        <v>0.7297099078832496</v>
       </c>
       <c r="F1918" t="n">
         <v>0.04218648162582966</v>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.172785767938336</v>
+        <v>-5.108015716592309</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7964841199081705</v>
+        <v>0.8223921404465813</v>
       </c>
       <c r="F1919" t="n">
         <v>0.04218648162582966</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.996893675470904</v>
+        <v>-4.932123624124877</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8704400804157921</v>
+        <v>0.8963481009542029</v>
       </c>
       <c r="F1920" t="n">
         <v>0.04218648162582966</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.825447212448441</v>
+        <v>-4.760677161102413</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9523461716793311</v>
+        <v>0.9782541922177421</v>
       </c>
       <c r="F1921" t="n">
         <v>0.2136329446482928</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.74542492533932</v>
+        <v>-4.680654873993292</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9833755641392765</v>
+        <v>1.009283584677688</v>
       </c>
       <c r="F1922" t="n">
         <v>0.2936552317574138</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.681789183105385</v>
+        <v>-4.617019131759358</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.013524662087168</v>
+        <v>1.039432682625578</v>
       </c>
       <c r="F1923" t="n">
         <v>0.3572909739913483</v>
@@ -45803,10 +45803,10 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.58809186488899</v>
+        <v>-4.523321813542963</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.032197848157521</v>
+        <v>1.058105868695932</v>
       </c>
       <c r="F1924" t="n">
         <v>0.3572909739913483</v>
@@ -45826,10 +45826,10 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.598594487954279</v>
+        <v>-4.533824436608252</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.029739875556283</v>
+        <v>1.055647896094694</v>
       </c>
       <c r="F1925" t="n">
         <v>0.3467883509260594</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.486108227285404</v>
+        <v>-4.421338175939377</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.078663693658653</v>
+        <v>1.104571714197064</v>
       </c>
       <c r="F1926" t="n">
         <v>0.3467883509260594</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.468394540407539</v>
+        <v>-4.403624489061512</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.086427752327139</v>
+        <v>1.11233577286555</v>
       </c>
       <c r="F1927" t="n">
         <v>0.3499696798229762</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.344920269094521</v>
+        <v>-4.280150217748494</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.13281553207234</v>
+        <v>1.158723552610751</v>
       </c>
       <c r="F1928" t="n">
         <v>0.3499696798229762</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.12489947105751</v>
+        <v>-4.060129419711483</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.222402888297758</v>
+        <v>1.248310908836169</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4911895248909565</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.992031781994232</v>
+        <v>-3.927261730648205</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.291444146724893</v>
+        <v>1.317352167263304</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4911895248909565</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.871858698629733</v>
+        <v>-3.807088647283706</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.340659224510995</v>
+        <v>1.366567245049405</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6113626082554554</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.736605337299756</v>
+        <v>-3.671835285953729</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.404848671604425</v>
+        <v>1.430756692142836</v>
       </c>
       <c r="F1932" t="n">
         <v>0.7466159695854325</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.796480164657448</v>
+        <v>-3.731710113311421</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.366936232062774</v>
+        <v>1.392844252601185</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6867411422277404</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.676659933746611</v>
+        <v>-3.611889882400584</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.430153493661318</v>
+        <v>1.456061514199728</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6867411422277404</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.679129640208417</v>
+        <v>-3.61435958886239</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.336809810399037</v>
+        <v>1.362717830937448</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6842714357659343</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.747499826532427</v>
+        <v>-3.6827297751864</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.228723597354734</v>
+        <v>1.254631617893145</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6935471348021492</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.859372106158578</v>
+        <v>-3.79460205481255</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.174411394136165</v>
+        <v>1.200319414674576</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6935471348021492</v>
@@ -46125,10 +46125,10 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.84339744067231</v>
+        <v>-3.778627389326283</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.1473757852547</v>
+        <v>1.173283805793111</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6935471348021492</v>
@@ -46148,10 +46148,10 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.66792318087984</v>
+        <v>-3.603153129533813</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.222132721163475</v>
+        <v>1.248040741701886</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6935471348021492</v>
@@ -46171,10 +46171,10 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.659998806294926</v>
+        <v>-3.595228754948899</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.201044499758648</v>
+        <v>1.226952520297059</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6935471348021492</v>
@@ -46194,10 +46194,10 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.653720603725077</v>
+        <v>-3.58895055237905</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.132094094188037</v>
+        <v>1.158002114726448</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6998253373719983</v>
@@ -46217,10 +46217,10 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.593867984521354</v>
+        <v>-3.529097933175327</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.166207528301659</v>
+        <v>1.19211554884007</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6998253373719983</v>
@@ -46240,10 +46240,10 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.507624521494977</v>
+        <v>-3.44285447014895</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.19565118408607</v>
+        <v>1.221559204624481</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6998253373719983</v>
@@ -46263,10 +46263,10 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.552931340893957</v>
+        <v>-3.488161289547929</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.169304231771004</v>
+        <v>1.195212252309415</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6590151743627675</v>
@@ -46286,10 +46286,10 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.581964445596258</v>
+        <v>-3.517194394250231</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.158242862923185</v>
+        <v>1.184150883461596</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6590151743627675</v>
@@ -46309,10 +46309,10 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.489153964145399</v>
+        <v>-3.424383912799372</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.124639747394894</v>
+        <v>1.150547767933305</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7518256558136268</v>
@@ -46332,10 +46332,10 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.533543433474827</v>
+        <v>-3.468773382128799</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.108757435587724</v>
+        <v>1.134665456126135</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7074361864841991</v>
@@ -46355,10 +46355,10 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.513039739589329</v>
+        <v>-3.448269688243302</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.112034621653646</v>
+        <v>1.137942642192057</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7279398803696965</v>
@@ -46378,10 +46378,10 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.552963834171901</v>
+        <v>-3.488193782825874</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.101556279651284</v>
+        <v>1.127464300189695</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7279398803696965</v>
@@ -46401,10 +46401,10 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.580744232073255</v>
+        <v>-3.515974180727227</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.101941322259282</v>
+        <v>1.127849342797693</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7001594824683435</v>
@@ -46424,10 +46424,10 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.699124904803393</v>
+        <v>-3.634354853457366</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8929447731678799</v>
+        <v>0.9188527937062907</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6329416303173673</v>
@@ -46447,10 +46447,10 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.807738983246724</v>
+        <v>-3.742968931900697</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9696488025097532</v>
+        <v>0.995556823048164</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6329416303173673</v>
@@ -46470,10 +46470,10 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.772329944998581</v>
+        <v>-3.707559893652554</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9983254439113332</v>
+        <v>1.024233464449744</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6329416303173673</v>
@@ -46493,10 +46493,10 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.780791113654042</v>
+        <v>-3.716021062308015</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9923604177915175</v>
+        <v>1.018268438329928</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6244804616619062</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.812060853445169</v>
+        <v>-3.538904732272849</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.976581550720369</v>
+        <v>1.085843999189297</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6244804616619062</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.857153098278715</v>
+        <v>-3.583996977106395</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9592280445488637</v>
+        <v>1.068490493017792</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5625844184925164</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.677777677039948</v>
+        <v>-3.404621555867627</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.024765188350785</v>
+        <v>1.134027636819713</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7193611766632351</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.722791890560554</v>
+        <v>-3.449635769388233</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9875669582741324</v>
+        <v>1.096829406743061</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6890122813486305</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.989796400832989</v>
+        <v>-3.716640279660669</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.886456716504104</v>
+        <v>0.9957191649730321</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4946492433056819</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.090994182270162</v>
+        <v>-3.817838061097842</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8451815258257365</v>
+        <v>0.9544439742946644</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4262404297603627</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.084483215655849</v>
+        <v>-3.811327094483529</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8453858740257783</v>
+        <v>0.9546483224947062</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4262404297603627</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.065445087948552</v>
+        <v>-3.792288966776232</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.849525844316942</v>
+        <v>0.9587882927858702</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3680568184291682</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.117960890223372</v>
+        <v>-3.844804769051052</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9478139250412041</v>
+        <v>1.057076373510133</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3680568184291682</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.121369201657952</v>
+        <v>-3.848213080485631</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9472839294535058</v>
+        <v>1.056546377922434</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4005733874385456</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.102013065764105</v>
+        <v>-3.828856944591784</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9610349142079708</v>
+        <v>1.070297362676899</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4005733874385456</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.954270095529103</v>
+        <v>-3.681113974356782</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9180823235791711</v>
+        <v>1.027344772048099</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5683807446734288</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.038091316803801</v>
+        <v>-3.76493519563148</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8873474566007729</v>
+        <v>0.996609905069701</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5683807446734288</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.031938610751016</v>
+        <v>-3.758782489578696</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.890470887413545</v>
+        <v>0.9997333358824732</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5745334507262131</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.048747908901518</v>
+        <v>-3.775591787729197</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8828276448934544</v>
+        <v>0.9920900933623829</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5577241525757115</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.986449910125396</v>
+        <v>-3.713293788953075</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9740823982007241</v>
+        <v>1.083344846669652</v>
       </c>
       <c r="F1970" t="n">
         <v>0.6030184168501536</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.784659712460238</v>
+        <v>-3.511503591287918</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8570904789809144</v>
+        <v>0.9663529274498426</v>
       </c>
       <c r="F1971" t="n">
         <v>0.801036609019308</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.835546425146433</v>
+        <v>-3.562390303974112</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9070260262286116</v>
+        <v>1.01628847469754</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7501498963331135</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319539</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.748935682496626</v>
+        <v>-3.475779561324305</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9562980594045782</v>
+        <v>1.065560507873506</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8287756275382717</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.80914498050191</v>
+        <v>-3.535988859329589</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9307503210271362</v>
+        <v>1.040012769496064</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7685663295329872</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397788</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.759958331817559</v>
+        <v>-3.486802210645238</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9489165985408052</v>
+        <v>1.058179047009733</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7685663295329872</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316243</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.71558520017899</v>
+        <v>-3.442429079006669</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9665287186316689</v>
+        <v>1.075791167100597</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8129394611715558</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.738065551037875</v>
+        <v>-3.464909429865554</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9519303724267054</v>
+        <v>1.061192820895634</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8129394611715558</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.69040982047682</v>
+        <v>-3.417253699304498</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9773744216789322</v>
+        <v>1.086636870147861</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8605951917326115</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.589891661978065</v>
+        <v>-3.316735540805744</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.022474058453159</v>
+        <v>1.131736506922087</v>
       </c>
       <c r="F1979" t="n">
         <v>0.961113350231366</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.573986332545712</v>
+        <v>-3.300830211373391</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.015590862701972</v>
+        <v>1.124853311170901</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8820006895221271</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.529147930937314</v>
+        <v>-3.255991809764993</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.03762392595596</v>
+        <v>1.146886374424888</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8865441224669965</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.548646387179323</v>
+        <v>-3.275490266007001</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.033985483090235</v>
+        <v>1.143247931559163</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8384594811870922</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.504443550093422</v>
+        <v>-3.231287428921101</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.057546220452432</v>
+        <v>1.166808668921361</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8826623182729927</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.512003215930469</v>
+        <v>-3.238847094758148</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.052932354586861</v>
+        <v>1.162194803055789</v>
       </c>
       <c r="F1984" t="n">
         <v>0.937465722282812</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.353711798391197</v>
+        <v>-3.080555677218876</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.167496686785609</v>
+        <v>1.276759135254538</v>
       </c>
       <c r="F1985" t="n">
         <v>0.937465722282812</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.146069794756721</v>
+        <v>-2.872913673584399</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.248994192833653</v>
+        <v>1.358256641302581</v>
       </c>
       <c r="F1986" t="n">
         <v>1.145107725917288</v>
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.140705407931997</v>
+        <v>-2.821881580861871</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.246088175801812</v>
+        <v>1.373617706629863</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.150472112742012</v>
+        <v>1.196139818639816</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.193010030933567</v>
+        <v>3.220410654472249</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.075481226804792</v>
+        <v>-2.756657399734666</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.289365252345399</v>
+        <v>1.41689478317345</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.215696293869218</v>
+        <v>1.261363999767022</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.249331943702595</v>
+        <v>3.276732567241277</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.038054206733658</v>
+        <v>-2.719230379663532</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.300297032673133</v>
+        <v>1.427826563501184</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.220947831898399</v>
+        <v>1.266615537796203</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.248443838819384</v>
+        <v>3.275844462358067</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.058165862768366</v>
+        <v>-2.73934203569824</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.29350916259049</v>
+        <v>1.421038693418541</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.231975176895818</v>
+        <v>1.277642882793623</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.256317038149076</v>
+        <v>3.283717661687759</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.029752599668483</v>
+        <v>-2.710928772598356</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.465432238851655</v>
+        <v>1.592961769679705</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.17299961414939</v>
+        <v>1.218667320047194</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.38148947152243</v>
+        <v>3.408890095061112</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.95497033864347</v>
+        <v>-2.636146511573344</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.615458052479477</v>
+        <v>1.742987583307527</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.247781875174402</v>
+        <v>1.293449581072206</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.546471737355255</v>
+        <v>3.573872360893937</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.928886254379662</v>
+        <v>-2.610062427309536</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.617599662198859</v>
+        <v>1.745129193026909</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.247781875174402</v>
+        <v>1.293449581072206</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.538179713369114</v>
+        <v>3.565580336907796</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.841008341270542</v>
+        <v>-2.522184514200415</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.650944023026287</v>
+        <v>1.778473553854337</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.363707517597753</v>
+        <v>1.409375223495557</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.605928294406903</v>
+        <v>3.633328917945586</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.832115879877258</v>
+        <v>-2.513292052807132</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.672055413310391</v>
+        <v>1.799584944138442</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.363707517597753</v>
+        <v>1.409375223495557</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.623482700133695</v>
+        <v>3.650883323672377</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.000591996847136</v>
+        <v>-2.68176816977701</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.596520013927024</v>
+        <v>1.724049544755075</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.335759681881173</v>
+        <v>1.381427387778977</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.59856904610833</v>
+        <v>3.625969669647013</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.554335804217696</v>
+        <v>-2.23551197714757</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.756292188166662</v>
+        <v>1.883821718994712</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.24104101221154</v>
+        <v>1.286708718109344</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.523007541494413</v>
+        <v>3.550408165033095</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.567069645917584</v>
+        <v>-2.212790873464417</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.741862673983611</v>
+        <v>1.883574182964878</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.24104101221154</v>
+        <v>1.286708718109344</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.513671563991317</v>
+        <v>3.541072187529999</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.696271459211627</v>
+        <v>-2.34199268675846</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.849088074517163</v>
+        <v>1.99079958349843</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.111839198917498</v>
+        <v>1.157506904815302</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.595056601866061</v>
+        <v>3.622457225404743</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.722145857685653</v>
+        <v>-2.367867085232485</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.875816137621199</v>
+        <v>2.017527646602467</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.156750807629239</v>
+        <v>1.202418513527043</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.659081389586752</v>
+        <v>3.686482013125434</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.715091167470479</v>
+        <v>-2.360812395017312</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.875313369696814</v>
+        <v>2.017024878678081</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.163805497844413</v>
+        <v>1.209473203742217</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.659989559705402</v>
+        <v>3.687390183244084</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.688139943143991</v>
+        <v>-2.333861170690824</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.896100013072151</v>
+        <v>2.037811522053418</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.178685843872132</v>
+        <v>1.224353549769936</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.678923920966775</v>
+        <v>3.706324544505457</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.709684170974778</v>
+        <v>-2.355405398521611</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.071585454084796</v>
+        <v>2.213296963066063</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.178685843872132</v>
+        <v>1.224353549769936</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.863027053111734</v>
+        <v>3.890427676650417</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.73209228877965</v>
+        <v>-2.377813516326483</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.05473890186584</v>
+        <v>2.196450410847107</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.178685843872132</v>
+        <v>1.224353549769936</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.855143748014727</v>
+        <v>3.88254437155341</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.760316524357251</v>
+        <v>-2.406037751904083</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.045503207184438</v>
+        <v>2.187214716165704</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.19666259632344</v>
+        <v>1.242330302221244</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.86798379903515</v>
+        <v>3.895384422573832</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.76975745024578</v>
+        <v>-2.415478677792613</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.097980554550873</v>
+        <v>2.239692063532139</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.319089713866832</v>
+        <v>1.364757419764636</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.997693787283032</v>
+        <v>4.025094410821715</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.858634081414254</v>
+        <v>-2.504355308961087</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.065320996628784</v>
+        <v>2.207032505610051</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.230213082698358</v>
+        <v>1.275880788596162</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.947258903127248</v>
+        <v>3.974659526665931</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.93496405901516</v>
+        <v>-2.580685286561993</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.032900818482196</v>
+        <v>2.174612327463463</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.230213082698358</v>
+        <v>1.275880788596162</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.945370716021023</v>
+        <v>3.972771339559706</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.028628003692702</v>
+        <v>-2.674349231239534</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.990255470214042</v>
+        <v>2.131966979195309</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.136549138020817</v>
+        <v>1.182216843918621</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.883992578817361</v>
+        <v>3.911393202356043</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.190196429219957</v>
+        <v>-2.83591765676679</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.924062110213293</v>
+        <v>2.06577361919456</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.009766214222937</v>
+        <v>1.055433920120741</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.806356834748786</v>
+        <v>3.833757458287468</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.298497091090076</v>
+        <v>-2.944218318636909</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.893815252331164</v>
+        <v>2.03552676131243</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.009766214222937</v>
+        <v>1.055433920120741</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.819430241614704</v>
+        <v>3.846830865153387</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.31630106281082</v>
+        <v>-2.962022290357653</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.878698860425806</v>
+        <v>2.020410369407073</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.939231591317736</v>
+        <v>0.9848992972155401</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.769114664654524</v>
+        <v>3.796515288193206</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.344201849920293</v>
+        <v>-2.989923077467126</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.866062586709019</v>
+        <v>2.007774095690285</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9046346671748012</v>
+        <v>0.9503023730726053</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.746880551295765</v>
+        <v>3.774281174834448</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.466727952623187</v>
+        <v>-3.11244918017002</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.81381658960506</v>
+        <v>1.955528098586327</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7821085644719074</v>
+        <v>0.8277762703697115</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.670129333651227</v>
+        <v>3.69752995718991</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.697242448808776</v>
+        <v>-3.342963676355609</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.788316750721328</v>
+        <v>1.930028259702595</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5515940682863186</v>
+        <v>0.5972617741841227</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.598526595530378</v>
+        <v>3.625927219069061</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.04598753403322</v>
+        <v>-3.691708761580053</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.789130435633398</v>
+        <v>1.930841944614665</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4428461143674208</v>
+        <v>0.4885138202652249</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.673589542180886</v>
+        <v>3.700990165719569</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.19997395180936</v>
+        <v>-3.845695179356193</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.796516137668581</v>
+        <v>1.938227646649848</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4428461143674208</v>
+        <v>0.4885138202652249</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.742569811326526</v>
+        <v>3.769970434865209</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.404573386672369</v>
+        <v>-4.050294614219202</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.700727565843499</v>
+        <v>1.842439074824765</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4428461143674208</v>
+        <v>0.4885138202652249</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.728621013446647</v>
+        <v>3.756021636985329</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.657048540680093</v>
+        <v>-4.302769768226926</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.611607993295823</v>
+        <v>1.75331950227709</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4428461143674208</v>
+        <v>0.4885138202652249</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.740491502502061</v>
+        <v>3.767892126040743</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.840593851384496</v>
+        <v>-4.595665524706338</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.539400403533005</v>
+        <v>1.637371734204269</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4428461143674208</v>
+        <v>0.4885138202652249</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.741702037021005</v>
+        <v>3.769102660559687</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.027257979519304</v>
+        <v>-4.782329652841146</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.468856494506404</v>
+        <v>1.566827825177667</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4161071435428609</v>
+        <v>0.461774849440665</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.72978039675359</v>
+        <v>3.757181020292272</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.173278666433267</v>
+        <v>-4.928350339755109</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.405526072477008</v>
+        <v>1.503497403148271</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.407024051749004</v>
+        <v>0.4526917576468081</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.719408394413465</v>
+        <v>3.746809017952148</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830323</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.264992675542851</v>
+        <v>-5.020064348864693</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.531044525532218</v>
+        <v>1.629015856203482</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.407024051749004</v>
+        <v>0.4526917576468081</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.88161245111251</v>
+        <v>3.909013074651192</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.296644334602821</v>
+        <v>-5.051716007924663</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.513230499872045</v>
+        <v>1.611201830543308</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4018555945045638</v>
+        <v>0.4475233004023679</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.873358014729659</v>
+        <v>3.900758638268342</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.75004401586814</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.378579152871704</v>
+        <v>-5.133650826193546</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.490685990132983</v>
+        <v>1.588657320804246</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3919208489174836</v>
+        <v>0.4375885548152877</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.877626584945903</v>
+        <v>3.905027208484585</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332685</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.480555275120111</v>
+        <v>-5.235626948441953</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.458821179689522</v>
+        <v>1.556792510360785</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.289944726669076</v>
+        <v>0.3356124325668801</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.82536655005276</v>
+        <v>3.852767173591443</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231803</v>
+        <v>3.798296784231801</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.37054899164289</v>
+        <v>-5.125620664964732</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.494976580324586</v>
+        <v>1.592947910995849</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3131492985863512</v>
+        <v>0.3588170044841553</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.831442180447301</v>
+        <v>3.858842803985983</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818516</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.227489415901964</v>
+        <v>-4.982561089223806</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.556450421342931</v>
+        <v>1.654421752014194</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3211627251763305</v>
+        <v>0.3668304310741346</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.840500247123263</v>
+        <v>3.867900870661945</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.926042690430126</v>
+        <v>-4.681114363751968</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.684289994414202</v>
+        <v>1.782261325085465</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6226094506481678</v>
+        <v>0.6682771565459719</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.028629165288901</v>
+        <v>4.056029788827583</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.95063293466531</v>
+        <v>-4.705704607987152</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.675425074472839</v>
+        <v>1.773396405144102</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6226094506481678</v>
+        <v>0.6682771565459719</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.029600343041611</v>
+        <v>4.057000966580294</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.89959455865879</v>
+        <v>-4.654666231980632</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.696683329255202</v>
+        <v>1.794654659926466</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6226094506481678</v>
+        <v>0.6682771565459719</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.030443247421367</v>
+        <v>4.05784387096005</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.858455263792159</v>
+        <v>-4.613526937114001</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.732177146076</v>
+        <v>1.830148476747264</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6637487455147986</v>
+        <v>0.7094164514126027</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.074164923215491</v>
+        <v>4.101565546754173</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700474</v>
+        <v>3.825752932700472</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.761820351773519</v>
+        <v>-4.516892025095361</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.587015107007391</v>
+        <v>1.684986437678654</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7603836575334385</v>
+        <v>0.8060513634312426</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.94832986655061</v>
+        <v>3.975730490089292</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.892401086304361</v>
+        <v>-4.647472759626203</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.538284857269018</v>
+        <v>1.636256187940281</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.629802923002596</v>
+        <v>0.6754706289004001</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.873483469906069</v>
+        <v>3.900884093444751</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.7279047521134</v>
+        <v>-4.482976425435242</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.588510210021485</v>
+        <v>1.686481540692748</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7942992571935579</v>
+        <v>0.839966963091362</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.956608089496728</v>
+        <v>3.98400871303541</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077623</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.650806150571527</v>
+        <v>-4.405877823893369</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.618537361074664</v>
+        <v>1.716508691745927</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7942992571935579</v>
+        <v>0.839966963091362</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.955795799933158</v>
+        <v>3.98319642347184</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.661191345461416</v>
+        <v>-4.416263018783258</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.624252062243781</v>
+        <v>1.722223392915044</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7839140623036686</v>
+        <v>0.8295817682014727</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.959433462124297</v>
+        <v>3.986834085662979</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.679779504183641</v>
+        <v>-4.434851177505483</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.687653804531316</v>
+        <v>1.785625135202579</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7653259035814433</v>
+        <v>0.8109936094792474</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.019117572667387</v>
+        <v>4.046518196206069</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.680078050879677</v>
+        <v>-4.435149724201519</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.6844033966712</v>
+        <v>1.782374727342463</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7650273568854074</v>
+        <v>0.8106950627832115</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.015807455468064</v>
+        <v>4.043208079006746</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.57925491718925</v>
+        <v>-4.334326590511091</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.729263545086762</v>
+        <v>1.827234875758026</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.7774915723697612</v>
+        <v>0.8231592782675653</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.027816879698067</v>
+        <v>4.05521750323675</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.388473556436843</v>
+        <v>-4.143545229758685</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.805705342866269</v>
+        <v>1.903676673537532</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9682729331221686</v>
+        <v>1.013940639019973</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.142414949628055</v>
+        <v>4.169815573166738</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.281510198587421</v>
+        <v>-4.036581871909263</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.828327531743634</v>
+        <v>1.926298862414897</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.02673754108197</v>
+        <v>1.072405246979774</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.157330560141532</v>
+        <v>4.184731183680215</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.226179610685659</v>
+        <v>-3.981251284007501</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.885426703516397</v>
+        <v>1.98339803418766</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.082068128983732</v>
+        <v>1.127735834881536</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.225495849494648</v>
+        <v>4.252896473033331</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.214125483772696</v>
+        <v>-3.969197157094538</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.88393492218302</v>
+        <v>1.981906252854283</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.094122255896695</v>
+        <v>1.139789961794499</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.226414893543864</v>
+        <v>4.253815517082546</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.255280603340917</v>
+        <v>-4.01035227666276</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.869353504539867</v>
+        <v>1.96732483521113</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.052967136328474</v>
+        <v>1.098634842226278</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.203602451987067</v>
+        <v>4.23100307552575</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.187232040649387</v>
+        <v>-3.94230371397123</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.909423955494362</v>
+        <v>2.007395286165625</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.121015699020004</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.257282615479867</v>
+        <v>4.28468323901855</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013421</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.418832433818888</v>
+        <v>-4.17390410714073</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.836986468400156</v>
+        <v>1.934957799071419</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.121015699020004</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.277485285653461</v>
+        <v>4.304885909192144</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.468883979348107</v>
+        <v>-4.22395565266995</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.80057208625535</v>
+        <v>1.898543416926613</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.121015699020004</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.261091521720344</v>
+        <v>4.288492145259026</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.643990811924551</v>
+        <v>-4.399062485246395</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.690781266818239</v>
+        <v>1.788752597489502</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.121015699020004</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.22134343531381</v>
+        <v>4.248744058852493</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.447890658494028</v>
+        <v>-4.202962331815872</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.776243947187388</v>
+        <v>1.874215277858651</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.317115852450527</v>
+        <v>1.362783558348331</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.346026146369064</v>
+        <v>4.373426769907747</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395084</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.294865266380744</v>
+        <v>-4.049936939702588</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.936625103605606</v>
+        <v>2.034596434276869</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.470141244563811</v>
+        <v>1.515808950461615</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.537012381209939</v>
+        <v>4.564413004748621</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.741278332791146</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.323172580254014</v>
+        <v>-4.078244253575858</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.112768402964591</v>
+        <v>2.210739733635854</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.470141244563811</v>
+        <v>1.515808950461615</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.724478606118232</v>
+        <v>4.751879229656914</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.489765805367536</v>
+        <v>-4.24483747868938</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.015534064273265</v>
+        <v>2.113505394944527</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.303548019450288</v>
+        <v>1.349215725348093</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.593925622404201</v>
+        <v>4.621326245942883</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.466730012005971</v>
+        <v>-4.221801685327814</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.028424784279609</v>
+        <v>2.126396114950871</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.303548019450288</v>
+        <v>1.349215725348093</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.597602025065918</v>
+        <v>4.625002648604601</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399468</v>
+        <v>3.740581401399466</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.437484031550274</v>
+        <v>-4.192555704872118</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.037741231585382</v>
+        <v>2.135712562256645</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.303548019450288</v>
+        <v>1.349215725348093</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.595220080189414</v>
+        <v>4.622620703728096</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256369</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.544409579428125</v>
+        <v>-4.299481252749969</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.992264251591877</v>
+        <v>2.09023558226314</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.196622471572437</v>
+        <v>1.242290177470241</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.528357990620338</v>
+        <v>4.555758614159021</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600700997</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.689428137935374</v>
+        <v>-4.444499811257217</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.935685630332212</v>
+        <v>2.033656961003475</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.051603913065189</v>
+        <v>1.097271618962993</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.442775657659223</v>
+        <v>4.470176281197905</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687008</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.807769903720091</v>
+        <v>-4.562841577041935</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.988280163276078</v>
+        <v>2.086251493947341</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.062289951628079</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.54911852005471</v>
+        <v>4.576519143593393</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790798</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.859180326040799</v>
+        <v>-4.614251999362643</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.965501691473734</v>
+        <v>2.063473022144996</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.062289951628079</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.546904217180649</v>
+        <v>4.574304840719331</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437326</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.938599777248551</v>
+        <v>-4.693671450570394</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.933637039064922</v>
+        <v>2.031608369736185</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.062289951628079</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.546807345254939</v>
+        <v>4.574207968793621</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298392</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.034062775165768</v>
+        <v>-4.789134448487612</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.895445733456078</v>
+        <v>1.993417064127341</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.062289951628079</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.546801238812981</v>
+        <v>4.574201862351663</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960217994</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.969686864315054</v>
+        <v>-4.724758537636897</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.919292494358975</v>
+        <v>2.017263825030238</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.126665862478794</v>
+        <v>1.172333568376598</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.58352318188602</v>
+        <v>4.610923805424703</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.73608941335353</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.025056026447247</v>
+        <v>-4.780127699769091</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.902878647253824</v>
+        <v>2.000849977925086</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.126665862478794</v>
+        <v>1.172333568376598</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.589256999633747</v>
+        <v>4.61665762317243</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113273</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.070493806278074</v>
+        <v>-4.825565479599918</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.884241898664426</v>
+        <v>1.982213229335688</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.083820871800634</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.563088368569784</v>
+        <v>4.590488992108467</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113682</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.982286972130496</v>
+        <v>-4.73735864545234</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.939399025173776</v>
+        <v>2.037370355845038</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.083820871800634</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.582962761420103</v>
+        <v>4.610363384958785</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.876251976925187</v>
+        <v>-4.631323650247031</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.965513723780627</v>
+        <v>2.06348505445189</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.083820871800634</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.566663461944831</v>
+        <v>4.594064085483513</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.794705093307667</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.693040313792092</v>
+        <v>-4.448111987113935</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.041229338497911</v>
+        <v>2.139200669169173</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.083820871800634</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.569094411408877</v>
+        <v>4.596495034947559</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863548</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.621318866778241</v>
+        <v>-4.376390540100084</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.035709103151341</v>
+        <v>2.133680433822604</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.155542318814485</v>
+        <v>1.201210024712289</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.577918465465077</v>
+        <v>4.605319089003759</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394108</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.598945841170535</v>
+        <v>-4.354017514492378</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.991574059315595</v>
+        <v>2.089545389986858</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.166798069927387</v>
+        <v>1.212465775825191</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.531587662053989</v>
+        <v>4.558988285592672</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456726</v>
+        <v>3.715607446456724</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.631962137081279</v>
+        <v>-4.387033810403123</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.163565745836652</v>
+        <v>2.261537076507915</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.097360693260635</v>
+        <v>1.143028399158439</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.675123440939293</v>
+        <v>4.702524064477975</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883673</v>
+        <v>3.713762536883671</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.620434501431671</v>
+        <v>-4.375506174753514</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.160098025924745</v>
+        <v>2.258069356596007</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.156361351461997</v>
+        <v>1.202029057359802</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.70244506168836</v>
+        <v>4.729845685227042</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236292</v>
+        <v>3.71715069923629</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.717776002774039</v>
+        <v>-4.472847676095883</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.124829537909586</v>
+        <v>2.222800868580848</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.111941169296509</v>
+        <v>1.157608875194313</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.679461064910855</v>
+        <v>4.706861688449537</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.705201079427678</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.803632032114006</v>
+        <v>-4.55870370543585</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.091738208366437</v>
+        <v>2.1897095390377</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.069565100070374</v>
+        <v>1.115232805968178</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.655286505568013</v>
+        <v>4.682687129106695</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610377</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.812468829530125</v>
+        <v>-4.567540502851969</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.070622691220492</v>
+        <v>2.168594021891754</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.062122927429023</v>
+        <v>1.107790633326827</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.633240403803704</v>
+        <v>4.660641027342386</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667451</v>
+        <v>3.715544411667449</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.903851392095584</v>
+        <v>-4.658923065417428</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.044234177239358</v>
+        <v>2.14220550791062</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.025558042709679</v>
+        <v>1.071225748607483</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.621465984017147</v>
+        <v>4.648866607555829</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889186</v>
+        <v>3.673978374889185</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.892144674108578</v>
+        <v>-4.647216347430422</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.151045122258427</v>
+        <v>2.249016452929689</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.037264760696685</v>
+        <v>1.082932466594489</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.730618272633618</v>
+        <v>4.7580188961723</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.68247609940956</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.792481170024915</v>
+        <v>-4.547552843346759</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.193942862623297</v>
+        <v>2.291914193294559</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.100451843900372</v>
+        <v>1.146119549798176</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.771562861287235</v>
+        <v>4.798963484825917</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452567</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.802797268191267</v>
+        <v>-4.557868941513111</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.402721256634814</v>
+        <v>2.500692587306077</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.100451843900372</v>
+        <v>1.146119549798176</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.984467694565293</v>
+        <v>5.011868318103975</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762281</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.802703300173895</v>
+        <v>-4.557774973495738</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.401937510753853</v>
+        <v>2.499908841425116</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.10082170524769</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.983868278285773</v>
+        <v>5.011268901824455</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988012</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.809922124373739</v>
+        <v>-4.564993797695583</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.393281967018269</v>
+        <v>2.491253297689532</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.10082170524769</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.978100264230127</v>
+        <v>5.005500887768809</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740918</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.808973701255701</v>
+        <v>-4.564045374577544</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.393661336265485</v>
+        <v>2.491632666936747</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.10082170524769</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.978100264230127</v>
+        <v>5.005500887768809</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.966042159511325</v>
+        <v>-4.721113832833169</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.343561560944327</v>
+        <v>2.441532891615589</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.10082170524769</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.990827872211219</v>
+        <v>5.018228495749901</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.960049912722513</v>
+        <v>-4.715121586044357</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.347904458084239</v>
+        <v>2.445875788755502</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.10082170524769</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.992773870635607</v>
+        <v>5.020174494174289</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.871491951591746</v>
+        <v>-4.626563624913589</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.376981778554315</v>
+        <v>2.474953109225578</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.10082170524769</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.986428006653376</v>
+        <v>5.013828630192058</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383087</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.853732874088672</v>
+        <v>-4.608804547410515</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.38339408699454</v>
+        <v>2.481365417665803</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.10082170524769</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.985736684092371</v>
+        <v>5.013137307631053</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.754102723039604</v>
+        <v>-4.509174396361447</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.436028333322755</v>
+        <v>2.533999663994017</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.200451856296757</v>
+        <v>1.246119562194561</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.058296960630399</v>
+        <v>5.085697584169081</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.77535709745527</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.769645373645788</v>
+        <v>-4.558573905050459</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.618965538579007</v>
+        <v>2.703394126017139</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.287068327129093</v>
+        <v>1.256378395626306</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.299421108628526</v>
+        <v>5.281007149726854</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.932150949698931</v>
+        <v>3.904223362177633</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.731171553180499</v>
+        <v>4.706422052389424</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.769645373645788</v>
+        <v>-4.558573905050459</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.618965538579007</v>
+        <v>2.703394126017139</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.287068327129093</v>
+        <v>1.256378395626306</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.724235350166867</v>
+        <v>4.699485849375792</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240915.xlsx
+++ b/tame_output/ON/bt/strategyON_20240915.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>63.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>159.0%</t>
+          <t>139.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-46.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-617.4%</t>
+          <t>-616.1%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>367.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-105.9%</t>
+          <t>-106.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.3%</t>
+          <t>-320.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-98.4%</t>
+          <t>-88.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>116.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>86.6%</t>
         </is>
       </c>
     </row>
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.236166003327313</v>
+        <v>-5.132221752781266</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.02185615028424</v>
+        <v>1.063433850502658</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.4017410483150389</v>
+        <v>-0.3045040951281515</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.87563434693989</v>
+        <v>2.933976518852022</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.644754780507992</v>
+        <v>-5.540810529961944</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.857182183426727</v>
+        <v>0.8987598836451465</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7130928723088299</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.629242624646241</v>
+        <v>2.687584796558374</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.758515192530857</v>
+        <v>-5.654570941984809</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.806863451089042</v>
+        <v>0.848441151307461</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7130928723088299</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.624428057117702</v>
+        <v>2.682770229029835</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.174907066817855</v>
+        <v>-6.070962816271806</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6383007519831203</v>
+        <v>0.6798784522015393</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7130928723088299</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.622422107726579</v>
+        <v>2.680764279638712</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.536080696634842</v>
+        <v>-6.432136446088794</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5040899907250038</v>
+        <v>0.5456676909434233</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7130928723088299</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.632680798395258</v>
+        <v>2.691022970307391</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.879339216277861</v>
+        <v>-6.775394965731813</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3628861480134917</v>
+        <v>0.4044638482319107</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7130928723088299</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.628780363540954</v>
+        <v>2.687122535453086</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.927542033520205</v>
+        <v>-6.823597782974157</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3420099411715549</v>
+        <v>0.3835876413899744</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7130928723088299</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.627185283595955</v>
+        <v>2.685527455508087</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.094350693494567</v>
+        <v>-6.990406442948519</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2790654531110186</v>
+        <v>0.3206431533294376</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.7553761960219665</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.605594265297281</v>
+        <v>2.663936437209413</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.28107040180387</v>
+        <v>-7.177126151257822</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2003512652528943</v>
+        <v>0.2419289654713133</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.7553761960219665</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.601567960762878</v>
+        <v>2.65991013267501</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.664071790546501</v>
+        <v>-7.560127540000453</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.04704860843425784</v>
+        <v>0.08862630865267684</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.7553761960219665</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.601465859441294</v>
+        <v>2.659808031353426</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.66855823574789</v>
+        <v>-7.564613985201841</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.04782554632513225</v>
+        <v>0.0894032465435517</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8570995944102426</v>
+        <v>-0.7598626412233551</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.601345508291891</v>
+        <v>2.659687680204023</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.028088558251891</v>
+        <v>-7.924144307705843</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.09063627937841856</v>
+        <v>-0.04905857915999867</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8570995944102426</v>
+        <v>-0.7598626412233551</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.606695811589941</v>
+        <v>2.665037983502073</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.078437621706113</v>
+        <v>-7.974493371160065</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1028598848029296</v>
+        <v>-0.06128218458451018</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.9074486578644647</v>
+        <v>-0.8102117046775772</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.584402393474585</v>
+        <v>2.642744565386717</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-8.072112648581463</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>-0.09728814493130011</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.005067935285861</v>
+        <v>-0.9078309820989738</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.528872577643516</v>
+        <v>2.587214749555649</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-8.126184148089822</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>-0.1160231884130716</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.059139434794221</v>
+        <v>-0.9619024816073333</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.499323234260073</v>
+        <v>2.557665406172205</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-8.129759934181569</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>-0.1119403057311281</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.084668356710713</v>
+        <v>-0.9874314035238259</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.489519078228819</v>
+        <v>2.547861250140952</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.163412772690043</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>-0.1209188866500814</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.185081724627751</v>
+        <v>-1.087844771440863</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.433753611963033</v>
+        <v>2.492095783875166</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.3024988873089</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.1611816310042031</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.324167839246607</v>
+        <v>-1.22693088605972</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.36567364468514</v>
+        <v>2.424015816597272</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.477623304695443</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.2166761772113039</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.402055303446264</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.275154215000731</v>
+        <v>2.333496386912863</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.712075398709933</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.3176761797186956</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.402055303446264</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.267935050099135</v>
+        <v>2.326277222011267</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-8.81645012973638</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.3660982629032503</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.603666987659597</v>
+        <v>-1.50643003447271</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.198638020709291</v>
+        <v>2.256980192621423</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-8.978963595434964</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.429987859344128</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.701300418078284</v>
+        <v>-1.604063464891397</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.141173752296635</v>
+        <v>2.199515924208768</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-9.105000388803253</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.4777088480623291</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.578811842081654</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.159018454611595</v>
+        <v>2.217360626523727</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-9.047928616907322</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.4508898036175557</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.578811842081654</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.163008790297996</v>
+        <v>2.221350962210129</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.189600458631443</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.5090337672059455</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.578811842081654</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.161533563399254</v>
+        <v>2.219875735311387</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-9.140009614206608</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.4741440192711397</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.626457950843708</v>
+        <v>-1.52922099765682</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.206341480219027</v>
+        <v>2.26468365213116</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-8.991091279734752</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.4276278191290799</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.595208360108535</v>
+        <v>-1.497971406921647</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.212040101013448</v>
+        <v>2.27038227292558</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.765246127015342</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.327710685005107</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.456044731334484</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.305117351314087</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.64066747067775</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.2767400779140115</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.456044731334484</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.306256495870146</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.61563078910924</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.2640916311244998</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.430715643783748</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.324087722562695</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.543497613821359</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.2295046567707111</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.430715643783748</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.329821426801332</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.576075471757756</v>
+        <v>-8.472131221211711</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2522730623391358</v>
+        <v>-0.2106953621207173</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.3593492511741</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.304561828061122</v>
+        <v>2.362903999973255</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.482616437772531</v>
+        <v>-8.378672187226487</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2247729300579535</v>
+        <v>-0.183195229839535</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.3593492511741</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.294678346748215</v>
+        <v>2.353020518660347</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.407193204873073</v>
+        <v>-8.303248954327028</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1964381973975438</v>
+        <v>-0.1548604971791252</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.3593492511741</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.292843786248842</v>
+        <v>2.351185958160974</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.309286166196582</v>
+        <v>-8.205341915650537</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1575756969004085</v>
+        <v>-0.11599799668199</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.388600454500431</v>
+        <v>-1.291363501313544</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.333334921191714</v>
+        <v>2.391677093103847</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.285332625220624</v>
+        <v>-8.181388374674579</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1473257743645315</v>
+        <v>-0.105748074146113</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.364646913524473</v>
+        <v>-1.267409960337586</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.348375551922782</v>
+        <v>2.406717723834915</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.021272686897827</v>
+        <v>-7.917328436351784</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05496211519716487</v>
+        <v>-0.01338441497874676</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.00335002201479</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.493551198754708</v>
+        <v>2.551893370666841</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.314193063392989</v>
+        <v>-7.210248812846945</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2250827005444695</v>
+        <v>0.2666604007628877</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.00335002201479</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.490764165094407</v>
+        <v>2.54910633700654</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.274008765026799</v>
+        <v>-7.170064514480755</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2415000437787871</v>
+        <v>0.2830777439972052</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.060402676835486</v>
+        <v>-0.963165723648599</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.515218368001963</v>
+        <v>2.573560539914095</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.110608894087436</v>
+        <v>-7.006664643541392</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.306226813375289</v>
+        <v>0.3478045135937071</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8970028058961237</v>
+        <v>-0.7997658527092365</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.612625111786337</v>
+        <v>2.67096728369847</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.877127671857838</v>
+        <v>-6.773183421311794</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4075437311049805</v>
+        <v>0.4491214313233991</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6635215836665251</v>
+        <v>-0.566284630479638</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.760638273961949</v>
+        <v>2.818980445874081</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.727461280850322</v>
+        <v>-6.623517030304279</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4645180771950277</v>
+        <v>0.5060957774134458</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5706180924239892</v>
+        <v>-0.473381139237102</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.813488158394511</v>
+        <v>2.871830330306644</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.595185807219436</v>
+        <v>-6.491241556673392</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4186890526545368</v>
+        <v>0.4602667528729549</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4383426187931025</v>
+        <v>-0.3411056656062154</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.794114228580198</v>
+        <v>2.852456400492331</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.423324591654533</v>
+        <v>-6.31938034110849</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4902485995681345</v>
+        <v>0.5318262997865526</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2664814032281997</v>
+        <v>-0.1692444500413125</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.900046018606776</v>
+        <v>2.958388190518909</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.338359924925214</v>
+        <v>-6.23441567437917</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5371408074835209</v>
+        <v>0.5787185077019394</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1815167364988801</v>
+        <v>-0.08427978331199293</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.963931159868027</v>
+        <v>3.022273331780159</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.443949914698319</v>
+        <v>-6.340005664152274</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3669288819750607</v>
+        <v>0.4085065821934792</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2871067262719845</v>
+        <v>-0.1898697730850973</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.772601236404946</v>
+        <v>2.830943408317078</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.375715330072891</v>
+        <v>-6.271771079526847</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4427670577023179</v>
+        <v>0.4843447579207365</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2686914033994485</v>
+        <v>-0.1714544502125613</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.832194772005554</v>
+        <v>2.890536943917686</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.227775288665292</v>
+        <v>-6.123831038119247</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3853222656269506</v>
+        <v>0.4268999658453692</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2483704874908909</v>
+        <v>-0.1511335343040037</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.727766512912281</v>
+        <v>2.786108684824413</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.174805766411303</v>
+        <v>-6.070861515865259</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3977960882750677</v>
+        <v>0.4393737884934863</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.09816401205001485</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.750834240011196</v>
+        <v>2.809176411923329</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.009017570451013</v>
+        <v>-5.905073319904968</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4571507545640907</v>
+        <v>0.4987284547825097</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.09816401205001485</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.743873627916103</v>
+        <v>2.802215799828236</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.975654363972244</v>
+        <v>-5.871710113426199</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4849583915367415</v>
+        <v>0.52653609175516</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.09816401205001485</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.758335982297246</v>
+        <v>2.816678154209379</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.867395226849722</v>
+        <v>-5.763450976303678</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5227941668449452</v>
+        <v>0.5643718670633637</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.09816401205001485</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.752868102756441</v>
+        <v>2.811210274668574</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.744104092032591</v>
+        <v>-5.640159841486547</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5696087147823743</v>
+        <v>0.6111864150007928</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.07210983041977154</v>
+        <v>0.02512712276711565</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.824340877657296</v>
+        <v>2.882683049569429</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.6914072249013</v>
+        <v>-5.587462974355256</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5983884398722163</v>
+        <v>0.6399661400906349</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.01941296328848036</v>
+        <v>0.07782398989840683</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.863659976173396</v>
+        <v>2.922002148085529</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.447641782917856</v>
+        <v>-5.343697532371811</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6916753250126444</v>
+        <v>0.7332530252310629</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.01941296328848036</v>
+        <v>0.07782398989840683</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.859440684520447</v>
+        <v>2.917782856432579</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.357866110541384</v>
+        <v>-5.253921859995339</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7297099078832496</v>
+        <v>0.7712876081016682</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.1394234348127169</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.898524665389049</v>
+        <v>2.956866837301181</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.108015716592309</v>
+        <v>-5.004071466046264</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8223921404465813</v>
+        <v>0.863969840665</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.1394234348127169</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.891266740372751</v>
+        <v>2.949608912284883</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.932123624124877</v>
+        <v>-4.828179373578832</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8963481009542029</v>
+        <v>0.9379258011726215</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.1394234348127169</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.8948658638934</v>
+        <v>2.953208035805532</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.760677161102413</v>
+        <v>-4.656732910556369</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9782541922177421</v>
+        <v>1.019831892436161</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2136329446482928</v>
+        <v>0.31086989783518</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.011061247761432</v>
+        <v>3.069403419673564</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.680654873993292</v>
+        <v>-4.576710623447248</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.009283584677688</v>
+        <v>1.050861284896106</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2936552317574138</v>
+        <v>0.3908921849443009</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.058095097643201</v>
+        <v>3.116437269555333</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.617019131759358</v>
+        <v>-4.513074881213313</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.039432682625578</v>
+        <v>1.081010382843997</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3572909739913483</v>
+        <v>0.4545279271782355</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.100971344037879</v>
+        <v>3.159313515950011</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.523321813542963</v>
+        <v>-4.419377562996918</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.058105868695932</v>
+        <v>1.099683568914351</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3572909739913483</v>
+        <v>0.4545279271782355</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.082165602821675</v>
+        <v>3.140507774733807</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.533824436608252</v>
+        <v>-4.429880186062207</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.055647896094694</v>
+        <v>1.097225596313113</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3467883509260594</v>
+        <v>0.4440253041129466</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.077607105607379</v>
+        <v>3.135949277519511</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.421338175939377</v>
+        <v>-4.317393925393333</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.104571714197064</v>
+        <v>1.146149414415483</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3467883509260594</v>
+        <v>0.4440253041129466</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.081536419442199</v>
+        <v>3.139878591354331</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.403624489061512</v>
+        <v>-4.299680238515467</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.11233577286555</v>
+        <v>1.153913473083969</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3499696798229762</v>
+        <v>0.4472066330098634</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.084123800697689</v>
+        <v>3.142465972609821</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.280150217748494</v>
+        <v>-4.176205967202449</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.158723552610751</v>
+        <v>1.200301252829169</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3499696798229762</v>
+        <v>0.4472066330098634</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.081121871917682</v>
+        <v>3.139464043829815</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.060129419711483</v>
+        <v>-3.956185169165438</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.248310908836169</v>
+        <v>1.289888609054588</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4911895248909565</v>
+        <v>0.5884264780778437</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.167432815969085</v>
+        <v>3.225774987881217</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.927261730648205</v>
+        <v>-3.82331748010216</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.317352167263304</v>
+        <v>1.358929867481723</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4911895248909565</v>
+        <v>0.5884264780778437</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.183326998770908</v>
+        <v>3.241669170683041</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.807088647283706</v>
+        <v>-3.703144396737661</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.366567245049405</v>
+        <v>1.408144945267824</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6113626082554554</v>
+        <v>0.7085995614423426</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.256576693229909</v>
+        <v>3.314918865142042</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.671835285953729</v>
+        <v>-3.567891035407684</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.430756692142836</v>
+        <v>1.472334392361255</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7466159695854325</v>
+        <v>0.8438529227723197</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.347816812589335</v>
+        <v>3.406158984501467</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.731710113311421</v>
+        <v>-3.627765862765377</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.392844252601185</v>
+        <v>1.434421952819604</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6867411422277404</v>
+        <v>0.7839780954146276</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.297929407576146</v>
+        <v>3.356271579488278</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.611889882400584</v>
+        <v>-3.507945631854539</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.456061514199728</v>
+        <v>1.497639214418147</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6867411422277404</v>
+        <v>0.7839780954146276</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.313218576810355</v>
+        <v>3.371560748722487</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.61435958886239</v>
+        <v>-3.510415338316345</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.362717830937448</v>
+        <v>1.404295531155866</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6842714357659343</v>
+        <v>0.7815083889528214</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.219380952255712</v>
+        <v>3.277723124167845</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.6827297751864</v>
+        <v>-3.578785524640355</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.254631617893145</v>
+        <v>1.296209318111564</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.7907840879890363</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.144208233162743</v>
+        <v>3.202550405074875</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.79460205481255</v>
+        <v>-3.690657804266506</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.200319414674576</v>
+        <v>1.241897114892995</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.7907840879890363</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.134644941794634</v>
+        <v>3.192987113706766</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.778627389326283</v>
+        <v>-3.674683138780238</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.173283805793111</v>
+        <v>1.214861506011529</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.7907840879890363</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.101219466718661</v>
+        <v>3.159561638630794</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.603153129533813</v>
+        <v>-3.499208878987769</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.248040741701886</v>
+        <v>1.289618441920305</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.7907840879890363</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.105786698710449</v>
+        <v>3.164128870622581</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.595228754948899</v>
+        <v>-3.491284504402854</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.226952520297059</v>
+        <v>1.268530220515477</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.7907840879890363</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.081528727471656</v>
+        <v>3.139870899383788</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.58895055237905</v>
+        <v>-3.485006301833006</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.158002114726448</v>
+        <v>1.199579814944867</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.7970622905588853</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.013833962415015</v>
+        <v>3.072176134327147</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.529097933175327</v>
+        <v>-3.425153682629282</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.19211554884007</v>
+        <v>1.233693249058488</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.7970622905588853</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.024006348847148</v>
+        <v>3.08234852075928</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.44285447014895</v>
+        <v>-3.338910219602905</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.221559204624481</v>
+        <v>1.2631369048429</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.7970622905588853</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.018952619421008</v>
+        <v>3.077294791333141</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.488161289547929</v>
+        <v>-3.384217039001885</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.195212252309415</v>
+        <v>1.236789952527833</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6590151743627675</v>
+        <v>0.7562521275496545</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.986242297059995</v>
+        <v>3.044584468972127</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.517194394250231</v>
+        <v>-3.413250143704186</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.184150883461596</v>
+        <v>1.225728583680014</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6590151743627675</v>
+        <v>0.7562521275496545</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.986794170093097</v>
+        <v>3.045136342005229</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.424383912799372</v>
+        <v>-3.320439662253327</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.150547767933305</v>
+        <v>1.192125468151723</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7518256558136268</v>
+        <v>0.8490626090005139</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.971753150854978</v>
+        <v>3.03009532276711</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.468773382128799</v>
+        <v>-3.364829131582755</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.134665456126135</v>
+        <v>1.176243156344553</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7074361864841991</v>
+        <v>0.8046731396710862</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.946992945181922</v>
+        <v>3.005335117094055</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.448269688243302</v>
+        <v>-3.344325437697258</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.137942642192057</v>
+        <v>1.179520342410475</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7279398803696965</v>
+        <v>0.8251768335565836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.954370870024944</v>
+        <v>3.012713041937076</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.488193782825874</v>
+        <v>-3.38424953227983</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.127464300189695</v>
+        <v>1.169042000408114</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7279398803696965</v>
+        <v>0.8251768335565836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.959862165855611</v>
+        <v>3.018204337767743</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.515974180727227</v>
+        <v>-3.412029930181183</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.127849342797693</v>
+        <v>1.169427043016111</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7001594824683435</v>
+        <v>0.7973964356552306</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.954691128883338</v>
+        <v>3.01303330079547</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.634354853457366</v>
+        <v>-3.530410602911321</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9188527937062907</v>
+        <v>0.9604304939247092</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.7301785835042544</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.752716137593405</v>
+        <v>2.811058309505538</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.742968931900697</v>
+        <v>-3.639024681354652</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.995556823048164</v>
+        <v>1.037134523266583</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.7301785835042544</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.872865798312611</v>
+        <v>2.931207970224744</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.707559893652554</v>
+        <v>-3.603615643106509</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.024233464449744</v>
+        <v>1.065811164668163</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.7301785835042544</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.887378824414934</v>
+        <v>2.945720996327067</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.716021062308015</v>
+        <v>-3.612076811761971</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.018268438329928</v>
+        <v>1.059846138548347</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6244804616619062</v>
+        <v>0.7217174148487933</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.879721564564026</v>
+        <v>2.938063736476159</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.538904732272849</v>
+        <v>-3.434960481726804</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.085843999189297</v>
+        <v>1.127421699407716</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6244804616619062</v>
+        <v>0.7217174148487933</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.876450593409329</v>
+        <v>2.934792765321461</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.583996977106395</v>
+        <v>-3.48005272656035</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.068490493017792</v>
+        <v>1.11006819323621</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5625844184925164</v>
+        <v>0.6598213716794035</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.839996359269608</v>
+        <v>2.89833853118174</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.404621555867627</v>
+        <v>-3.300677305321583</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.134027636819713</v>
+        <v>1.175605337038132</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7193611766632351</v>
+        <v>0.8165981298501221</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.927849389478454</v>
+        <v>2.986191561390586</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.449635769388233</v>
+        <v>-3.345691518842189</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.096829406743061</v>
+        <v>1.138407106961479</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6890122813486305</v>
+        <v>0.7862492345355175</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.890447507621281</v>
+        <v>2.948789679533413</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.716640279660669</v>
+        <v>-3.612696029114624</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9957191649730321</v>
+        <v>1.037296865191451</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4946492433056819</v>
+        <v>0.591886196492569</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.779521247134457</v>
+        <v>2.837863419046589</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.817838061097842</v>
+        <v>-3.713893810551797</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9544439742946644</v>
+        <v>0.996021674513083</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4262404297603627</v>
+        <v>0.5234773829472499</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.737679880903767</v>
+        <v>2.796022052815899</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.811327094483529</v>
+        <v>-3.707382843937484</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9546483224947062</v>
+        <v>0.9962260227131248</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4262404297603627</v>
+        <v>0.5234773829472499</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.735279842458084</v>
+        <v>2.793622014370216</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.792288966776232</v>
+        <v>-3.688344716230187</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9587882927858702</v>
+        <v>1.000365993004289</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3680568184291682</v>
+        <v>0.4652937716160553</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.696894394867612</v>
+        <v>2.755236566779744</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.844804769051052</v>
+        <v>-3.740860518505007</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.057076373510133</v>
+        <v>1.098654073728551</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3680568184291682</v>
+        <v>0.4652937716160553</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.816188796501802</v>
+        <v>2.874530968413934</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.848213080485631</v>
+        <v>-3.744268829939587</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.056546377922434</v>
+        <v>1.098124078140853</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4005733874385456</v>
+        <v>0.4978103406254327</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.836532066893562</v>
+        <v>2.894874238805694</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.828856944591784</v>
+        <v>-3.72491269404574</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.070297362676899</v>
+        <v>1.111875062895317</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4005733874385456</v>
+        <v>0.4978103406254327</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.842540597290488</v>
+        <v>2.90088276920262</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.681113974356782</v>
+        <v>-3.577169723810738</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.027344772048099</v>
+        <v>1.068922472266518</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5683807446734288</v>
+        <v>0.6656176978603159</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.841175232908618</v>
+        <v>2.89951740482075</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.76493519563148</v>
+        <v>-3.660990945085436</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.996609905069701</v>
+        <v>1.03818760528812</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5683807446734288</v>
+        <v>0.6656176978603159</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.843968854440099</v>
+        <v>2.902311026352231</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.758782489578696</v>
+        <v>-3.654838239032651</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9997333358824732</v>
+        <v>1.041311036100892</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5745334507262131</v>
+        <v>0.6717704039131002</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.848322826463427</v>
+        <v>2.90666499837556</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.775591787729197</v>
+        <v>-3.671647537183153</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9920900933623829</v>
+        <v>1.033667793580801</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5577241525757115</v>
+        <v>0.6549611057625986</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.837317724313237</v>
+        <v>2.895659896225369</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.713293788953075</v>
+        <v>-3.609349538407031</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.083344846669652</v>
+        <v>1.124922546888071</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6030184168501536</v>
+        <v>0.7002553700370406</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.930829836674723</v>
+        <v>2.989172008586855</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.511503591287918</v>
+        <v>-3.407559340741873</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9663529274498426</v>
+        <v>1.007930627668261</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.801036609019308</v>
+        <v>0.898273562206195</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.851932753690343</v>
+        <v>2.910274925602475</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.562390303974112</v>
+        <v>-3.458446053428068</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.01628847469754</v>
+        <v>1.057866174915959</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7501498963331135</v>
+        <v>0.8473868495200005</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.891690958400801</v>
+        <v>2.950033130312933</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319539</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.475779561324305</v>
+        <v>-3.37183531077826</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.065560507873506</v>
+        <v>1.107138208091925</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8287756275382717</v>
+        <v>0.9260125807251588</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.95349413323994</v>
+        <v>3.011836305152072</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.535988859329589</v>
+        <v>-3.432044608783545</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.040012769496064</v>
+        <v>1.081590469714483</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7685663295329872</v>
+        <v>0.8658032827198743</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.915904535261441</v>
+        <v>2.974246707173573</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397788</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.486802210645238</v>
+        <v>-3.382857960099193</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.058179047009733</v>
+        <v>1.099756747228152</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7685663295329872</v>
+        <v>0.8658032827198743</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.914396153301369</v>
+        <v>2.972738325213502</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316243</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.442429079006669</v>
+        <v>-3.338484828460625</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.075791167100597</v>
+        <v>1.117368867319016</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8129394611715558</v>
+        <v>0.9101764143584429</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.940882899719947</v>
+        <v>2.999225071632079</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.464909429865554</v>
+        <v>-3.36096517931951</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.061192820895634</v>
+        <v>1.102770521114052</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8129394611715558</v>
+        <v>0.9101764143584429</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.935276693858537</v>
+        <v>2.993618865770669</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.417253699304498</v>
+        <v>-3.313309448758454</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.086636870147861</v>
+        <v>1.128214570366279</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8605951917326115</v>
+        <v>0.9578321449194985</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.970251889222975</v>
+        <v>3.028594061135108</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.316735540805744</v>
+        <v>-3.212791290259699</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.131736506922087</v>
+        <v>1.173314207140506</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.961113350231366</v>
+        <v>1.058350303418253</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.035455157696953</v>
+        <v>3.093797329609085</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.300830211373391</v>
+        <v>-3.196885960827347</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.124853311170901</v>
+        <v>1.166431011389319</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8820006895221271</v>
+        <v>0.9792376427090141</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.974742233747282</v>
+        <v>3.033084405659414</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.255991809764993</v>
+        <v>-3.152047559218949</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.146886374424888</v>
+        <v>1.188464074643307</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8865441224669965</v>
+        <v>0.9837810756538836</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.981565996124832</v>
+        <v>3.039908168036964</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.275490266007001</v>
+        <v>-3.171546015460957</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.143247931559163</v>
+        <v>1.184825631777582</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8384594811870922</v>
+        <v>0.9356964343739793</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.956876150987967</v>
+        <v>3.0152183229001</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.231287428921101</v>
+        <v>-3.127343178375056</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.166808668921361</v>
+        <v>1.208386369139779</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8826623182729927</v>
+        <v>0.9798992714598798</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.989277455767345</v>
+        <v>3.047619627679477</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.238847094758148</v>
+        <v>-3.134902844212103</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.162194803055789</v>
+        <v>1.203772503274208</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.937465722282812</v>
+        <v>1.034702675469699</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.020569498642484</v>
+        <v>3.078911670554616</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.080555677218876</v>
+        <v>-2.976611426672831</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.276759135254538</v>
+        <v>1.318336835472956</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.937465722282812</v>
+        <v>1.034702675469699</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.071817263825523</v>
+        <v>3.130159435737656</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.872913673584399</v>
+        <v>-2.768969423038355</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.358256641302581</v>
+        <v>1.399834341521</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.145107725917288</v>
+        <v>1.242344679104175</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.194843170600462</v>
+        <v>3.253185342512595</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.821881580861871</v>
+        <v>-2.717937330315827</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.373617706629863</v>
+        <v>1.415195406848281</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.196139818639816</v>
+        <v>1.293376771826703</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.220410654472249</v>
+        <v>3.278752826384381</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.756657399734666</v>
+        <v>-2.652713149188621</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.41689478317345</v>
+        <v>1.458472483391869</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.261363999767022</v>
+        <v>1.358600952953909</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.276732567241277</v>
+        <v>3.33507473915341</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.719230379663532</v>
+        <v>-2.615286129117487</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.427826563501184</v>
+        <v>1.469404263719602</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.266615537796203</v>
+        <v>1.363852490983091</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.275844462358067</v>
+        <v>3.334186634270199</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.73934203569824</v>
+        <v>-2.635397785152195</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.421038693418541</v>
+        <v>1.462616393636959</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.277642882793623</v>
+        <v>1.37487983598051</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.283717661687759</v>
+        <v>3.342059833599891</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.710928772598356</v>
+        <v>-2.606984522052312</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.592961769679705</v>
+        <v>1.634539469898123</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.218667320047194</v>
+        <v>1.315904273234081</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.408890095061112</v>
+        <v>3.467232266973244</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.636146511573344</v>
+        <v>-2.532202261027299</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.742987583307527</v>
+        <v>1.784565283525946</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.293449581072206</v>
+        <v>1.390686534259094</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.573872360893937</v>
+        <v>3.632214532806069</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.610062427309536</v>
+        <v>-2.506118176763491</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.745129193026909</v>
+        <v>1.786706893245328</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.293449581072206</v>
+        <v>1.390686534259094</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.565580336907796</v>
+        <v>3.623922508819928</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.522184514200415</v>
+        <v>-2.418240263654371</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.778473553854337</v>
+        <v>1.820051254072756</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.409375223495557</v>
+        <v>1.506612176682445</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.633328917945586</v>
+        <v>3.691671089857718</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.513292052807132</v>
+        <v>-2.409347802261087</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.799584944138442</v>
+        <v>1.841162644356861</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.409375223495557</v>
+        <v>1.506612176682445</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.650883323672377</v>
+        <v>3.709225495584509</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.68176816977701</v>
+        <v>-2.577823919230965</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.724049544755075</v>
+        <v>1.765627244973493</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.381427387778977</v>
+        <v>1.478664340965864</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.625969669647013</v>
+        <v>3.684311841559145</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.23551197714757</v>
+        <v>-2.131567726601525</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.883821718994712</v>
+        <v>1.925399419213131</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.286708718109344</v>
+        <v>1.383945671296231</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.550408165033095</v>
+        <v>3.608750336945227</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.212790873464417</v>
+        <v>-2.108846622918373</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.883574182964878</v>
+        <v>1.925151883183297</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.286708718109344</v>
+        <v>1.383945671296231</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.541072187529999</v>
+        <v>3.599414359442132</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.34199268675846</v>
+        <v>-2.238048436212415</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.99079958349843</v>
+        <v>2.032377283716849</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.157506904815302</v>
+        <v>1.254743858002189</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.622457225404743</v>
+        <v>3.680799397316876</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.367867085232485</v>
+        <v>-2.263922834686441</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.017527646602467</v>
+        <v>2.059105346820885</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.202418513527043</v>
+        <v>1.29965546671393</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.686482013125434</v>
+        <v>3.744824185037567</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.360812395017312</v>
+        <v>-2.256868144471267</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.017024878678081</v>
+        <v>2.0586025788965</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.209473203742217</v>
+        <v>1.306710156929104</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.687390183244084</v>
+        <v>3.745732355156216</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.333861170690824</v>
+        <v>-2.229916920144779</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.037811522053418</v>
+        <v>2.079389222271836</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.224353549769936</v>
+        <v>1.321590502956823</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.706324544505457</v>
+        <v>3.764666716417589</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.355405398521611</v>
+        <v>-2.251461147975566</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.213296963066063</v>
+        <v>2.254874663284481</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.224353549769936</v>
+        <v>1.321590502956823</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.890427676650417</v>
+        <v>3.948769848562549</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.377813516326483</v>
+        <v>-2.273869265780438</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.196450410847107</v>
+        <v>2.238028111065526</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.224353549769936</v>
+        <v>1.321590502956823</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.88254437155341</v>
+        <v>3.940886543465542</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.406037751904083</v>
+        <v>-2.302093501358039</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.187214716165704</v>
+        <v>2.228792416384123</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.242330302221244</v>
+        <v>1.339567255408132</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.895384422573832</v>
+        <v>3.953726594485965</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.415478677792613</v>
+        <v>-2.311534427246569</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.239692063532139</v>
+        <v>2.281269763750558</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.364757419764636</v>
+        <v>1.461994372951523</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.025094410821715</v>
+        <v>4.083436582733847</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.504355308961087</v>
+        <v>-2.400411058415043</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.207032505610051</v>
+        <v>2.248610205828469</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.275880788596162</v>
+        <v>1.373117741783049</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.974659526665931</v>
+        <v>4.033001698578063</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.580685286561993</v>
+        <v>-2.476741036015949</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.174612327463463</v>
+        <v>2.216190027681882</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.275880788596162</v>
+        <v>1.373117741783049</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.972771339559706</v>
+        <v>4.031113511471839</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887749</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.674349231239534</v>
+        <v>-2.57040498069349</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.131966979195309</v>
+        <v>2.173544679413728</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.182216843918621</v>
+        <v>1.279453797105508</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.911393202356043</v>
+        <v>3.969735374268176</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.83591765676679</v>
+        <v>-2.731973406220745</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.06577361919456</v>
+        <v>2.107351319412978</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.055433920120741</v>
+        <v>1.152670873307629</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.833757458287468</v>
+        <v>3.892099630199601</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.944218318636909</v>
+        <v>-2.840274068090864</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.03552676131243</v>
+        <v>2.077104461530849</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.055433920120741</v>
+        <v>1.152670873307629</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.846830865153387</v>
+        <v>3.905173037065519</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.962022290357653</v>
+        <v>-2.858078039811609</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.020410369407073</v>
+        <v>2.061988069625492</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9848992972155401</v>
+        <v>1.082136250402427</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.796515288193206</v>
+        <v>3.854857460105339</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.989923077467126</v>
+        <v>-2.885978826921082</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.007774095690285</v>
+        <v>2.049351795908704</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9503023730726053</v>
+        <v>1.047539326259493</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.774281174834448</v>
+        <v>3.83262334674658</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.11244918017002</v>
+        <v>-3.008504929623975</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.955528098586327</v>
+        <v>1.997105798804745</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8277762703697115</v>
+        <v>0.9250132235565989</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.69752995718991</v>
+        <v>3.755872129102042</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.342963676355609</v>
+        <v>-3.239019425809564</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.930028259702595</v>
+        <v>1.971605959921013</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5972617741841227</v>
+        <v>0.6944987273710101</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.625927219069061</v>
+        <v>3.684269390981193</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.691708761580053</v>
+        <v>-3.587764511034008</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.930841944614665</v>
+        <v>1.972419644833083</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.5857507734521123</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.700990165719569</v>
+        <v>3.759332337631701</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.845695179356193</v>
+        <v>-3.741750928810148</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.938227646649848</v>
+        <v>1.979805346868266</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.5857507734521123</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.769970434865209</v>
+        <v>3.828312606777341</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.050294614219202</v>
+        <v>-3.946350363673157</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.842439074824765</v>
+        <v>1.884016775043184</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.5857507734521123</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.756021636985329</v>
+        <v>3.814363808897462</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.302769768226926</v>
+        <v>-4.198825517680882</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.75331950227709</v>
+        <v>1.794897202495508</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.5857507734521123</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.767892126040743</v>
+        <v>3.826234297952876</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.595665524706338</v>
+        <v>-4.491721274160294</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.637371734204269</v>
+        <v>1.678949434422687</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.5857507734521123</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.769102660559687</v>
+        <v>3.827444832471819</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.782329652841146</v>
+        <v>-4.678385402295102</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.566827825177667</v>
+        <v>1.608405525396085</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.461774849440665</v>
+        <v>0.5590118026275525</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.757181020292272</v>
+        <v>3.815523192204405</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.928350339755109</v>
+        <v>-4.824406089209064</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.503497403148271</v>
+        <v>1.54507510336669</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4526917576468081</v>
+        <v>0.5499287108336954</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.746809017952148</v>
+        <v>3.80515118986428</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830323</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.020064348864693</v>
+        <v>-4.916120098318649</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.629015856203482</v>
+        <v>1.6705935564219</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4526917576468081</v>
+        <v>0.5499287108336954</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.909013074651192</v>
+        <v>3.967355246563324</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.051716007924663</v>
+        <v>-4.947771757378618</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.611201830543308</v>
+        <v>1.652779530761727</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4475233004023679</v>
+        <v>0.5447602535892553</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.900758638268342</v>
+        <v>3.959100810180474</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586814</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.133650826193546</v>
+        <v>-5.029706575647501</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.588657320804246</v>
+        <v>1.630235021022664</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4375885548152877</v>
+        <v>0.5348255080021751</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.905027208484585</v>
+        <v>3.963369380396718</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332685</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.235626948441953</v>
+        <v>-5.131682697895909</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.556792510360785</v>
+        <v>1.598370210579204</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3356124325668801</v>
+        <v>0.4328493857537675</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.852767173591443</v>
+        <v>3.911109345503576</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231801</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.125620664964732</v>
+        <v>-5.021676414418687</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.592947910995849</v>
+        <v>1.634525611214268</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3588170044841553</v>
+        <v>0.4560539576710427</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.858842803985983</v>
+        <v>3.917184975898116</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818516</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.982561089223806</v>
+        <v>-4.878616838677761</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.654421752014194</v>
+        <v>1.695999452232613</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3668304310741346</v>
+        <v>0.464067384261022</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.867900870661945</v>
+        <v>3.926243042574078</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051782</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.681114363751968</v>
+        <v>-4.577170113205923</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.782261325085465</v>
+        <v>1.823839025303884</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6682771565459719</v>
+        <v>0.7655141097328593</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.056029788827583</v>
+        <v>4.114371960739716</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.705704607987152</v>
+        <v>-4.601760357441107</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.773396405144102</v>
+        <v>1.814974105362521</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6682771565459719</v>
+        <v>0.7655141097328593</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.057000966580294</v>
+        <v>4.115343138492427</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.654666231980632</v>
+        <v>-4.550721981434587</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.794654659926466</v>
+        <v>1.836232360144884</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6682771565459719</v>
+        <v>0.7655141097328593</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.05784387096005</v>
+        <v>4.116186042872182</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.613526937114001</v>
+        <v>-4.509582686567956</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.830148476747264</v>
+        <v>1.871726176965682</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7094164514126027</v>
+        <v>0.8066534045994901</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.101565546754173</v>
+        <v>4.159907718666306</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700472</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.516892025095361</v>
+        <v>-4.412947774549316</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.684986437678654</v>
+        <v>1.726564137897073</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8060513634312426</v>
+        <v>0.90328831661813</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.975730490089292</v>
+        <v>4.034072662001424</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077634</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.647472759626203</v>
+        <v>-4.543528509080159</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.636256187940281</v>
+        <v>1.6778338881587</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6754706289004001</v>
+        <v>0.7727075820872875</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.900884093444751</v>
+        <v>3.959226265356883</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833451</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.482976425435242</v>
+        <v>-4.379032174889197</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.686481540692748</v>
+        <v>1.728059240911167</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.839966963091362</v>
+        <v>0.9372039162782494</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.98400871303541</v>
+        <v>4.042350884947543</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077623</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.405877823893369</v>
+        <v>-4.301933573347324</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.716508691745927</v>
+        <v>1.758086391964346</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.839966963091362</v>
+        <v>0.9372039162782494</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.98319642347184</v>
+        <v>4.041538595383972</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.416263018783258</v>
+        <v>-4.312318768237214</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.722223392915044</v>
+        <v>1.763801093133462</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8295817682014727</v>
+        <v>0.9268187213883601</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.986834085662979</v>
+        <v>4.045176257575111</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735275</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.434851177505483</v>
+        <v>-4.330906926959439</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.785625135202579</v>
+        <v>1.827202835420998</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8109936094792474</v>
+        <v>0.9082305626661347</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.046518196206069</v>
+        <v>4.104860368118201</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.435149724201519</v>
+        <v>-4.331205473655475</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.782374727342463</v>
+        <v>1.823952427560882</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8106950627832115</v>
+        <v>0.9079320159700988</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.043208079006746</v>
+        <v>4.101550250918878</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108851</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.334326590511091</v>
+        <v>-4.230382339965047</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.827234875758026</v>
+        <v>1.868812575976444</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8231592782675653</v>
+        <v>0.9203962314544526</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.05521750323675</v>
+        <v>4.113559675148882</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812146</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.143545229758685</v>
+        <v>-4.03960097921264</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.903676673537532</v>
+        <v>1.94525437375595</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.013940639019973</v>
+        <v>1.11117759220686</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.169815573166738</v>
+        <v>4.22815774507887</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.036581871909263</v>
+        <v>-3.932637621363218</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.926298862414897</v>
+        <v>1.967876562633315</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.072405246979774</v>
+        <v>1.169642200166662</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.184731183680215</v>
+        <v>4.243073355592347</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912979</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.981251284007501</v>
+        <v>-3.877307033461456</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.98339803418766</v>
+        <v>2.024975734406079</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.127735834881536</v>
+        <v>1.224972788068424</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.252896473033331</v>
+        <v>4.311238644945463</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539888</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.969197157094538</v>
+        <v>-3.865252906548494</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.981906252854283</v>
+        <v>2.023483953072701</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.139789961794499</v>
+        <v>1.237026914981386</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.253815517082546</v>
+        <v>4.312157688994678</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811003</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.01035227666276</v>
+        <v>-3.906408026116714</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.96732483521113</v>
+        <v>2.008902535429549</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.098634842226278</v>
+        <v>1.195871795413165</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.23100307552575</v>
+        <v>4.289345247437882</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.94230371397123</v>
+        <v>-3.838359463425185</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.007395286165625</v>
+        <v>2.048972986384044</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.166683404917808</v>
+        <v>1.263920358104695</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.28468323901855</v>
+        <v>4.343025410930682</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013421</v>
+        <v>3.645256780013428</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.17390410714073</v>
+        <v>-4.069959856594686</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.934957799071419</v>
+        <v>1.976535499289837</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.166683404917808</v>
+        <v>1.263920358104695</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.304885909192144</v>
+        <v>4.363228081104277</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.22395565266995</v>
+        <v>-4.120011402123906</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.898543416926613</v>
+        <v>1.940121117145031</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.166683404917808</v>
+        <v>1.263920358104695</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.288492145259026</v>
+        <v>4.346834317171158</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.399062485246395</v>
+        <v>-4.29511823470035</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.788752597489502</v>
+        <v>1.83033029770792</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.166683404917808</v>
+        <v>1.263920358104695</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.248744058852493</v>
+        <v>4.307086230764625</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.202962331815872</v>
+        <v>-4.099018081269827</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.874215277858651</v>
+        <v>1.915792978077069</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.362783558348331</v>
+        <v>1.460020511535218</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.373426769907747</v>
+        <v>4.431768941819879</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395084</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.049936939702588</v>
+        <v>-3.945992689156543</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.034596434276869</v>
+        <v>2.076174134495287</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.515808950461615</v>
+        <v>1.613045903648502</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.564413004748621</v>
+        <v>4.622755176660753</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791146</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.078244253575858</v>
+        <v>-3.974300003029813</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.210739733635854</v>
+        <v>2.252317433854272</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.515808950461615</v>
+        <v>1.613045903648502</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.751879229656914</v>
+        <v>4.810221401569046</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620432</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.24483747868938</v>
+        <v>-4.140893228143335</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.113505394944527</v>
+        <v>2.155083095162946</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.349215725348093</v>
+        <v>1.44645267853498</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.621326245942883</v>
+        <v>4.679668417855015</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.221801685327814</v>
+        <v>-4.11785743478177</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.126396114950871</v>
+        <v>2.16797381516929</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.349215725348093</v>
+        <v>1.44645267853498</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.625002648604601</v>
+        <v>4.683344820516733</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399466</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.192555704872118</v>
+        <v>-4.088611454326073</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.135712562256645</v>
+        <v>2.177290262475064</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.349215725348093</v>
+        <v>1.44645267853498</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.622620703728096</v>
+        <v>4.680962875640228</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.299481252749969</v>
+        <v>-4.195537002203924</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.09023558226314</v>
+        <v>2.131813282481558</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.242290177470241</v>
+        <v>1.339527130657129</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.555758614159021</v>
+        <v>4.614100786071153</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700997</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.444499811257217</v>
+        <v>-4.340555560711173</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.033656961003475</v>
+        <v>2.075234661221893</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.097271618962993</v>
+        <v>1.19450857214988</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.470176281197905</v>
+        <v>4.528518453110038</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687008</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.562841577041935</v>
+        <v>-4.45889732649589</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.086251493947341</v>
+        <v>2.127829194165759</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.107957657525883</v>
+        <v>1.20519461071277</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.576519143593393</v>
+        <v>4.634861315505525</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790798</v>
+        <v>3.714879051790804</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.614251999362643</v>
+        <v>-4.510307748816598</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.063473022144996</v>
+        <v>2.105050722363415</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.107957657525883</v>
+        <v>1.20519461071277</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.574304840719331</v>
+        <v>4.632647012631464</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437326</v>
+        <v>3.704757949437332</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.693671450570394</v>
+        <v>-4.58972720002435</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.031608369736185</v>
+        <v>2.073186069954604</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.107957657525883</v>
+        <v>1.20519461071277</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.574207968793621</v>
+        <v>4.632550140705753</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298392</v>
+        <v>3.736804952298399</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.789134448487612</v>
+        <v>-4.685190197941568</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.993417064127341</v>
+        <v>2.034994764345759</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.107957657525883</v>
+        <v>1.20519461071277</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.574201862351663</v>
+        <v>4.632544034263796</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217994</v>
+        <v>3.715372960218002</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.724758537636897</v>
+        <v>-4.620814287090853</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.017263825030238</v>
+        <v>2.058841525248656</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.172333568376598</v>
+        <v>1.269570521563485</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.610923805424703</v>
+        <v>4.669265977336836</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73608941335353</v>
+        <v>3.736089413353538</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.780127699769091</v>
+        <v>-4.676183449223046</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.000849977925086</v>
+        <v>2.042427678143505</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.172333568376598</v>
+        <v>1.269570521563485</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.61665762317243</v>
+        <v>4.674999795084562</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113273</v>
+        <v>3.736822870113281</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.825565479599918</v>
+        <v>-4.721621229053873</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.982213229335688</v>
+        <v>2.023790929554107</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.129488577698438</v>
+        <v>1.226725530885326</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.590488992108467</v>
+        <v>4.648831164020599</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113682</v>
+        <v>3.79027250011369</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.73735864545234</v>
+        <v>-4.633414394906295</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.037370355845038</v>
+        <v>2.078948056063457</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.129488577698438</v>
+        <v>1.226725530885326</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.610363384958785</v>
+        <v>4.668705556870917</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016435</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.631323650247031</v>
+        <v>-4.527379399700986</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.06348505445189</v>
+        <v>2.105062754670308</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.129488577698438</v>
+        <v>1.226725530885326</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.594064085483513</v>
+        <v>4.652406257395645</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307667</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.448111987113935</v>
+        <v>-4.344167736567891</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.139200669169173</v>
+        <v>2.180778369387592</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.129488577698438</v>
+        <v>1.226725530885326</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.596495034947559</v>
+        <v>4.654837206859691</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863548</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.376390540100084</v>
+        <v>-4.27244628955404</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.133680433822604</v>
+        <v>2.175258134041022</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.201210024712289</v>
+        <v>1.298446977899177</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.605319089003759</v>
+        <v>4.663661260915891</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394108</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.354017514492378</v>
+        <v>-4.250073263946334</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.089545389986858</v>
+        <v>2.131123090205276</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.212465775825191</v>
+        <v>1.309702729012078</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.558988285592672</v>
+        <v>4.617330457504804</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456724</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.387033810403123</v>
+        <v>-4.283089559857078</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.261537076507915</v>
+        <v>2.303114776726333</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.143028399158439</v>
+        <v>1.240265352345326</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.702524064477975</v>
+        <v>4.760866236390108</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883671</v>
+        <v>3.713762536883678</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.375506174753514</v>
+        <v>-4.27156192420747</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.258069356596007</v>
+        <v>2.299647056814426</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.202029057359802</v>
+        <v>1.299266010546689</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.729845685227042</v>
+        <v>4.788187857139174</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.71715069923629</v>
+        <v>3.717150699236299</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.472847676095883</v>
+        <v>-4.368903425549838</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.222800868580848</v>
+        <v>2.264378568799267</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.157608875194313</v>
+        <v>1.254845828381201</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.706861688449537</v>
+        <v>4.76520386036167</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427678</v>
+        <v>3.705201079427686</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.55870370543585</v>
+        <v>-4.454759454889805</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.1897095390377</v>
+        <v>2.231287239256118</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.115232805968178</v>
+        <v>1.212469759155065</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.682687129106695</v>
+        <v>4.741029301018827</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610377</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.567540502851969</v>
+        <v>-4.463596252305924</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.168594021891754</v>
+        <v>2.210171722110172</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.107790633326827</v>
+        <v>1.205027586513715</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.660641027342386</v>
+        <v>4.718983199254518</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667449</v>
+        <v>3.715544411667456</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.658923065417428</v>
+        <v>-4.554978814871383</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.14220550791062</v>
+        <v>2.183783208129038</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.071225748607483</v>
+        <v>1.16846270179437</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.648866607555829</v>
+        <v>4.707208779467962</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889185</v>
+        <v>3.673978374889192</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.647216347430422</v>
+        <v>-4.543272096884377</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.249016452929689</v>
+        <v>2.290594153148108</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.082932466594489</v>
+        <v>1.180169419781377</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.7580188961723</v>
+        <v>4.816361068084433</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940956</v>
+        <v>3.682476099409567</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.547552843346759</v>
+        <v>-4.443608592800715</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.291914193294559</v>
+        <v>2.333491893512978</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.146119549798176</v>
+        <v>1.243356502985063</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.798963484825917</v>
+        <v>4.857305656738049</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452567</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.557868941513111</v>
+        <v>-4.453924690967066</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.500692587306077</v>
+        <v>2.542270287524495</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.146119549798176</v>
+        <v>1.243356502985063</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.011868318103975</v>
+        <v>5.070210490016107</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762281</v>
+        <v>3.623960959762289</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.557774973495738</v>
+        <v>-4.453830722949694</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.499908841425116</v>
+        <v>2.541486541643534</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.146489411145494</v>
+        <v>1.243726364332381</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.011268901824455</v>
+        <v>5.069611073736588</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988012</v>
+        <v>3.633213467988019</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.564993797695583</v>
+        <v>-4.461049547149538</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.491253297689532</v>
+        <v>2.53283099790795</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.146489411145494</v>
+        <v>1.243726364332381</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.005500887768809</v>
+        <v>5.063843059680941</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740918</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.564045374577544</v>
+        <v>-4.4601011240315</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.491632666936747</v>
+        <v>2.533210367155165</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.146489411145494</v>
+        <v>1.243726364332381</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.005500887768809</v>
+        <v>5.063843059680941</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.721113832833169</v>
+        <v>-4.617169582287124</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.441532891615589</v>
+        <v>2.483110591834008</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.146489411145494</v>
+        <v>1.243726364332381</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.018228495749901</v>
+        <v>5.076570667662033</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.715121586044357</v>
+        <v>-4.611177335498312</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.445875788755502</v>
+        <v>2.48745348897392</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.146489411145494</v>
+        <v>1.243726364332381</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.020174494174289</v>
+        <v>5.078516666086421</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.626563624913589</v>
+        <v>-4.522619374367545</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.474953109225578</v>
+        <v>2.516530809443996</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.146489411145494</v>
+        <v>1.243726364332381</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.013828630192058</v>
+        <v>5.07217080210419</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383087</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.608804547410515</v>
+        <v>-4.504860296864471</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.481365417665803</v>
+        <v>2.522943117884221</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.146489411145494</v>
+        <v>1.243726364332381</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.013137307631053</v>
+        <v>5.071479479543186</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.509174396361447</v>
+        <v>-4.405230145815403</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.533999663994017</v>
+        <v>2.575577364212435</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.246119562194561</v>
+        <v>1.343356515381449</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.085697584169081</v>
+        <v>5.144039756081213</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455268</v>
+        <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.558573905050459</v>
+        <v>-4.454629654504414</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.703394126017139</v>
+        <v>2.744971826235557</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.256378395626306</v>
+        <v>1.353615348813193</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.281007149726854</v>
+        <v>5.339349321638987</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.904223362177633</v>
+        <v>3.913861647214537</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.706422052389424</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.558573905050459</v>
+        <v>-4.545025196181179</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.703394126017139</v>
+        <v>2.696002282667713</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.256378395626306</v>
+        <v>1.353615348813193</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.699485849375792</v>
+        <v>5.326537994741849</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240915.xlsx
+++ b/tame_output/ON/bt/strategyON_20240915.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>62.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-46.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>422.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-616.1%</t>
+          <t>-626.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>367.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-106.6%</t>
+          <t>-110.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.6%</t>
+          <t>-331.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-88.6%</t>
+          <t>-101.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>116.7%</t>
+          <t>113.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>106.5%</t>
+          <t>103.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>79.0%</t>
         </is>
       </c>
     </row>
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.132221752781266</v>
+        <v>-5.236166003327313</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.063433850502658</v>
+        <v>1.02185615028424</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3045040951281515</v>
+        <v>-0.4017410483150389</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.933976518852022</v>
+        <v>2.87563434693989</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.540810529961944</v>
+        <v>-5.644754780507992</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8987598836451465</v>
+        <v>0.857182183426727</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.7130928723088299</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.687584796558374</v>
+        <v>2.629242624646241</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.654570941984809</v>
+        <v>-5.758515192530857</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.848441151307461</v>
+        <v>0.806863451089042</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.7130928723088299</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.682770229029835</v>
+        <v>2.624428057117702</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.070962816271806</v>
+        <v>-6.174907066817855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6798784522015393</v>
+        <v>0.6383007519831203</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.7130928723088299</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.680764279638712</v>
+        <v>2.622422107726579</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.432136446088794</v>
+        <v>-6.536080696634842</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5456676909434233</v>
+        <v>0.5040899907250038</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.7130928723088299</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.691022970307391</v>
+        <v>2.632680798395258</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.775394965731813</v>
+        <v>-6.879339216277861</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4044638482319107</v>
+        <v>0.3628861480134917</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.7130928723088299</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.687122535453086</v>
+        <v>2.628780363540954</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.823597782974157</v>
+        <v>-6.927542033520205</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3835876413899744</v>
+        <v>0.3420099411715549</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.7130928723088299</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.685527455508087</v>
+        <v>2.627185283595955</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.990406442948519</v>
+        <v>-7.094350693494567</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3206431533294376</v>
+        <v>0.2790654531110186</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.7553761960219665</v>
+        <v>-0.852613149208854</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.663936437209413</v>
+        <v>2.605594265297281</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.177126151257822</v>
+        <v>-7.28107040180387</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2419289654713133</v>
+        <v>0.2003512652528943</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.7553761960219665</v>
+        <v>-0.852613149208854</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.65991013267501</v>
+        <v>2.601567960762878</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.560127540000453</v>
+        <v>-7.664071790546501</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.08862630865267684</v>
+        <v>0.04704860843425784</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.7553761960219665</v>
+        <v>-0.852613149208854</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.659808031353426</v>
+        <v>2.601465859441294</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.564613985201841</v>
+        <v>-7.66855823574789</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.0894032465435517</v>
+        <v>0.04782554632513225</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.7598626412233551</v>
+        <v>-0.8570995944102426</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.659687680204023</v>
+        <v>2.601345508291891</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737168</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.924144307705843</v>
+        <v>-8.028088558251891</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04905857915999867</v>
+        <v>-0.09063627937841856</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.7598626412233551</v>
+        <v>-0.8570995944102426</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.665037983502073</v>
+        <v>2.606695811589941</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.974493371160065</v>
+        <v>-8.078437621706113</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.06128218458451018</v>
+        <v>-0.1028598848029296</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8102117046775772</v>
+        <v>-0.9074486578644647</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.642744565386717</v>
+        <v>2.584402393474585</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.072112648581463</v>
+        <v>-8.176056899127509</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.09728814493130011</v>
+        <v>-0.1388658451497196</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9078309820989738</v>
+        <v>-1.005067935285861</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.587214749555649</v>
+        <v>2.528872577643516</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.126184148089822</v>
+        <v>-8.230128398635868</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1160231884130716</v>
+        <v>-0.1576008886314906</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.9619024816073333</v>
+        <v>-1.059139434794221</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.557665406172205</v>
+        <v>2.499323234260073</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.129759934181569</v>
+        <v>-8.233704184727616</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1119403057311281</v>
+        <v>-0.1535180059495476</v>
       </c>
       <c r="F1878" t="n">
-        <v>-0.9874314035238259</v>
+        <v>-1.084668356710713</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.547861250140952</v>
+        <v>2.489519078228819</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.163412772690043</v>
+        <v>-8.267357023236089</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1209188866500814</v>
+        <v>-0.1624965868685009</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.087844771440863</v>
+        <v>-1.185081724627751</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.492095783875166</v>
+        <v>2.433753611963033</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.3024988873089</v>
+        <v>-8.406443137854946</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1611816310042031</v>
+        <v>-0.2027593312226226</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.22693088605972</v>
+        <v>-1.324167839246607</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.424015816597272</v>
+        <v>2.36567364468514</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.477623304695443</v>
+        <v>-8.58156755524149</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2166761772113039</v>
+        <v>-0.2582538774297229</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.402055303446264</v>
+        <v>-1.499292256633151</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.333496386912863</v>
+        <v>2.275154215000731</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.712075398709933</v>
+        <v>-8.816019649255979</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3176761797186956</v>
+        <v>-0.359253879937115</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.402055303446264</v>
+        <v>-1.499292256633151</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.326277222011267</v>
+        <v>2.267935050099135</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.81645012973638</v>
+        <v>-8.920394380282426</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3660982629032503</v>
+        <v>-0.4076759631216698</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.50643003447271</v>
+        <v>-1.603666987659597</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.256980192621423</v>
+        <v>2.198638020709291</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.978963595434964</v>
+        <v>-9.08290784598101</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.429987859344128</v>
+        <v>-0.471565559562547</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.604063464891397</v>
+        <v>-1.701300418078284</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.199515924208768</v>
+        <v>2.141173752296635</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.105000388803253</v>
+        <v>-9.2089446393493</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4777088480623291</v>
+        <v>-0.5192865482807481</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.578811842081654</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.217360626523727</v>
+        <v>2.159018454611595</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.047928616907322</v>
+        <v>-9.151872867453369</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4508898036175557</v>
+        <v>-0.4924675038359752</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.578811842081654</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.221350962210129</v>
+        <v>2.163008790297996</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.189600458631443</v>
+        <v>-9.293544709177489</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5090337672059455</v>
+        <v>-0.550611467424365</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.578811842081654</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.219875735311387</v>
+        <v>2.161533563399254</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.140009614206608</v>
+        <v>-9.243953864752655</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4741440192711397</v>
+        <v>-0.5157217194895587</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.52922099765682</v>
+        <v>-1.626457950843708</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.26468365213116</v>
+        <v>2.206341480219027</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.991091279734752</v>
+        <v>-9.095035530280798</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4276278191290799</v>
+        <v>-0.4692055193474993</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.497971406921647</v>
+        <v>-1.595208360108535</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.27038227292558</v>
+        <v>2.212040101013448</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.765246127015342</v>
+        <v>-8.869190377561386</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.327710685005107</v>
+        <v>-0.3692883852235256</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.456044731334484</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.305117351314087</v>
+        <v>2.246775179401955</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.64066747067775</v>
+        <v>-8.744611721223794</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2767400779140115</v>
+        <v>-0.31831777813243</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.456044731334484</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.306256495870146</v>
+        <v>2.247914323958013</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.61563078910924</v>
+        <v>-8.719575039655284</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2640916311244998</v>
+        <v>-0.3056693313429184</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.430715643783748</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.324087722562695</v>
+        <v>2.265745550650562</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.543497613821359</v>
+        <v>-8.647441864367403</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2295046567707111</v>
+        <v>-0.2710823569891296</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.430715643783748</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.329821426801332</v>
+        <v>2.271479254889199</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.472131221211711</v>
+        <v>-8.576075471757756</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2106953621207173</v>
+        <v>-0.2522730623391358</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.3593492511741</v>
+        <v>-1.456586204360987</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.362903999973255</v>
+        <v>2.304561828061122</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.378672187226487</v>
+        <v>-8.482616437772531</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.183195229839535</v>
+        <v>-0.2247729300579535</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.3593492511741</v>
+        <v>-1.456586204360987</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.353020518660347</v>
+        <v>2.294678346748215</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436231</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.303248954327028</v>
+        <v>-8.4719632562191</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1548604971791252</v>
+        <v>-0.2223462179359545</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.3593492511741</v>
+        <v>-1.456586204360987</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.351185958160974</v>
+        <v>2.292843786248842</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.205341915650537</v>
+        <v>-8.374056217542609</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.11599799668199</v>
+        <v>-0.1834837174388193</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.291363501313544</v>
+        <v>-1.388600454500431</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.391677093103847</v>
+        <v>2.333334921191714</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097246</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.181388374674579</v>
+        <v>-8.350102676566651</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.105748074146113</v>
+        <v>-0.1732337949029423</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.267409960337586</v>
+        <v>-1.364646913524473</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.406717723834915</v>
+        <v>2.348375551922782</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.917328436351784</v>
+        <v>-8.086042738243854</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.01338441497874676</v>
+        <v>-0.08087013573557567</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.00335002201479</v>
+        <v>-1.100586975201677</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.551893370666841</v>
+        <v>2.493551198754708</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.210248812846945</v>
+        <v>-7.378963114739016</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2666604007628877</v>
+        <v>0.1991746800060588</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.00335002201479</v>
+        <v>-1.100586975201677</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.54910633700654</v>
+        <v>2.490764165094407</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.170064514480755</v>
+        <v>-7.338778816372826</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2830777439972052</v>
+        <v>0.2155920232403763</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.963165723648599</v>
+        <v>-1.060402676835486</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.573560539914095</v>
+        <v>2.515218368001963</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.006664643541392</v>
+        <v>-7.175378945433463</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3478045135937071</v>
+        <v>0.2803187928368782</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7997658527092365</v>
+        <v>-0.8970028058961237</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.67096728369847</v>
+        <v>2.612625111786337</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.773183421311794</v>
+        <v>-6.941897723203865</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4491214313233991</v>
+        <v>0.3816357105665698</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.566284630479638</v>
+        <v>-0.6635215836665251</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.818980445874081</v>
+        <v>2.760638273961949</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.623517030304279</v>
+        <v>-6.79223133219635</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.5060957774134458</v>
+        <v>0.4386100566566169</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.473381139237102</v>
+        <v>-0.5706180924239892</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.871830330306644</v>
+        <v>2.813488158394511</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.491241556673392</v>
+        <v>-6.659955858565463</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4602667528729549</v>
+        <v>0.392781032116126</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3411056656062154</v>
+        <v>-0.4383426187931025</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.852456400492331</v>
+        <v>2.794114228580198</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.31938034110849</v>
+        <v>-6.488094643000561</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5318262997865526</v>
+        <v>0.4643405790297237</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1692444500413125</v>
+        <v>-0.2664814032281997</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.958388190518909</v>
+        <v>2.900046018606776</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.23441567437917</v>
+        <v>-6.403129976271241</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5787185077019394</v>
+        <v>0.5112327869451101</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.08427978331199293</v>
+        <v>-0.1815167364988801</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.022273331780159</v>
+        <v>2.963931159868027</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.340005664152274</v>
+        <v>-6.508719966044346</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4085065821934792</v>
+        <v>0.3410208614366494</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1898697730850973</v>
+        <v>-0.2871067262719845</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.830943408317078</v>
+        <v>2.772601236404946</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.271771079526847</v>
+        <v>-6.440485381418918</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4843447579207365</v>
+        <v>0.4168590371639072</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1714544502125613</v>
+        <v>-0.2686914033994485</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.890536943917686</v>
+        <v>2.832194772005554</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.123831038119247</v>
+        <v>-6.292545340011319</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4268999658453692</v>
+        <v>0.3594142450885398</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1511335343040037</v>
+        <v>-0.2483704874908909</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.786108684824413</v>
+        <v>2.727766512912281</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.070861515865259</v>
+        <v>-6.239575817757331</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4393737884934863</v>
+        <v>0.3718880677366569</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.09816401205001485</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.809176411923329</v>
+        <v>2.750834240011196</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.905073319904968</v>
+        <v>-6.07378762179704</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4987284547825097</v>
+        <v>0.4312427340256799</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.09816401205001485</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.802215799828236</v>
+        <v>2.743873627916103</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.871710113426199</v>
+        <v>-6.040424415318271</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.52653609175516</v>
+        <v>0.4590503709983307</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.09816401205001485</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.816678154209379</v>
+        <v>2.758335982297246</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.763450976303678</v>
+        <v>-5.932165278195749</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5643718670633637</v>
+        <v>0.4968861463065344</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.09816401205001485</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.811210274668574</v>
+        <v>2.752868102756441</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.640159841486547</v>
+        <v>-5.808874143378619</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6111864150007928</v>
+        <v>0.5437006942439635</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.02512712276711565</v>
+        <v>-0.07210983041977154</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.882683049569429</v>
+        <v>2.824340877657296</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.587462974355256</v>
+        <v>-5.756177276247327</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6399661400906349</v>
+        <v>0.5724804193338051</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.07782398989840683</v>
+        <v>-0.01941296328848036</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.922002148085529</v>
+        <v>2.863659976173396</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.343697532371811</v>
+        <v>-5.512411834263883</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7332530252310629</v>
+        <v>0.6657673044742336</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.07782398989840683</v>
+        <v>-0.01941296328848036</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.917782856432579</v>
+        <v>2.859440684520447</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.253921859995339</v>
+        <v>-5.422636161887411</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7712876081016682</v>
+        <v>0.7038018873448384</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1394234348127169</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.956866837301181</v>
+        <v>2.898524665389049</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.004071466046264</v>
+        <v>-5.172785767938336</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.863969840665</v>
+        <v>0.7964841199081705</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1394234348127169</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.949608912284883</v>
+        <v>2.891266740372751</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.828179373578832</v>
+        <v>-4.996893675470904</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9379258011726215</v>
+        <v>0.8704400804157921</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1394234348127169</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.953208035805532</v>
+        <v>2.8948658638934</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.656732910556369</v>
+        <v>-4.825447212448441</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.019831892436161</v>
+        <v>0.9523461716793311</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.31086989783518</v>
+        <v>0.2136329446482928</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.069403419673564</v>
+        <v>3.011061247761432</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.576710623447248</v>
+        <v>-4.74542492533932</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.050861284896106</v>
+        <v>0.9833755641392765</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3908921849443009</v>
+        <v>0.2936552317574138</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.116437269555333</v>
+        <v>3.058095097643201</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.513074881213313</v>
+        <v>-4.681789183105385</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.081010382843997</v>
+        <v>1.013524662087168</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4545279271782355</v>
+        <v>0.3572909739913483</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.159313515950011</v>
+        <v>3.100971344037879</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.419377562996918</v>
+        <v>-4.58809186488899</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.099683568914351</v>
+        <v>1.032197848157521</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4545279271782355</v>
+        <v>0.3572909739913483</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.140507774733807</v>
+        <v>3.082165602821675</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.429880186062207</v>
+        <v>-4.538130884326367</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.097225596313113</v>
+        <v>1.053925317007448</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4440253041129466</v>
+        <v>0.4072519545539708</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.135949277519511</v>
+        <v>3.113885267784125</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.317393925393333</v>
+        <v>-4.425644623657492</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.146149414415483</v>
+        <v>1.102849135109818</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4440253041129466</v>
+        <v>0.4072519545539708</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.139878591354331</v>
+        <v>3.117814581618946</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.299680238515467</v>
+        <v>-4.407930936779627</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.153913473083969</v>
+        <v>1.110613193778304</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4472066330098634</v>
+        <v>0.4104332834508876</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.142465972609821</v>
+        <v>3.120401962874435</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.176205967202449</v>
+        <v>-4.284456665466609</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.200301252829169</v>
+        <v>1.157000973523505</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4472066330098634</v>
+        <v>0.4104332834508876</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.139464043829815</v>
+        <v>3.117400034094429</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.956185169165438</v>
+        <v>-4.064435867429598</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.289888609054588</v>
+        <v>1.246588329748923</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5884264780778437</v>
+        <v>0.5516531285188678</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.225774987881217</v>
+        <v>3.203710978145832</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.82331748010216</v>
+        <v>-3.93156817836632</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.358929867481723</v>
+        <v>1.315629588176058</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5884264780778437</v>
+        <v>0.5516531285188678</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.241669170683041</v>
+        <v>3.219605160947655</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.703144396737661</v>
+        <v>-3.811395095001821</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.408144945267824</v>
+        <v>1.364844665962159</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7085995614423426</v>
+        <v>0.6718262118833668</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.314918865142042</v>
+        <v>3.292854855406656</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.567891035407684</v>
+        <v>-3.676141733671844</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.472334392361255</v>
+        <v>1.42903411305559</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8438529227723197</v>
+        <v>0.8070795732133439</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.406158984501467</v>
+        <v>3.384094974766082</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.627765862765377</v>
+        <v>-3.736016561029536</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.434421952819604</v>
+        <v>1.391121673513939</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7839780954146276</v>
+        <v>0.7472047458556518</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.356271579488278</v>
+        <v>3.334207569752893</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.507945631854539</v>
+        <v>-3.616196330118699</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.497639214418147</v>
+        <v>1.454338935112482</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7839780954146276</v>
+        <v>0.7472047458556518</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.371560748722487</v>
+        <v>3.349496738987101</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.510415338316345</v>
+        <v>-3.618666036580505</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.404295531155866</v>
+        <v>1.360995251850202</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7815083889528214</v>
+        <v>0.7447350393938457</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.277723124167845</v>
+        <v>3.255659114432459</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.578785524640355</v>
+        <v>-3.687036222904514</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.296209318111564</v>
+        <v>1.252909038805899</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7907840879890363</v>
+        <v>0.7540107384300606</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.202550405074875</v>
+        <v>3.18048639533949</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.690657804266506</v>
+        <v>-3.798908502530665</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.241897114892995</v>
+        <v>1.19859683558733</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7907840879890363</v>
+        <v>0.7540107384300606</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.192987113706766</v>
+        <v>3.170923103971381</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.674683138780238</v>
+        <v>-3.782933837044397</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.214861506011529</v>
+        <v>1.171561226705865</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7907840879890363</v>
+        <v>0.7540107384300606</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.159561638630794</v>
+        <v>3.137497628895408</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.499208878987769</v>
+        <v>-3.607459577251928</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.289618441920305</v>
+        <v>1.24631816261464</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7907840879890363</v>
+        <v>0.7540107384300606</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.164128870622581</v>
+        <v>3.142064860887196</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.491284504402854</v>
+        <v>-3.599535202667014</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.268530220515477</v>
+        <v>1.225229941209813</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7907840879890363</v>
+        <v>0.7540107384300606</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.139870899383788</v>
+        <v>3.117806889648403</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.485006301833006</v>
+        <v>-3.593257000097165</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.199579814944867</v>
+        <v>1.156279535639202</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7970622905588853</v>
+        <v>0.7602889409999096</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.072176134327147</v>
+        <v>3.050112124591762</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.425153682629282</v>
+        <v>-3.533404380893442</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.233693249058488</v>
+        <v>1.190392969752824</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7970622905588853</v>
+        <v>0.7602889409999096</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.08234852075928</v>
+        <v>3.060284511023895</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.338910219602905</v>
+        <v>-3.447160917867064</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.2631369048429</v>
+        <v>1.219836625537235</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7970622905588853</v>
+        <v>0.7602889409999096</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.077294791333141</v>
+        <v>3.055230781597755</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.384217039001885</v>
+        <v>-3.492467737266044</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.236789952527833</v>
+        <v>1.193489673222169</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7562521275496545</v>
+        <v>0.7194787779906788</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.044584468972127</v>
+        <v>3.022520459236742</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.413250143704186</v>
+        <v>-3.521500841968346</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.225728583680014</v>
+        <v>1.18242830437435</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7562521275496545</v>
+        <v>0.7194787779906788</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.045136342005229</v>
+        <v>3.023072332269844</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.320439662253327</v>
+        <v>-3.428690360517487</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.192125468151723</v>
+        <v>1.148825188846059</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8490626090005139</v>
+        <v>0.8122892594415382</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.03009532276711</v>
+        <v>3.008031313031725</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.364829131582755</v>
+        <v>-3.473079829846914</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.176243156344553</v>
+        <v>1.132942877038889</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8046731396710862</v>
+        <v>0.7678997901121105</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.005335117094055</v>
+        <v>2.983271107358669</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.344325437697258</v>
+        <v>-3.452576135961417</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.179520342410475</v>
+        <v>1.136220063104811</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.8251768335565836</v>
+        <v>0.7884034839976078</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.012713041937076</v>
+        <v>2.990649032201691</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.38424953227983</v>
+        <v>-3.492500230543989</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.169042000408114</v>
+        <v>1.125741721102449</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.8251768335565836</v>
+        <v>0.7884034839976078</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.018204337767743</v>
+        <v>2.996140328032358</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.412029930181183</v>
+        <v>-3.520280628445342</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.169427043016111</v>
+        <v>1.126126763710447</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7973964356552306</v>
+        <v>0.7606230860962548</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.01303330079547</v>
+        <v>2.990969291060085</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.530410602911321</v>
+        <v>-3.63866130117548</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9604304939247092</v>
+        <v>0.917130214619045</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7301785835042544</v>
+        <v>0.6934052339452786</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.811058309505538</v>
+        <v>2.788994299770152</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.639024681354652</v>
+        <v>-3.747275379618812</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.037134523266583</v>
+        <v>0.993834243960918</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7301785835042544</v>
+        <v>0.6934052339452786</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.931207970224744</v>
+        <v>2.909143960489358</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.603615643106509</v>
+        <v>-3.711866341370669</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.065811164668163</v>
+        <v>1.022510885362498</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7301785835042544</v>
+        <v>0.6934052339452786</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.945720996327067</v>
+        <v>2.923656986591681</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.612076811761971</v>
+        <v>-3.72032751002613</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.059846138548347</v>
+        <v>1.016545859242682</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7217174148487933</v>
+        <v>0.6849440652898175</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.938063736476159</v>
+        <v>2.915999726740773</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.434960481726804</v>
+        <v>-3.543211179990964</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.127421699407716</v>
+        <v>1.084121420102051</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7217174148487933</v>
+        <v>0.6849440652898175</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.934792765321461</v>
+        <v>2.912728755586075</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.48005272656035</v>
+        <v>-3.58830342482451</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.11006819323621</v>
+        <v>1.066767913930546</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6598213716794035</v>
+        <v>0.6230480221204278</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.89833853118174</v>
+        <v>2.876274521446355</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.300677305321583</v>
+        <v>-3.408928003585742</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.175605337038132</v>
+        <v>1.132305057732467</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8165981298501221</v>
+        <v>0.7798247802911464</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.986191561390586</v>
+        <v>2.9641275516552</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.345691518842189</v>
+        <v>-3.453942217106348</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.138407106961479</v>
+        <v>1.095106827655815</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7862492345355175</v>
+        <v>0.7494758849765418</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.948789679533413</v>
+        <v>2.926725669798027</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.612696029114624</v>
+        <v>-3.720946727378784</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.037296865191451</v>
+        <v>0.9939965858857862</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.591886196492569</v>
+        <v>0.5551128469335933</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.837863419046589</v>
+        <v>2.815799409311204</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.713893810551797</v>
+        <v>-3.822144508815956</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.996021674513083</v>
+        <v>0.9527213952074187</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5234773829472499</v>
+        <v>0.4867040333882741</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.796022052815899</v>
+        <v>2.773958043080514</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.707382843937484</v>
+        <v>-3.815633542201644</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9962260227131248</v>
+        <v>0.9529257434074605</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5234773829472499</v>
+        <v>0.4867040333882741</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.793622014370216</v>
+        <v>2.77155800463483</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.688344716230187</v>
+        <v>-3.796595414494346</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.000365993004289</v>
+        <v>0.9570657136986243</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4652937716160553</v>
+        <v>0.4285204220570796</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.755236566779744</v>
+        <v>2.733172557044359</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.740860518505007</v>
+        <v>-3.849111216769166</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.098654073728551</v>
+        <v>1.055353794422887</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4652937716160553</v>
+        <v>0.4285204220570796</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.874530968413934</v>
+        <v>2.852466958678549</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.744268829939587</v>
+        <v>-3.852519528203746</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.098124078140853</v>
+        <v>1.054823798835188</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4978103406254327</v>
+        <v>0.461036991066457</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.894874238805694</v>
+        <v>2.872810229070309</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.72491269404574</v>
+        <v>-3.833163392309899</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.111875062895317</v>
+        <v>1.068574783589653</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4978103406254327</v>
+        <v>0.461036991066457</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.90088276920262</v>
+        <v>2.878818759467235</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.577169723810738</v>
+        <v>-3.685420422074897</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.068922472266518</v>
+        <v>1.025622192960853</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6656176978603159</v>
+        <v>0.6288443483013402</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.89951740482075</v>
+        <v>2.877453395085364</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.660990945085436</v>
+        <v>-3.769241643349595</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.03818760528812</v>
+        <v>0.9948873259824551</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6656176978603159</v>
+        <v>0.6288443483013402</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.902311026352231</v>
+        <v>2.880247016616845</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.654838239032651</v>
+        <v>-3.763088937296811</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.041311036100892</v>
+        <v>0.9980107567952272</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6717704039131002</v>
+        <v>0.6349970543541245</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.90666499837556</v>
+        <v>2.884600988640174</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.671647537183153</v>
+        <v>-3.779898235447312</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.033667793580801</v>
+        <v>0.9903675142751369</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6549611057625986</v>
+        <v>0.6181877562036229</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.895659896225369</v>
+        <v>2.873595886489984</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.609349538407031</v>
+        <v>-3.71760023667119</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.124922546888071</v>
+        <v>1.081622267582407</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7002553700370406</v>
+        <v>0.6634820204780649</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.989172008586855</v>
+        <v>2.96710799885147</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.407559340741873</v>
+        <v>-3.515810039006032</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.007930627668261</v>
+        <v>0.9646303483625966</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.898273562206195</v>
+        <v>0.8615002126472193</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.910274925602475</v>
+        <v>2.88821091586709</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.458446053428068</v>
+        <v>-3.566696751692227</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.057866174915959</v>
+        <v>1.014565895610294</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8473868495200005</v>
+        <v>0.8106134999610248</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.950033130312933</v>
+        <v>2.927969120577548</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319539</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.37183531077826</v>
+        <v>-3.48008600904242</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.107138208091925</v>
+        <v>1.063837928786261</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9260125807251588</v>
+        <v>0.8892392311661831</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.011836305152072</v>
+        <v>2.989772295416687</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.432044608783545</v>
+        <v>-3.540295307047704</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.081590469714483</v>
+        <v>1.038290190408818</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8658032827198743</v>
+        <v>0.8290299331608986</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.974246707173573</v>
+        <v>2.952182697438188</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397788</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.382857960099193</v>
+        <v>-3.491108658363353</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.099756747228152</v>
+        <v>1.056456467922488</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8658032827198743</v>
+        <v>0.8290299331608986</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.972738325213502</v>
+        <v>2.950674315478116</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316243</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.338484828460625</v>
+        <v>-3.446735526724784</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.117368867319016</v>
+        <v>1.074068588013351</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9101764143584429</v>
+        <v>0.8734030647994672</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.999225071632079</v>
+        <v>2.977161061896694</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.36096517931951</v>
+        <v>-3.469215877583669</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.102770521114052</v>
+        <v>1.059470241808388</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9101764143584429</v>
+        <v>0.8734030647994672</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.993618865770669</v>
+        <v>2.971554856035284</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.313309448758454</v>
+        <v>-3.421560147022613</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.128214570366279</v>
+        <v>1.084914291060615</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9578321449194985</v>
+        <v>0.9210587953605228</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.028594061135108</v>
+        <v>3.006530051399722</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.212791290259699</v>
+        <v>-3.321041988523858</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.173314207140506</v>
+        <v>1.130013927834842</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.058350303418253</v>
+        <v>1.021576953859277</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.093797329609085</v>
+        <v>3.0717333198737</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.196885960827347</v>
+        <v>-3.305136659091506</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.166431011389319</v>
+        <v>1.123130732083655</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9792376427090141</v>
+        <v>0.9424642931500384</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.033084405659414</v>
+        <v>3.011020395924028</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.152047559218949</v>
+        <v>-3.260298257483108</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.188464074643307</v>
+        <v>1.145163795337643</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9837810756538836</v>
+        <v>0.9470077260949079</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.039908168036964</v>
+        <v>3.017844158301579</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.171546015460957</v>
+        <v>-3.279796713725116</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.184825631777582</v>
+        <v>1.141525352471917</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9356964343739793</v>
+        <v>0.8989230848150036</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.0152183229001</v>
+        <v>2.993154313164714</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.127343178375056</v>
+        <v>-3.235593876639216</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.208386369139779</v>
+        <v>1.165086089834115</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9798992714598798</v>
+        <v>0.9431259219009041</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.047619627679477</v>
+        <v>3.025555617944092</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.134902844212103</v>
+        <v>-3.243153542476263</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.203772503274208</v>
+        <v>1.160472223968543</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.034702675469699</v>
+        <v>0.9979293259107234</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.078911670554616</v>
+        <v>3.056847660819231</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.976611426672831</v>
+        <v>-3.08486212493699</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.318336835472956</v>
+        <v>1.275036556167292</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.034702675469699</v>
+        <v>0.9979293259107234</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.130159435737656</v>
+        <v>3.10809542600227</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.768969423038355</v>
+        <v>-2.877220121302514</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.399834341521</v>
+        <v>1.356534062215336</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.242344679104175</v>
+        <v>1.2055713295452</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.253185342512595</v>
+        <v>3.231121332777209</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.717937330315827</v>
+        <v>-2.826188028579986</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.415195406848281</v>
+        <v>1.371895127542617</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.293376771826703</v>
+        <v>1.256603422267728</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.278752826384381</v>
+        <v>3.256688816648996</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.652713149188621</v>
+        <v>-2.76096384745278</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.458472483391869</v>
+        <v>1.415172204086204</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.358600952953909</v>
+        <v>1.321827603394933</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.33507473915341</v>
+        <v>3.313010729418024</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.615286129117487</v>
+        <v>-2.723536827381646</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.469404263719602</v>
+        <v>1.426103984413938</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.363852490983091</v>
+        <v>1.327079141424115</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.334186634270199</v>
+        <v>3.312122624534814</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.635397785152195</v>
+        <v>-2.743648483416355</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.462616393636959</v>
+        <v>1.419316114331295</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.37487983598051</v>
+        <v>1.338106486421534</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.342059833599891</v>
+        <v>3.319995823864506</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.606984522052312</v>
+        <v>-2.715235220316471</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.634539469898123</v>
+        <v>1.591239190592459</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.315904273234081</v>
+        <v>1.279130923675105</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.467232266973244</v>
+        <v>3.445168257237859</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.532202261027299</v>
+        <v>-2.640452959291459</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.784565283525946</v>
+        <v>1.741265004220282</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.390686534259094</v>
+        <v>1.353913184700118</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.632214532806069</v>
+        <v>3.610150523070684</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.506118176763491</v>
+        <v>-2.614368875027651</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.786706893245328</v>
+        <v>1.743406613939664</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.390686534259094</v>
+        <v>1.353913184700118</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.623922508819928</v>
+        <v>3.601858499084543</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.418240263654371</v>
+        <v>-2.52649096191853</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.820051254072756</v>
+        <v>1.776750974767091</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.506612176682445</v>
+        <v>1.469838827123469</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.691671089857718</v>
+        <v>3.669607080122333</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.409347802261087</v>
+        <v>-2.517598500525247</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.841162644356861</v>
+        <v>1.797862365051196</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.506612176682445</v>
+        <v>1.469838827123469</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.709225495584509</v>
+        <v>3.687161485849124</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.577823919230965</v>
+        <v>-2.686074617495124</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.765627244973493</v>
+        <v>1.722326965667829</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.478664340965864</v>
+        <v>1.441890991406888</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.684311841559145</v>
+        <v>3.66224783182376</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.131567726601525</v>
+        <v>-2.239818424865684</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.925399419213131</v>
+        <v>1.882099139907467</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.383945671296231</v>
+        <v>1.347172321737256</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.608750336945227</v>
+        <v>3.586686327209842</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.108846622918373</v>
+        <v>-2.217097321182532</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.925151883183297</v>
+        <v>1.881851603877632</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.383945671296231</v>
+        <v>1.347172321737256</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.599414359442132</v>
+        <v>3.577350349706746</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.238048436212415</v>
+        <v>-2.346299134476574</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.032377283716849</v>
+        <v>1.989077004411184</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.254743858002189</v>
+        <v>1.217970508443213</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.680799397316876</v>
+        <v>3.65873538758149</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.263922834686441</v>
+        <v>-2.3721735329506</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.059105346820885</v>
+        <v>2.01580506751522</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.29965546671393</v>
+        <v>1.262882117154954</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.744824185037567</v>
+        <v>3.722760175302181</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.256868144471267</v>
+        <v>-2.365118842735427</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.0586025788965</v>
+        <v>2.015302299590835</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.306710156929104</v>
+        <v>1.269936807370128</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.745732355156216</v>
+        <v>3.723668345420831</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.229916920144779</v>
+        <v>-2.338167618408939</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.079389222271836</v>
+        <v>2.036088942966172</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.321590502956823</v>
+        <v>1.284817153397847</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.764666716417589</v>
+        <v>3.742602706682204</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.251461147975566</v>
+        <v>-2.359711846239726</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.254874663284481</v>
+        <v>2.211574383978817</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.321590502956823</v>
+        <v>1.284817153397847</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.948769848562549</v>
+        <v>3.926705838827163</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.273869265780438</v>
+        <v>-2.382119964044598</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.238028111065526</v>
+        <v>2.194727831759861</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.321590502956823</v>
+        <v>1.284817153397847</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.940886543465542</v>
+        <v>3.918822533730157</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.302093501358039</v>
+        <v>-2.410344199622198</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.228792416384123</v>
+        <v>2.185492137078458</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.339567255408132</v>
+        <v>1.302793905849156</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.953726594485965</v>
+        <v>3.93166258475058</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.311534427246569</v>
+        <v>-2.419785125510728</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.281269763750558</v>
+        <v>2.237969484444894</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.461994372951523</v>
+        <v>1.425221023392548</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.083436582733847</v>
+        <v>4.061372572998462</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.400411058415043</v>
+        <v>-2.508661756679202</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.248610205828469</v>
+        <v>2.205309926522805</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.373117741783049</v>
+        <v>1.336344392224074</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.033001698578063</v>
+        <v>4.010937688842678</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.476741036015949</v>
+        <v>-2.584991734280108</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.216190027681882</v>
+        <v>2.172889748376218</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.373117741783049</v>
+        <v>1.336344392224074</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.031113511471839</v>
+        <v>4.009049501736453</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887749</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.57040498069349</v>
+        <v>-2.678655678957649</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.173544679413728</v>
+        <v>2.130244400108063</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.279453797105508</v>
+        <v>1.242680447546532</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.969735374268176</v>
+        <v>3.94767136453279</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.731973406220745</v>
+        <v>-2.840224104484904</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.107351319412978</v>
+        <v>2.064051040107314</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.152670873307629</v>
+        <v>1.115897523748653</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.892099630199601</v>
+        <v>3.870035620464215</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389351</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.840274068090864</v>
+        <v>-2.948524766355024</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.077104461530849</v>
+        <v>2.033804182225184</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.152670873307629</v>
+        <v>1.115897523748653</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.905173037065519</v>
+        <v>3.883109027330134</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.858078039811609</v>
+        <v>-2.966328738075768</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.061988069625492</v>
+        <v>2.018687790319827</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.082136250402427</v>
+        <v>1.045362900843452</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.854857460105339</v>
+        <v>3.832793450369953</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.885978826921082</v>
+        <v>-2.994229525185241</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.049351795908704</v>
+        <v>2.00605151660304</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.047539326259493</v>
+        <v>1.010765976700517</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.83262334674658</v>
+        <v>3.810559337011195</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.008504929623975</v>
+        <v>-3.116755627888135</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.997105798804745</v>
+        <v>1.953805519499081</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9250132235565989</v>
+        <v>0.8882398739976232</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.755872129102042</v>
+        <v>3.733808119366657</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.239019425809564</v>
+        <v>-3.347270124073724</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.971605959921013</v>
+        <v>1.928305680615349</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6944987273710101</v>
+        <v>0.6577253778120344</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.684269390981193</v>
+        <v>3.662205381245808</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.587764511034008</v>
+        <v>-3.696015209298167</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.972419644833083</v>
+        <v>1.929119365527419</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5857507734521123</v>
+        <v>0.5489774238931366</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.759332337631701</v>
+        <v>3.737268327896316</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.741750928810148</v>
+        <v>-3.850001627074308</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.979805346868266</v>
+        <v>1.936505067562602</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5857507734521123</v>
+        <v>0.5489774238931366</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.828312606777341</v>
+        <v>3.806248597041956</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.946350363673157</v>
+        <v>-4.054601061937317</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.884016775043184</v>
+        <v>1.840716495737519</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5857507734521123</v>
+        <v>0.5489774238931366</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.814363808897462</v>
+        <v>3.792299799162076</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.198825517680882</v>
+        <v>-4.307076215945041</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.794897202495508</v>
+        <v>1.751596923189844</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5857507734521123</v>
+        <v>0.5489774238931366</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.826234297952876</v>
+        <v>3.80417028821749</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.491721274160294</v>
+        <v>-4.599971972424453</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.678949434422687</v>
+        <v>1.635649155117023</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5857507734521123</v>
+        <v>0.5489774238931366</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.827444832471819</v>
+        <v>3.805380822736434</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.678385402295102</v>
+        <v>-4.786636100559261</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.608405525396085</v>
+        <v>1.565105246090421</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5590118026275525</v>
+        <v>0.5222384530685767</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.815523192204405</v>
+        <v>3.79345918246902</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.824406089209064</v>
+        <v>-4.932656787473223</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.54507510336669</v>
+        <v>1.501774824061025</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5499287108336954</v>
+        <v>0.5131553612747197</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.80515118986428</v>
+        <v>3.783087180128895</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830323</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.916120098318649</v>
+        <v>-5.024370796582808</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.6705935564219</v>
+        <v>1.627293277116236</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5499287108336954</v>
+        <v>0.5131553612747197</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.967355246563324</v>
+        <v>3.945291236827939</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.947771757378618</v>
+        <v>-5.056022455642777</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.652779530761727</v>
+        <v>1.609479251456062</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5447602535892553</v>
+        <v>0.5079869040302796</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.959100810180474</v>
+        <v>3.937036800445089</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.75004401586814</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.029706575647501</v>
+        <v>-5.137957273911661</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.630235021022664</v>
+        <v>1.586934741717</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5348255080021751</v>
+        <v>0.4980521584431994</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.963369380396718</v>
+        <v>3.941305370661332</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332685</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.131682697895909</v>
+        <v>-5.239933396160068</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.598370210579204</v>
+        <v>1.555069931273539</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4328493857537675</v>
+        <v>0.3960760361947918</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.911109345503576</v>
+        <v>3.88904533576819</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231801</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.021676414418687</v>
+        <v>-5.129927112682847</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.634525611214268</v>
+        <v>1.591225331908603</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4560539576710427</v>
+        <v>0.419280608112067</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.917184975898116</v>
+        <v>3.895120966162731</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818516</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.878616838677761</v>
+        <v>-4.98686753694192</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.695999452232613</v>
+        <v>1.652699172926948</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.464067384261022</v>
+        <v>0.4272940347020463</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.926243042574078</v>
+        <v>3.904179032838692</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.577170113205923</v>
+        <v>-4.685420811470083</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.823839025303884</v>
+        <v>1.780538745998219</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7655141097328593</v>
+        <v>0.7287407601738836</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.114371960739716</v>
+        <v>4.09230795100433</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.601760357441107</v>
+        <v>-4.710011055705267</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.814974105362521</v>
+        <v>1.771673826056856</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7655141097328593</v>
+        <v>0.7287407601738836</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.115343138492427</v>
+        <v>4.093279128757041</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.550721981434587</v>
+        <v>-4.658972679698747</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.836232360144884</v>
+        <v>1.79293208083922</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7655141097328593</v>
+        <v>0.7287407601738836</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.116186042872182</v>
+        <v>4.094122033136797</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.509582686567956</v>
+        <v>-4.617833384832116</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.871726176965682</v>
+        <v>1.828425897660018</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8066534045994901</v>
+        <v>0.7698800550405144</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.159907718666306</v>
+        <v>4.13784370893092</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700472</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.412947774549316</v>
+        <v>-4.521198472813476</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.726564137897073</v>
+        <v>1.683263858591408</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.90328831661813</v>
+        <v>0.8665149670591543</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.034072662001424</v>
+        <v>4.012008652266039</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.543528509080159</v>
+        <v>-4.651779207344318</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.6778338881587</v>
+        <v>1.634533608853035</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7727075820872875</v>
+        <v>0.7359342325283118</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.959226265356883</v>
+        <v>3.937162255621498</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.379032174889197</v>
+        <v>-4.487282873153356</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.728059240911167</v>
+        <v>1.684758961605503</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9372039162782494</v>
+        <v>0.9004305667192737</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.042350884947543</v>
+        <v>4.020286875212157</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077623</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.301933573347324</v>
+        <v>-4.410184271611484</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.758086391964346</v>
+        <v>1.714786112658681</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9372039162782494</v>
+        <v>0.9004305667192737</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.041538595383972</v>
+        <v>4.019474585648587</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.312318768237214</v>
+        <v>-4.420569466501373</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.763801093133462</v>
+        <v>1.720500813827798</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9268187213883601</v>
+        <v>0.8900453718293844</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.045176257575111</v>
+        <v>4.023112247839726</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.330906926959439</v>
+        <v>-4.439157625223598</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.827202835420998</v>
+        <v>1.783902556115333</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9082305626661347</v>
+        <v>0.871457213107159</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.104860368118201</v>
+        <v>4.082796358382816</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.331205473655475</v>
+        <v>-4.439456171919634</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.823952427560882</v>
+        <v>1.780652148255217</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9079320159700988</v>
+        <v>0.8711586664111231</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.101550250918878</v>
+        <v>4.079486241183493</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.230382339965047</v>
+        <v>-4.338633038229206</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.868812575976444</v>
+        <v>1.82551229667078</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9203962314544526</v>
+        <v>0.8836228818954769</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.113559675148882</v>
+        <v>4.091495665413497</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.03960097921264</v>
+        <v>-4.147851677476799</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.94525437375595</v>
+        <v>1.901954094450286</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.11117759220686</v>
+        <v>1.074404242647884</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.22815774507887</v>
+        <v>4.206093735343485</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.932637621363218</v>
+        <v>-4.040888319627378</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.967876562633315</v>
+        <v>1.924576283327651</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.169642200166662</v>
+        <v>1.132868850607686</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.243073355592347</v>
+        <v>4.221009345856962</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.877307033461456</v>
+        <v>-3.985557731725616</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.024975734406079</v>
+        <v>1.981675455100414</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.224972788068424</v>
+        <v>1.188199438509448</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.311238644945463</v>
+        <v>4.289174635210077</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.865252906548494</v>
+        <v>-3.973503604812653</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.023483953072701</v>
+        <v>1.980183673767037</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.237026914981386</v>
+        <v>1.200253565422411</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.312157688994678</v>
+        <v>4.290093679259293</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.906408026116714</v>
+        <v>-4.014658724380874</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.008902535429549</v>
+        <v>1.965602256123884</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.195871795413165</v>
+        <v>1.15909844585419</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.289345247437882</v>
+        <v>4.267281237702496</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.838359463425185</v>
+        <v>-3.946610161689344</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.048972986384044</v>
+        <v>2.005672707078379</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.263920358104695</v>
+        <v>1.22714700854572</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.343025410930682</v>
+        <v>4.320961401195297</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013428</v>
+        <v>3.645256780013421</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.069959856594686</v>
+        <v>-4.178210554858845</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.976535499289837</v>
+        <v>1.933235219984173</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.263920358104695</v>
+        <v>1.22714700854572</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.363228081104277</v>
+        <v>4.341164071368891</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.120011402123906</v>
+        <v>-4.228262100388065</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.940121117145031</v>
+        <v>1.896820837839367</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.263920358104695</v>
+        <v>1.22714700854572</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.346834317171158</v>
+        <v>4.324770307435773</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.29511823470035</v>
+        <v>-4.40336893296451</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.83033029770792</v>
+        <v>1.787030018402256</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.263920358104695</v>
+        <v>1.22714700854572</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.307086230764625</v>
+        <v>4.28502222102924</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.099018081269827</v>
+        <v>-4.207268779533987</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.915792978077069</v>
+        <v>1.872492698771405</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.460020511535218</v>
+        <v>1.423247161976243</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.431768941819879</v>
+        <v>4.409704932084494</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395084</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.945992689156543</v>
+        <v>-4.054243387420702</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.076174134495287</v>
+        <v>2.032873855189623</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.613045903648502</v>
+        <v>1.576272554089527</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.622755176660753</v>
+        <v>4.600691166925368</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.741278332791146</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.974300003029813</v>
+        <v>-4.082550701293973</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.252317433854272</v>
+        <v>2.209017154548607</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.613045903648502</v>
+        <v>1.576272554089527</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.810221401569046</v>
+        <v>4.788157391833661</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.140893228143335</v>
+        <v>-4.249143926407495</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.155083095162946</v>
+        <v>2.111782815857281</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.44645267853498</v>
+        <v>1.409679328976004</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.679668417855015</v>
+        <v>4.65760440811963</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.11785743478177</v>
+        <v>-4.226108133045929</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.16797381516929</v>
+        <v>2.124673535863626</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.44645267853498</v>
+        <v>1.409679328976004</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.683344820516733</v>
+        <v>4.661280810781347</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399466</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.088611454326073</v>
+        <v>-4.196862152590232</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.177290262475064</v>
+        <v>2.133989983169399</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.44645267853498</v>
+        <v>1.409679328976004</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.680962875640228</v>
+        <v>4.658898865904843</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.195537002203924</v>
+        <v>-4.303787700468083</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.131813282481558</v>
+        <v>2.088513003175894</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.339527130657129</v>
+        <v>1.302753781098153</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.614100786071153</v>
+        <v>4.592036776335767</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600700997</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.340555560711173</v>
+        <v>-4.448806258975332</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.075234661221893</v>
+        <v>2.031934381916229</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.19450857214988</v>
+        <v>1.157735222590904</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.528518453110038</v>
+        <v>4.506454443374652</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687008</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.45889732649589</v>
+        <v>-4.56714802476005</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.127829194165759</v>
+        <v>2.084528914860095</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.20519461071277</v>
+        <v>1.168421261153795</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.634861315505525</v>
+        <v>4.612797305770139</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790804</v>
+        <v>3.714879051790798</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.510307748816598</v>
+        <v>-4.618558447080757</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.105050722363415</v>
+        <v>2.06175044305775</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.20519461071277</v>
+        <v>1.168421261153795</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.632647012631464</v>
+        <v>4.610583002896078</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437332</v>
+        <v>3.704757949437326</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.58972720002435</v>
+        <v>-4.697977898288509</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.073186069954604</v>
+        <v>2.029885790648939</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.20519461071277</v>
+        <v>1.168421261153795</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.632550140705753</v>
+        <v>4.610486130970368</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298399</v>
+        <v>3.736804952298392</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.685190197941568</v>
+        <v>-4.793440896205727</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.034994764345759</v>
+        <v>1.991694485040095</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.20519461071277</v>
+        <v>1.168421261153795</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.632544034263796</v>
+        <v>4.61048002452841</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218002</v>
+        <v>3.715372960217994</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.620814287090853</v>
+        <v>-4.729064985355012</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.058841525248656</v>
+        <v>2.015541245942992</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.269570521563485</v>
+        <v>1.23279717200451</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.669265977336836</v>
+        <v>4.64720196760145</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353538</v>
+        <v>3.73608941335353</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.676183449223046</v>
+        <v>-4.784434147487206</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.042427678143505</v>
+        <v>1.999127398837841</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.269570521563485</v>
+        <v>1.23279717200451</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.674999795084562</v>
+        <v>4.652935785349177</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113281</v>
+        <v>3.736822870113273</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.721621229053873</v>
+        <v>-4.829871927318033</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.023790929554107</v>
+        <v>1.980490650248442</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.226725530885326</v>
+        <v>1.18995218132635</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.648831164020599</v>
+        <v>4.626767154285214</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79027250011369</v>
+        <v>3.790272500113682</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.633414394906295</v>
+        <v>-4.741665093170455</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.078948056063457</v>
+        <v>2.035647776757792</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.226725530885326</v>
+        <v>1.18995218132635</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.668705556870917</v>
+        <v>4.646641547135532</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.527379399700986</v>
+        <v>-4.635630097965145</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.105062754670308</v>
+        <v>2.061762475364644</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.226725530885326</v>
+        <v>1.18995218132635</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.652406257395645</v>
+        <v>4.63034224766026</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307667</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.344167736567891</v>
+        <v>-4.45241843483205</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.180778369387592</v>
+        <v>2.137478090081927</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.226725530885326</v>
+        <v>1.18995218132635</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.654837206859691</v>
+        <v>4.632773197124306</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863548</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.27244628955404</v>
+        <v>-4.380696987818199</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.175258134041022</v>
+        <v>2.131957854735357</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.298446977899177</v>
+        <v>1.261673628340201</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.663661260915891</v>
+        <v>4.641597251180506</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394108</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.250073263946334</v>
+        <v>-4.358323962210493</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.131123090205276</v>
+        <v>2.087822810899612</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.309702729012078</v>
+        <v>1.272929379453102</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.617330457504804</v>
+        <v>4.595266447769419</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456724</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.283089559857078</v>
+        <v>-4.391340258121238</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.303114776726333</v>
+        <v>2.259814497420669</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.240265352345326</v>
+        <v>1.203492002786351</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.760866236390108</v>
+        <v>4.738802226654722</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883678</v>
+        <v>3.713762536883671</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.27156192420747</v>
+        <v>-4.379812622471629</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.299647056814426</v>
+        <v>2.256346777508761</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.299266010546689</v>
+        <v>1.262492660987713</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.788187857139174</v>
+        <v>4.766123847403789</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236299</v>
+        <v>3.71715069923629</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.368903425549838</v>
+        <v>-4.477154123813998</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.264378568799267</v>
+        <v>2.221078289493603</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.254845828381201</v>
+        <v>1.218072478822225</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.76520386036167</v>
+        <v>4.743139850626285</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427686</v>
+        <v>3.705201079427678</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.454759454889805</v>
+        <v>-4.563010153153964</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.231287239256118</v>
+        <v>2.187986959950454</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.212469759155065</v>
+        <v>1.17569640959609</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.741029301018827</v>
+        <v>4.718965291283442</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610377</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.463596252305924</v>
+        <v>-4.571846950570084</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.210171722110172</v>
+        <v>2.166871442804508</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.205027586513715</v>
+        <v>1.168254236954739</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.718983199254518</v>
+        <v>4.696919189519133</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667456</v>
+        <v>3.715544411667449</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.554978814871383</v>
+        <v>-4.663229513135542</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.183783208129038</v>
+        <v>2.140482928823374</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.16846270179437</v>
+        <v>1.131689352235394</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.707208779467962</v>
+        <v>4.685144769732576</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889192</v>
+        <v>3.673978374889185</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.543272096884377</v>
+        <v>-4.651522795148536</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.290594153148108</v>
+        <v>2.247293873842444</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.180169419781377</v>
+        <v>1.143396070222401</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.816361068084433</v>
+        <v>4.794297058349047</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409567</v>
+        <v>3.68247609940956</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.443608592800715</v>
+        <v>-4.551859291064874</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.333491893512978</v>
+        <v>2.290191614207314</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.243356502985063</v>
+        <v>1.206583153426087</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.857305656738049</v>
+        <v>4.835241647002664</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452567</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.453924690967066</v>
+        <v>-4.562175389231226</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.542270287524495</v>
+        <v>2.498970008218831</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.243356502985063</v>
+        <v>1.206583153426087</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.070210490016107</v>
+        <v>5.048146480280722</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762289</v>
+        <v>3.623960959762281</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.453830722949694</v>
+        <v>-4.562081421213853</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.541486541643534</v>
+        <v>2.49818626233787</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.243726364332381</v>
+        <v>1.206953014773405</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.069611073736588</v>
+        <v>5.047547064001202</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988019</v>
+        <v>3.633213467988012</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.461049547149538</v>
+        <v>-4.569300245413698</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.53283099790795</v>
+        <v>2.489530718602285</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.243726364332381</v>
+        <v>1.206953014773405</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.063843059680941</v>
+        <v>5.041779049945556</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740918</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.4601011240315</v>
+        <v>-4.568351822295659</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.533210367155165</v>
+        <v>2.489910087849501</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.243726364332381</v>
+        <v>1.206953014773405</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.063843059680941</v>
+        <v>5.041779049945556</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.617169582287124</v>
+        <v>-4.725420280551283</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.483110591834008</v>
+        <v>2.439810312528343</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.243726364332381</v>
+        <v>1.206953014773405</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.076570667662033</v>
+        <v>5.054506657926648</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.611177335498312</v>
+        <v>-4.719428033762472</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.48745348897392</v>
+        <v>2.444153209668256</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.243726364332381</v>
+        <v>1.206953014773405</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.078516666086421</v>
+        <v>5.056452656351036</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.522619374367545</v>
+        <v>-4.630870072631704</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.516530809443996</v>
+        <v>2.473230530138331</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.243726364332381</v>
+        <v>1.206953014773405</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.07217080210419</v>
+        <v>5.050106792368805</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383087</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.504860296864471</v>
+        <v>-4.61311099512863</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.522943117884221</v>
+        <v>2.479642838578557</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.243726364332381</v>
+        <v>1.206953014773405</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.071479479543186</v>
+        <v>5.0494154698078</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.405230145815403</v>
+        <v>-4.513480844079562</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.575577364212435</v>
+        <v>2.532277084906771</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.343356515381449</v>
+        <v>1.306583165822473</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.144039756081213</v>
+        <v>5.121975746345828</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.77535709745527</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.454629654504414</v>
+        <v>-4.562880352768573</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.744971826235557</v>
+        <v>2.701671546929893</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.353615348813193</v>
+        <v>1.316841999254218</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.339349321638987</v>
+        <v>5.317285311903601</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.913861647214537</v>
+        <v>3.903525342880116</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.545025196181179</v>
+        <v>-4.653090137854425</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.696002282667713</v>
+        <v>2.652776305998414</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.353615348813193</v>
+        <v>1.226632214168366</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.326537994741849</v>
+        <v>5.250348113954952</v>
       </c>
     </row>
   </sheetData>
